--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0002.xlsx
@@ -580,11 +580,11 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Đến với Cảng Vách Đá, hãy bắt đầu hành trình bằng việc ghé thăm Ruins Cầu Farrow, chứng nhân im lặng cho sự chia rẽ bởi đức tin giữa Septimont và Ragunna. Tiếp tục dọc theo Con Đường Anh Hùng, lối mòn cổ xưa từng được các Chiến Binh Đấu Vật đi qua trong cuộc hành hương đến đấu trường huyền thoại Colosseum Olymdos. Những tần số cảm xúc của họ vẫn còn vương vấn dọc đường, dẫn lối du khách đến thành phố nguy nga trên đỉnh Capitoline Hill, nơi Pháo Đài Đại Bàng hùng vĩ sừng sững.
+          <t>Đến với Cảng Vách Đá, hãy bắt đầu hành trình bằng việc ghé thăm Tàn Tích Cầu Farrow, chứng nhân im lặng cho sự chia rẽ bởi đức tin giữa Septimont và Ragunna. Tiếp tục dọc theo Con Đường Anh Hùng, lối mòn cổ xưa từng được các Chiến Binh Đấu Vật đi qua trong cuộc hành hương đến đấu trường huyền thoại Colosseum Olymdos. Những tần số cảm xúc của họ vẫn còn vương vấn dọc đường, dẫn lối du khách đến thành phố nguy nga trên đỉnh Đồi Capitoline, nơi Pháo Đài Đại Bàng hùng vĩ sừng sững.
 ...
-Hãy bắt đầu ngày mới bằng việc ghé thăm Colosseum Olymdos để chứng kiến trận đấu của các Chiến Binh Đấu Vật (kiểm tra lịch sự kiện trước và chọn trận đấu yêu thích). Explore khu vực nghỉ ngơi công cộng của các Chiến Binh Đấu Vật hàng đầu để có cái nhìn hậu trường. Tiếp theo, hãy đến Thung Lũng Glory, nơi những vũ khí được chạm khắc trên đá tưởng nhớ các anh hùng và Chiến Binh Đấu Vật huyền thoại của Septimont, những cái tên vẫn còn vang vọng qua thời gian.
+Hãy bắt đầu ngày mới bằng việc ghé thăm Colosseum Olymdos để chứng kiến trận đấu của các Chiến Binh Đấu Vật (kiểm tra lịch sự kiện trước và chọn trận đấu yêu thích). Khám phá khu vực nghỉ ngơi công cộng của các Chiến Binh Đấu Vật hàng đầu để có cái nhìn hậu trường. Tiếp theo, hãy đến Thung Lũng Vinh Quang, nơi những vũ khí được chạm khắc trên đá tưởng nhớ các anh hùng và Chiến Binh Đấu Vật huyền thoại của Septimont, những cái tên vẫn còn vang vọng qua thời gian.
 ...
-Hãy lên cáp treo và lướt xuống khu chợ Caracalla sầm uất, nơi bạn có thể nhâm nhi những loại trà đặc trưng tại Solis, xem qua vũ khí và giáp trụ tại Silver Helmet Cửa hàng, và mua những món quà lưu niệm độc đáo tại Xưởng Pygmalion. Kết thúc hành trình bằng một buổi thư giãn tại Nhà Tắm Thermes, nơi dòng nước ấm sẽ xoa dịu mọi mệt nhọc sau chuyến phiêu lưu.
+Hãy lên cáp treo và lướt xuống khu chợ Caracalla sầm uất, nơi bạn có thể nhâm nhi những loại trà đặc trưng tại Solis, xem qua vũ khí và giáp trụ tại Cửa Hàng Mũ Bạc, và mua những món quà lưu niệm độc đáo tại Xưởng Pygmalion. Kết thúc hành trình bằng một buổi thư giãn tại Nhà Tắm Thermes, nơi dòng nước ấm sẽ xoa dịu mọi mệt nhọc sau chuyến phiêu lưu.
 ...
 Bản hướng dẫn này chỉ mang tính tham khảo. Hãy tự do lên kế hoạch cho ngày của mình theo nhịp độ riêng. Lịch trình tuyệt vời nhất luôn là lịch trình phù hợp với bạn. Chúc bạn có những trải nghiệm khó quên tại Septimont!</t>
         </is>
@@ -665,7 +665,7 @@
 Một số nhà sinh thái học cho rằng loài này đã tồn tại từ Kỷ Nguyên Ngàn Đảo. Dù hiếm gặp, chúng vẫn sống sót, có lẽ nhờ khả năng nhạy bén với những thay đổi môi trường. Đôi râu trên đầu chúng có thể phát hiện những biến đổi nhỏ trong môi trường, giúp chúng tránh nguy hiểm từ trước. Mô hình mà ta quan sát được chỉ ra một lời giải thích thực tế hơn: Scourgewing cảm nhận được thảm họa sắp đến, và có lẽ, theo cách riêng của chúng, đang cố gắng cảnh báo chúng ta.
 Chúng không phải là điềm báo của tai họa, mà là những sứ giả báo trước.
 ...
-Địa điểm đáng chú ý: &lt;color=YellowD&gt;Tower Quan Sát tại Mournfell Canyon, Mộ Dragon Tro tại Dãy Border Mountains&lt;/color&gt;</t>
+Địa điểm đáng chú ý: &lt;color=YellowD&gt;Tháp Quan Sát tại Hẻm Núi Mournfell, Mộ Rồng Tro tại Dãy Núi Biên Giới&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
           <t>Bất kỳ đấu sĩ nào ở Septimont cũng biết nơi này. Đây là chốn săn bắn và thử thách bản lĩnh của chúng ta.
 Xác rồng nằm ngoài kia thu hút đủ loại Tacet Discord, thú dữ và những đấu sĩ như chúng ta—những kẻ săn đuổi vinh quang. Tôi chắc chắn Flavio đã ở đây. Tôi nhìn thấy áo giáp của hắn trong một đại sảnh cũ. Huy hiệu gia tộc bị xé đôi, có lẽ là cách hắn đoạn tuyệt với dòng họ. Tôi cũng không thể không để ý những vết lõm và vết rách khắp bộ giáp, có vết sâu, có vết chỉ là xước. Với chúng tôi, đó là huân chương.
 Người dân địa phương kể rằng bộ giáp sần sùi ấy từng thuộc về một người đã thuần phục một con rồng khủng khiếp—một con Scourgewing. Hắn đối mặt với nó một mình và bắt nó khuất phục. Trong khi tôi chìm đắm trong men rượu vì cái chết của em gái, Flavio lại đang chinh phục thế giới hoang dã bằng thanh kiếm của mình. Không ai biết hắn đã đi đâu cùng con rồng, nhưng tôi biết hắn đang bước trên con đường vinh quang... Hắn đang trở thành huyền thoại.
-Một tốp đấu sĩ ngông nghênh đi ngang qua tôi, vũ khí đầy mình. Tôi nghe lỏm được họ nói chuyện. Họ đang truy lùng một con Scourgewing gần vùng Border Mountains. Nhưng không như Flavio, họ không tìm kiếm một cuộc đấu tay đôi, mà chỉ là một cuộc săn bẩn thỉu.
+Một tốp đấu sĩ ngông nghênh đi ngang qua tôi, vũ khí đầy mình. Tôi nghe lỏm được họ nói chuyện. Họ đang truy lùng một con Scourgewing gần vùng Núi Biên Giới. Nhưng không như Flavio, họ không tìm kiếm một cuộc đấu tay đôi, mà chỉ là một cuộc săn bẩn thỉu.
 Chắc họ sẽ kéo nó về thành phố và bán đi kiếm lời. Đối với họ, đó chỉ là vậy thôi.</t>
         </is>
       </c>
@@ -882,7 +882,7 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>Trên dãy Biên Cương, giữa đống tro tàn của một con rồng gục ngã, trận chiến giữa người và rồng bắt đầu.
-Gladiator nín thở, thanh kiếm chĩa thẳng lên trời, như một bức tượng sống. Không khí rung chuyển bởi tiếng gầm vang trời khi đôi cánh rực rỡ xòe rộng, phủ bóng tối xuống mặt đất. Một kẻ sẽ sa xuống, một kẻ sẽ vươn lên. Chỉ một trong hai được quyền chiến thắng.
+Đấu sĩ nín thở, thanh kiếm chĩa thẳng lên trời, như một bức tượng sống. Không khí rung chuyển bởi tiếng gầm vang trời khi đôi cánh rực rỡ xòe rộng, phủ bóng tối xuống mặt đất. Một kẻ sẽ sa xuống, một kẻ sẽ vươn lên. Chỉ một trong hai được quyền chiến thắng.
 Khi mặt trời nhuộm đỏ núi rừng, con rồng cuối cùng cũng cúi đầu khuất phục, đầu hàng trước người đã chế ngự được nơi hoang dã.
 Ngày hôm ấy, một anh hùng nữa đã ra đời trên bãi thử thách.</t>
         </is>
@@ -1187,16 +1187,16 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chuyến lưu diễn này đã dẫn ta đến một người bạn. {Male=Anh ấy;Female=Cô ấy} hiểu được những cảm xúc chân thật trong bản nhạc của ta, và tự nhiên, ta kể hết những câu chuyện về quê hương mình. Ta trải lòng với người lạ mặt này mà không hề ngần ngại, và kỳ lạ thay, lòng ta nhẹ nhõm hơn. {Male=Anh ấy;Female=Cô ấy} lắng nghe như thể {Male=anh;Female=cô} thực sự thấu hiểu. Điều gì đã khiến {Male=anh ấy;Female=cô ấy} thấu hiểu nỗi tuyệt vọng như vậy? Ta mong gặp lại {Male=anh ấy;Female=cô ấy} trong buổi hòa nhạc tới. Ta muốn biết thêm về câu chuyện của {Male=anh ấy;Female=cô ấy} và ý nghĩa của "bắt đầu lại" mà {Male=anh ấy;Female=cô ấy} nói đến.
-Tricktown, {Male=anh ấy;Female=cô ấy} không đến.
-Peyero, {Male=anh ấy;Female=cô ấy} không đến.
-Mendon, {Male=anh ấy;Female=cô ấy} không đến.
-Skob, {Male=anh ấy;Female=cô ấy} không đến.
-Dolores, {Male=anh ấy;Female=cô ấy} không đến.
-Kentart, {Male=anh ấy;Female=cô ấy} không đến.
-Korr, {Male=anh ấy;Female=cô ấy} không đến.
+          <t>Chuyến lưu diễn này đã dẫn ta đến một người bạn. {Male=He;Female=She} hiểu được những cảm xúc chân thật trong bản nhạc của ta, và tự nhiên, ta kể hết những câu chuyện về quê hương mình. Ta trải lòng với người lạ mặt này mà không hề ngần ngại, và kỳ lạ thay, lòng ta nhẹ nhõm hơn. {Male=He;Female=She} lắng nghe như thể {Male=he;Female=she} thực sự thấu hiểu. Điều gì đã khiến {Male=him;Female=her} thấu hiểu nỗi tuyệt vọng như vậy? Ta mong gặp lại {Male=him;Female=her} trong buổi hòa nhạc tới. Ta muốn biết thêm về câu chuyện của {Male=his;Female=her} và ý nghĩa của "bắt đầu lại" mà {Male=he;Female=she} nói đến.
+Tricktown, {Male=he;Female=she} không đến.
+Peyero, {Male=he;Female=she} không đến.
+Mendon, {Male=he;Female=she} không đến.
+Skob, {Male=he;Female=she} không đến.
+Dolores, {Male=he;Female=she} không đến.
+Kentart, {Male=he;Female=she} không đến.
+Korr, {Male=he;Female=she} không đến.
 …
-&lt;color=RedD&gt;{Male=Anh ấy;Female=Cô ấy} sẽ không bao giờ đến.&lt;/color&gt;</t>
+&lt;color=RedD&gt;{Male=He;Female=She} sẽ không bao giờ đến.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1277,16 +1277,16 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1. Đã cầu nguyện các Thần Linh đến và phục hồi mọi thứ. Fail.
-2. Đã tìm kiếm các thí nghiệm về tái sinh và bất tử. Fail.
-3. Đã tìm kiếm sự sống trong Hiện Tượng Sóng Xói Mòn. Fail.
+          <t>1. Đã cầu nguyện các Thần Linh đến và phục hồi mọi thứ. Thất bại.
+2. Đã tìm kiếm các thí nghiệm về tái sinh và bất tử. Thất bại.
+3. Đã tìm kiếm sự sống trong Hiện Tượng Sóng Xói Mòn. Thất bại.
 ...
-47. Fail.
-84. Fail.
+47. Thất bại.
+84. Thất bại.
 ...
-126. Fail. 132. Fail.
+126. Thất bại. 132. Thất bại.
 ...
-189. Fail.
+189. Thất bại.
 ...
 &lt;color=RedD&gt;THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI, THẤT BẠI...&lt;/color&gt;
 &lt;color=RedD&gt;Tại sao... tại sao ta lại THẤT BẠI nữa?!&lt;/color&gt;
@@ -1365,14 +1365,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>@realAbbowser: Ngươi đã đặt rương ở những màn đó chưa?
-@recruitZ: Xin lỗi, tiến độ đang chậm 20% so với kế hoạch vì thiếu nhân lực.
-@realAbbowser: Sao lại thế được? Ta đã cử cho ngươi mười thằng lính cơ mà!
-@recruitZ: Năm đứa bị đưa vào bệnh viện sau khi gia nhập New Black Shores. Ba đứa đi tỏ tình với Primus trong Order of the D rồi biến mất luôn. Hai đứa cuối thì ông bán cho nhà Montellis rồi.
-@realAbbowser: Khoan, vậy là ngươi đang làm việc một mình à? Ngươi là Echo người thật à?
-@realAbbowser: Thôi, đừng có viện cớ nữa. Ngươi phải làm việc chủ động hơn!
-@realAbbowser: Ta còn chưa kể đến cái rương giả khổng lồ ngươi đặt mà cắn ta nữa! Lần sau mà hỏng việc là ngươi chết!
-@recruitZ: Vâng ạ.</t>
+          <t>@realAbbowser: Have you set up the chests in those levels?
+@recruitZ: Sorry, the progress is 20% behind schedule due to a lack of manpower.
+@realAbbowser: How can this be? I sent you ten minions!
+@recruitZ: Five of them were sent to the hospital after joining the New Black Shores. Three of them went to confess to the Primus in the Order of the D and never returned. You sold the last two to the Montellis.
+@realAbbowser: Wait, so you're doing 10 guys' jobs? Are you a human Echo?
+@realAbbowser: No, I mean, just quit all these excuses. You should work more proactively!
+@realAbbowser: I haven't even brought up that giant Chest Mimic you set up that bit me! You'll be cooked if you screw up again!
+@recruitZ: Okay.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>@realAbbowser: Ê, ngươi! Xong chưa?
+          <t>@realAbbowser: Ê, mày! Xong chưa?
 @recruitZ: Với tiến độ hiện tại, chúng ta sẽ hoàn thành đúng hạn. Tuy nhiên, một số vật liệu bị thiếu, như bánh snack Cube và bánh ngọt.
 @realAbbowser: Sao lại thiếu được?
 @recruitZ: Lúc tôi kiểm kê thì vẫn đủ. Có thể ai đó đã ăn vụng. Chúng ta có thể kiểm tra camera giám sát.
@@ -1515,9 +1515,9 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>@realAbbowser: Này, xong hết chưa? {Male=Hắn;Female=Cô ấy} sắp đến nơi rồi đấy.
+          <t>@realAbbowser: Này, xong hết chưa? {Male=He;Female=She} sắp đến nơi rồi đấy.
 @recruitZ: Xong rồi. Mọi thứ đều theo kế hoạch.
-@realAbbowser: Tốt. Mau về phía ta ngay!
+@realAbbowser: Tốt. Mau về phía tao ngay!
 @recruitZ: Vâng. Tôi sẽ tìm cách đến đó.</t>
         </is>
       </c>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ragunna Echoes Archive
+          <t>Lưu Trữ Echoes Ragunna
 ...Năng lượng của Common Echoes đến từ Sentinel và những thế giới bí ẩn sâu thẳm hơn cả đại dương. Dưới sự dẫn dắt của Sentinel, Order of the Deep nhanh chóng kiểm soát Common Echoes và sử dụng chúng để dẫn dắt dân chúng...
 ...Cuộc khủng hoảng thiếu hụt Common Echoes nghiêm trọng đầu tiên đã xảy ra, kéo theo sự gia tăng buôn lậu và mua bán Echoes riêng lẻ trong giới quý tộc thành phố. Cần phải nâng cấp công nghệ cắt tần số ngay lập tức để giảm thời gian cắt và hợp nhất các tần số TD khác nhau, từ đó thiết lập dây chuyền sản xuất hàng loạt cho các Echoes với hình dạng và khả năng đa dạng...
 ...Order of the Deep đã giành được quyền kiểm soát trực tiếp công nghệ tổng hợp tầm xa. Các Common Echoes họ tạo ra sẽ duy trì trạng thái tổng hợp tần số vĩnh viễn trong phạm vi Rinascita, chỉ được tháo dỡ trong những trường hợp hiếm hoi. Điều này đánh dấu bước đột phá về giới hạn không gian và thời gian của Common Echoes, cũng như cải thiện đáng kể độ ổn định của chúng...
-...Khi sự phản đối gia tăng, Order đã phát triển một loại Echoes mới: La Guardia. Họ đóng vai trò như đôi mắt cảnh giác và cánh tay thực thi của Order, và sự ra đời của họ đã khôi phục niềm tin của công chúng vào các Common Echoes thông thường...
-...Các thí nghiệm về cấy ghép và định hình ý thức của Echoes trong Fabricatorium đã có tiến triển. Tuy nhiên, dữ liệu từ các mẫu đầu tiên không thể áp dụng cho bất kỳ Common Echoes nào, và sự ổn định của ý thức của chúng vẫn cần được hoàn thiện thêm...</t>
+...Khi sự phản đối gia tăng, Order đã phát triển một loại Echo mới: La Guardia. Họ đóng vai trò như đôi mắt cảnh giác và cánh tay thực thi của Order, và sự ra đời của họ đã khôi phục niềm tin của công chúng vào các Common Echoes thông thường...
+...Các thí nghiệm về cấy ghép và định hình ý thức của Echoes trong Fabricatorium đã có tiến triển. Tuy nhiên, dữ liệu từ các mẫu đầu tiên không thể áp dụng cho bất kỳ Common Echo nào, và sự ổn định của ý thức của chúng vẫn cần được hoàn thiện thêm...</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>"Biên bản cuộc họp \"Dự án Echoes Tái Sinh\"
-- Nhiều Tacet Discord vốn đã sở hữu ý thức. Ngay cả sau khi bị cắt và bắc cầu tần số, ý thức hỗn loạn của chúng vẫn tồn tại. Điều đó có nghĩa là sau khi được ổn định thành Echoes Thông thường, chúng vẫn có xu hướng tiến hóa bằng cách hấp thụ Dư Âm. Dù chúng ta đã kiềm chế được bản năng hấp thụ này sau khi cắt tần số, ngăn chặn sự tiến hóa hỗn loạn của chúng, nhưng để loại bỏ hoàn toàn ý thức của chúng...
-- Có lẽ ta nên thay đổi hướng đi và tạo ra những mô-đun ý thức hoàn toàn mới. Chúng ta có thể cấy vào Echoes chỉ những ý thức cần thiết, ép buộc chúng ghi đè lên ý thức gốc. Sức mạnh mà Bọn Họ ban cho cho phép ta làm điều này. Ta đã thử nghiệm rồi.
-- Ghi đè ý thức sẽ chỉ khiến Echoes Thông thường càng bất ổn và phá vỡ các phương pháp tạo ra chúng đã được thiết lập.
-- Ta nghĩ có thể có giải pháp. Mô-đun ý thức mới có thể được cấy sâu vào ý thức gốc của Echoes, chỉ hoạt động khi cần thiết. Trong lúc đó, chúng ta vẫn tiếp tục nghiên cứu cải thiện tính ổn định của quá trình biến đổi ý thức. Nhưng có một điều, nếu ý thức sâu hơn được kích hoạt, nó sẽ không thể đảo ngược.
-- Chúng ta phải trì hoãn việc kích hoạt vô thời hạn cho đến khi đảm bảo được sự ổn định của Echoes sau khi biến đổi.</t>
+          <t>"Biên bản cuộc họp \"Dự án Echo Tái Sinh\"
+- Nhiều Tacet Discord vốn đã sở hữu ý thức. Ngay cả sau khi bị cắt và bắc cầu tần số, ý thức hỗn loạn của chúng vẫn tồn tại. Điều đó có nghĩa là sau khi được ổn định thành Echo Thông thường, chúng vẫn có xu hướng tiến hóa bằng cách hấp thụ Dư Âm. Dù chúng ta đã kiềm chế được bản năng hấp thụ này sau khi cắt tần số, ngăn chặn sự tiến hóa hỗn loạn của chúng, nhưng để loại bỏ hoàn toàn ý thức của chúng...
+- Có lẽ ta nên thay đổi hướng đi và tạo ra những mô-đun ý thức hoàn toàn mới. Chúng ta có thể cấy vào Echo chỉ những ý thức cần thiết, ép buộc chúng ghi đè lên ý thức gốc. Sức mạnh mà Bọn Họ ban cho cho phép ta làm điều này. Ta đã thử nghiệm rồi.
+- Ghi đè ý thức sẽ chỉ khiến Echo Thông thường càng bất ổn và phá vỡ các phương pháp tạo ra chúng đã được thiết lập.
+- Ta nghĩ có thể có giải pháp. Mô-đun ý thức mới có thể được cấy sâu vào ý thức gốc của Echo, chỉ hoạt động khi cần thiết. Trong lúc đó, chúng ta vẫn tiếp tục nghiên cứu cải thiện tính ổn định của quá trình biến đổi ý thức. Nhưng có một điều, nếu ý thức sâu hơn được kích hoạt, nó sẽ không thể đảo ngược.
+- Chúng ta phải trì hoãn việc kích hoạt vô thời hạn cho đến khi đảm bảo được sự ổn định của Echo sau khi biến đổi.</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ta muốn học thật nhiều nhạc cụ. Ta muốn hiểu mọi âm thanh trong âm nhạc.
-Cô Searle bảo rằng nhiều nhạc trưởng đều thành thạo nhiều loại nhạc cụ. Ta cũng muốn được như vậy.
-Nếu ta có thể khiến một dàn nhạc tái hiện được bản nhạc hoàn hảo trong đầu mình, chắc hẳn đó sẽ là niềm vui lớn nhất của ta.
-Liệu ngày đó có đến không, khi ta có thể nhận biết và điều khiển chính xác âm thanh của từng nhạc cụ, biến mỗi nốt nhạc thành tiếng thét đầy nhiệt huyết?
-Cô Searle còn nói rằng đôi khi ta nên buông bỏ ham muốn kiểm soát và để dàn nhạc được tự do thở, tự do sáng tạo.
-Nhưng nếu ta làm vậy, làm sao ta chắc chắn được bản nhạc dưới sự chỉ huy của mình sẽ hoàn hảo?</t>
+          <t>Tao muốn học thật nhiều nhạc cụ. Tao muốn hiểu mọi âm thanh trong âm nhạc.
+Cô Searle bảo rằng nhiều nhạc trưởng đều thành thạo nhiều loại nhạc cụ. Tao cũng muốn được như vậy.
+Nếu tao có thể khiến một dàn nhạc tái hiện được bản nhạc hoàn hảo trong đầu mình, chắc hẳn đó sẽ là niềm vui lớn nhất của tao.
+Liệu ngày đó có đến không, khi tao có thể nhận biết và điều khiển chính xác âm thanh của từng nhạc cụ, biến mỗi nốt nhạc thành tiếng thét đầy nhiệt huyết?
+Cô Searle còn nói rằng đôi khi tao nên buông bỏ ham muốn kiểm soát và để dàn nhạc được tự do thở, tự do sáng tạo.
+Nhưng nếu tao làm vậy, làm sao tao chắc chắn được bản nhạc dưới sự chỉ huy của mình sẽ hoàn hảo?</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} không bao giờ xuất hiện nữa.
+          <t>{Male=He;Female=She} không bao giờ xuất hiện nữa.
 Ta đã tìm ra con đường của riêng mình. Con đường mới này chính là con đường đúng đắn để ta hoàn thành bản giao hưởng sinh tử.
 Ta không cần bạn bè nữa. Tất cả những gì ta cần là một lưỡi kiếm sắc bén.</t>
         </is>
@@ -2356,8 +2356,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Tổng kết lại, vì Kerasaurs có thể thích ứng nhanh với Attribute Cộng hưởng của Gladiator, tốt nhất là chuẩn bị thật nhiều bẫy hoặc hạ gục nhanh trước khi chúng kịp thích ứng. Nếu không, cần ít nhất hai người thay phiên nhau săn đuổi.
-Nếu hôm đó, tôi cùng Master Cato đối đầu với Kerasaur, thì…</t>
+          <t>Tổng kết lại, vì Kerasaurs có thể thích ứng nhanh với Thuộc tính Cộng hưởng của Gladiator, tốt nhất là chuẩn bị thật nhiều bẫy hoặc hạ gục nhanh trước khi chúng kịp thích ứng. Nếu không, cần ít nhất hai người thay phiên nhau săn đuổi.
+Nếu hôm đó, tôi cùng Sư phụ Cato đối đầu với Kerasaur, thì…</t>
         </is>
       </c>
     </row>
@@ -2505,8 +2505,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kế hoạch với Kẻ Vô Danh... Ta không ngờ {Male=hắn;Female=cô ta} lại nhìn thấu ta dễ dàng như vậy.
-{Male=Hắn;Female:Cô ta} cũng đã trải qua chuyện tương tự sao? Dù vậy, {Male=hắn;Female:cô ta} vẫn đưa ra lời đề nghị. Và ta không có lý do gì để từ chối.
+          <t>Kế hoạch với Kẻ Vô Danh... Ta không ngờ {Male=he;Female=her} lại nhìn thấu ta dễ dàng như vậy.
+{Male=he;Female=she} cũng đã trải qua chuyện tương tự sao? Dù vậy, {Male=he;Female=her} vẫn đưa ra lời đề nghị. Và ta không có lý do gì để từ chối.
 Dù sao, chẳng ai muốn đối mặt với kẻ đứng sau đôi tay đó hơn ta. Ta cần hỏi hắn, tại sao số phận này lại bị áp đặt lên ta? Bằng quyền gì hắn tạo ra cuộc đời ta và bịa đặt sự tồn tại của ta?
 Nhưng... ta đã đợi quá lâu. Ta bắt đầu nghi ngờ liệu kế hoạch này có bao giờ thành công hay không. Ai thèm quan tâm đến một con tốt bị vứt đi chứ?
 Nhưng còn con đường nào khác nữa đây?</t>
@@ -2599,7 +2599,7 @@
 Ước gì mình được ra ngoài chơi. Hay ít nhất là về nhà. Nhưng mọi người đều tập trung quá… Hôm nay Chị Sophia khắc cả một bức tường. Chị ấy thật tuyệt vời.
 7:00 Tối
 Đi dạo một chút sau bữa tối. Thấy vài ngôi sao!
-11:00 Night Khuya
+11:00 Đêm Khuya
 Đến giờ đi ngủ rồi, dù mình chẳng buồn ngủ chút nào. Đôi khi việc tuân theo lịch trình cứ như một công việc nhàm chán. Nhưng hôm nay… cũng không tệ lắm.</t>
         </is>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>Trong Huyền Thoại Về Huy Hiệu Ba Anh Hùng, ngoài chiến công của Anh Hùng Trong Các Anh Hùng, còn có một câu chuyện ít người biết đến.
-Một võ sĩ đấu trường trẻ từng một mình leo lên đỉnh núi sau một cuộc săn. Khi trở về trại, đồng đội của anh vô cùng kinh ngạc, bởi "Kẻ Sát Dragon" này mang trên người hơn trăm vết thương lớn nhỏ. Rõ ràng anh đã trải qua một trận chiến kinh hoàng, một thử thách vượt ngoài sức tưởng tượng.
+Một võ sĩ đấu trường trẻ từng một mình leo lên đỉnh núi sau một cuộc săn. Khi trở về trại, đồng đội của anh vô cùng kinh ngạc, bởi "Kẻ Sát Rồng" này mang trên người hơn trăm vết thương lớn nhỏ. Rõ ràng anh đã trải qua một trận chiến kinh hoàng, một thử thách vượt ngoài sức tưởng tượng.
 Võ sĩ mỉm cười chua chát, thừa nhận thất bại của mình. Nhiều người nhớ về điều này như thất bại đầu tiên của "Anh Hùng Không Tì Vết". Thất bại thứ hai—bi kịch Fabianum—sẽ đến không lâu sau đó.
 Võ sĩ ấy chính là Magno, cựu Ephor của Septimont.</t>
         </is>
@@ -3063,13 +3063,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Khu Thử Nghiệm: Vùng Core, Cấp L4 (Phòng Phân Phối Điện Neon Tower Cũ)
+          <t>Khu Thử Nghiệm: Vùng Lõi, Cấp L4 (Phòng Phân Phối Điện Tháp Neon Cũ)
 Mức kết tinh Irideglow: ■■■□ (Vượt ngưỡng cảnh báo Cấp 3)
 Trong Thử Nghiệm Trường Số 20, sự quá tải của thiết bị ngăn chặn đã gây ra vết nứt không-thời gian cục bộ.
 Thiết bị Thu Nhặt Than Thở đã chặn được một tần số nguồn gốc bất định.
 Phân tích dấu hiệu hoàn tất—vùng nguồn gốc sơ bộ: La███Roi.
 Giải mã tần số thất bại…
-Signal đang phân rã…
+Tín hiệu đang phân rã…
 Toàn bộ nhân sự sơ tán ngay lập tức!</t>
         </is>
       </c>
@@ -3158,7 +3158,7 @@
 Đồ nhà quê không biết thưởng thức. Rồi một ngày, cậu sẽ hiểu được sự tinh tế của nước ngọt vị tiêu. ——Firi
 Sao tất cả lũ chuột lang nước ở đây đều được đặt tên theo các tuyến đường sắt... Nếu hôm đó tớ đi tàu đi tìm cô ấy, liệu mọi chuyện có khác đi không? ——Aoba
 ……
-Tớ đến quán cà phê mà Aoba từng nhắc tới. Chúng ta chưa từng gặp nhau ở đây, nhưng tớ nhận ra Dodget chữ của cậu ấy ở đâu cũng được. ——Ichika
+Tớ đến quán cà phê mà Aoba từng nhắc tới. Chúng ta chưa từng gặp nhau ở đây, nhưng tớ nhận ra nét chữ của cậu ấy ở đâu cũng được. ——Ichika
 Hôm nay tớ được phỏng vấn trên đài địa phương với tư cách chủ quán! Lần đầu lên tivi... xấu hổ quá đi! Nhưng... nếu những mối liên kết của con người giống như mạng lưới đường sắt, thì có lẽ một ngày nào đó, chuyến tàu từ ga nhỏ này sẽ chạy thẳng đến nơi bố tớ đang ở. ——Miki
 Nơi này khá thú vị đấy. Có tiềm năng đầu tư thực sự! Nhưng chủ quán bảo cô ấy hài lòng với nó như thế này và lo rằng khách quen sẽ không tìm thấy nếu dời đi. Tớ không hiểu. Chỉ cần treo biển là xong mà. ——Eriko
 ……
@@ -3317,7 +3317,7 @@
         <is>
           <t>Gửi người tốt bụng tìm thấy mảnh giấy này:
 Exoswarm và ta không thể trụ vững được nữa.
-Những ai bị Void Storm cuốn đi sẽ đi về đâu?
+Những ai bị Bão Hư Không cuốn đi sẽ đi về đâu?
 Ước gì ta có thể trở về với ánh sáng như Soliskin.
 Ước gì ta hóa thành một tia sáng, mãi mãi chiếu rọi con gái ta.
 Người lạ tốt bụng, hãy mang những miếng dán, đồ tiếp tế và mảnh giấy trước đến cho con gái ta.
@@ -3396,7 +3396,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Gửi {Male=anh;Female=chị} ơi:
+          <t>Gửi {Male=big brother;Female=big sister} ơi:
 Khi mẹ nói mẹ sẽ đi xa lâu ngày, ý mẹ là sẽ "trở về với ánh sáng, như Soliskin" phải không?
 Lâu lắm rồi con biết ngày này sẽ đến. Mẹ sẽ ra đi, và con cũng vậy.
 Thật ra, con đáng lẽ phải "trở về với ánh sáng" từ lâu rồi. Con ở lại chỉ vì mẹ.
@@ -3515,7 +3515,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Quy trình Vận hành và Danh sách Liên lạc Được Phê duyệt cho Hoạt động Đi chơi Có Hộ tống của Resonator "Denia" Bị Giam Giữ Special
+          <t>Quy trình Vận hành và Danh sách Liên lạc Được Phê duyệt cho Hoạt động Đi chơi Có Hộ tống của Resonator "Denia" Bị Giam Giữ Đặc Biệt
 Mức độ bảo mật: Tối mật
 I. Căn cứ Phê duyệt
 Theo Quy định Bảo vệ và An toàn Vật chất Hư không Lahai-Roi, và sau khi được xem xét chung bởi Bộ phận Vật chất Hư không cùng Hiệu trưởng Học viện Lucilla, giấy phép tiến hành các hoạt động có giám sát trong khu vực hạn chế cho Resonator "Denia" bị giam giữ đặc biệt đã được phê duyệt.
@@ -3523,19 +3523,19 @@
 Trưởng dự án: Tiến sĩ Arman
 Trưởng nhóm tại hiện trường: {PlayerName}
 Cấu hình An ninh: {PlayerName} sẽ đồng hành cùng đối tượng trong suốt quá trình. Lực lượng Đặc nhiệm Ứng phó Khẩn cấp sẽ ở chế độ chờ.
-Resonator "Denia" bị giam giữ sẽ phải đeo thiết bị ức chế Resonance, được kết nối với hệ thống I.R.I.S. Quyền kích hoạt thiết bị được ủy quyền cho {PlayerName}. Trưởng nhóm tại hiện trường có thể ra lệnh kích hoạt hệ thống I.R.I.S. bất cứ lúc nào.
+Resonator "Denia" bị giam giữ sẽ phải đeo thiết bị ức chế Cộng Hưởng, được kết nối với hệ thống I.R.I.S. Quyền kích hoạt thiết bị được ủy quyền cho {PlayerName}. Trưởng nhóm tại hiện trường có thể ra lệnh kích hoạt hệ thống I.R.I.S. bất cứ lúc nào.
 Giai đoạn Một: Khởi hành
-Đối tượng "Denia" sẽ được bàn giao cho trưởng nhóm tại hiện trường tại ga Startorch Academy.
+Đối tượng "Denia" sẽ được bàn giao cho trưởng nhóm tại hiện trường tại ga Học viện Startorch.
 Giai đoạn Hai: Thang máy Trung tâm
-Đối tượng sẽ di chuyển bằng Thang máy Trung tâm đến Tầng 1 của Startorch Academy. Các cuộc gặp với những người liên lạc đã khai báo được phép diễn ra trong khu vực này.
-Giai đoạn Ba: Hoạt động tại Khu vườn Giải trí
-Hoạt động trong Khu vườn Giải trí được phép. Trưởng nhóm tại hiện trường sẽ điều chỉnh và hạn chế tiếp xúc của đối tượng với những người liên lạc phụ.
+Đối tượng sẽ di chuyển bằng Thang máy Trung tâm đến Tầng 1 của Học viện Startorch. Các cuộc gặp với những người liên lạc đã khai báo được phép diễn ra trong khu vực này.
+Giai đoạn Ba: Hoạt động tại Khu Vườn Giải trí
+Hoạt động trong Khu Vườn Giải trí được phép. Trưởng nhóm tại hiện trường sẽ điều chỉnh và hạn chế tiếp xúc của đối tượng với những người liên lạc phụ.
 Giai đoạn Bốn: Tiếp cận Khu Dân cư
 Được phép thăm quan khu liên lạc và thương mại. Chỉ được xem qua cửa sổ; không được mua sắm. Việc tiếp xúc với những người liên lạc phụ vẫn do trưởng nhóm tại hiện trường quyết định.
 Giai đoạn Năm: Tiếp cận Kho Lưu trữ
 Được phép vào Kho Lưu trữ để xem tài liệu hoặc gặp gỡ những người liên lạc đã khai báo. Việc phân bổ nhân sự và kiểm soát truy cập khu vực này đã được sắp xếp trước.
 Giai đoạn Sáu: Trở về
-Đối tượng sẽ được {PlayerName} hộ tống trở lại ga Startorch Academy và vận chuyển bằng tàu chỉ định đến Tập thể Spacetrek để giam giữ lại.
+Đối tượng sẽ được {PlayerName} hộ tống trở lại ga Học viện Startorch và vận chuyển bằng tàu chỉ định đến Tập thể Spacetrek để giam giữ lại.
 Lưu ý bổ sung:
 Thời gian tiếp xúc với những người liên lạc phụ phải được giới hạn nghiêm ngặt. Đối tượng bị cấm tuyệt đối không được ăn uống ngoài kế hoạch trong suốt quá trình.
 III. Biện pháp An ninh Dự phòng
@@ -3546,8 +3546,8 @@
 Quản lý Tiếp xúc Bất ngờ:
 Lực lượng Đặc nhiệm Ứng phó sẽ thực thi hạn chế truy cập. Trong trường hợp có tiếp cận ngoài kế hoạch, trưởng nhóm tại hiện trường, {PlayerName}, sẽ đưa ra phán quyết ban đầu, với Lực lượng Đặc nhiệm Ứng phó ở chế độ chờ.
 Giao thức Khẩn cấp:
-Trưởng nhóm tại hiện trường có thể ra lệnh kích hoạt qua Terminal hoặc giọng nói để kích hoạt thiết bị ức chế trên hệ thống I.R.I.S. Sau khi kích hoạt, Lực lượng Đặc nhiệm Ứng phó sẽ thực hiện thu hồi đối tượng.
-Ngoài ra, trưởng nhóm tại hiện trường được phép hành động theo quyết định của {Male=anh;Female=cô} trong các tình huống khẩn cấp.
+Trưởng nhóm tại hiện trường có thể ra lệnh kích hoạt qua Thiết bị đầu cuối hoặc giọng nói để kích hoạt thiết bị ức chế trên hệ thống I.R.I.S. Sau khi kích hoạt, Lực lượng Đặc nhiệm Ứng phó sẽ thực hiện thu hồi đối tượng.
+Ngoài ra, trưởng nhóm tại hiện trường được phép hành động theo quyết định của {Male=his;Female=her} trong các tình huống khẩn cấp.
 IV. Phụ lục: Danh sách Liên lạc Được Phê duyệt
 Liên lạc Cốt lõi:
 {PlayerName} (Trưởng nhóm tại hiện trường)
@@ -3557,10 +3557,10 @@
 Nastasha (Người liên lạc đã khai báo)
 Liên lạc Phụ:
 Isaiah (Ga Học viện)
-Banlu (Hoạt động Bộ phận được phê duyệt tại khu vực Square Học viện)
-Elska (Hoạt động Bộ phận được phê duyệt tại khu vực Square Học viện)
-Munson (Hoạt động Bộ phận được phê duyệt tại khu vực Square Học viện)
-Cosmo (Square Học viện)
+Banlu (Hoạt động Bộ phận được phê duyệt tại khu vực Quảng trường Học viện)
+Elska (Hoạt động Bộ phận được phê duyệt tại khu vực Quảng trường Học viện)
+Munson (Hoạt động Bộ phận được phê duyệt tại khu vực Quảng trường Học viện)
+Cosmo (Quảng trường Học viện)
 ...</t>
         </is>
       </c>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nổi Tiếng Nhất: Câu lạc bộ Fan Peaks of Prestige
-Ngài Furius xứ Septimont, người sáng tạo duy nhất của Peaks of Prestige, trân trọng mời ngài trải nghiệm trò chơi chiến thuật Echo đỉnh cao do ông dày công chế tác!
-Tham gia những trận đấu kịch tính, sử dụng chiến thuật liều lĩnh "được ăn cả ngã về không" để đánh bại kẻ thù hùng mạnh, và được tôn vinh như một đấu sĩ chân chính!
-Độc Đáo Nhất: Argus Workshop
-Nơi công nghệ hiện đại giao thoa với truyền thống cổ xưa, thiên đường dành cho những người đam mê vũ khí và trang bị!
-Muốn tự tay rèn nên một vũ khí huyền thoại? Tò mò về nghề chế tác vũ khí Resonator? Hãy đến Argus Workshop, nơi mọi thứ ngài cần đều có sẵn!
-Lưu ý: Câu lạc bộ này họp tại Xưởng Chế Tác của Học viện. Để biết thêm chi tiết, vui lòng liên hệ trưởng câu lạc bộ, Garris.
-Kỳ Lạ Nhất... à, Thực Dụng Nhất: Câu lạc bộ Fan Gastro-Alchemist.</t>
+          <t>Nổi Tiếng Nhất: Peaks of Prestige Fan Club
+Mr. Furius of Septimont, creator of the one and only Peaks of Prestige, invites you to experience his masterfully crafted Echo battle strategy game!
+Fight thrilling duels, use bold all-or-nothing tactics to defeat powerful foes, and be honored as a true duelist!
+Most Quirky: Argus Workshop
+Where modern technology and ancient tradition meet, a paradise for arms and armament enthusiasts!
+Want to craft a legendary weapon by your own hand? Curious about Resonator weapon-making craftsmanship? Come to the Argus Workshop, where everything you need can be found!
+Note: This fan club meets in the Academy's Crafting Bay. For more details, please contact the club leader, Garris.
+Weirdest... er, Most Practical: Gastro-Alchemist Fan Club.</t>
         </is>
       </c>
     </row>
@@ -3711,9 +3711,9 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>Báo cáo về một chuyến Spacetrek Convey, kèm theo danh sách hàng hóa chi tiết, lộ trình di chuyển, cùng thời gian và địa điểm khởi hành, đến nơi.
-Các ghi chú màu đỏ trên báo cáo đánh dấu Đèo Orbit Valley - Phía Bắc và Spacetrek–Bjartr Bridge. Một số đoạn lộ trình được khoanh tròn, với mũi tên chỉ vào.
+Các ghi chú màu đỏ trên báo cáo đánh dấu Đèo Orbit Valley - Phía Bắc và Cầu Spacetrek–Bjartr. Một số đoạn lộ trình được khoanh tròn, với mũi tên chỉ vào.
 “Ta không phản đối. Còn Yvan?”
-“Get to work.”
+“Bắt tay vào việc đi.”
 Hai dòng ghi chú viết tay ngắn gọn xuất hiện ở cuối trang.
 Phía trên báo cáo có chữ ký: Macknay.</t>
         </is>
@@ -3794,9 +3794,9 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>Đã bốn mươi tám tiếng rồi. Tôi không nghĩ họ sẽ tìm ra chúng ta đâu.
-Cậu đã làm rất tốt, người bạn già. Đây là nơi hành trình của cậu kết thúc. Tôi không ngờ lại là một Sabercat Reaver. None công cụ thích hợp, tôi không thể sửa chữa cậu được.
-Có vẻ như tôi sinh ra đã vô dụng và sẽ chết đi cũng thế. Ban đầu, tôi hy vọng cậu sẽ ghi lại tác động của Void Storm lên cơ thể con người và môi trường xung quanh khi tôi bước vào đó, rồi chuyển dữ liệu cho Spacetrek Collective. Một tia hy vọng cuối cùng của kẻ hèn nhát.
-Viện Hàn lâm sẽ sớm tìm thấy bức thư trong phòng tôi thôi. Đúng vậy, đây là một chuyến đi để chết. Tôi định để Void Storm lấy đi mạng sống của mình.
+Cậu đã làm rất tốt, người bạn già. Đây là nơi hành trình của cậu kết thúc. Tôi không ngờ lại là một Sabercat Reaver. Không có công cụ thích hợp, tôi không thể sửa chữa cậu được.
+Có vẻ như tôi sinh ra đã vô dụng và sẽ chết đi cũng thế. Ban đầu, tôi hy vọng cậu sẽ ghi lại tác động của Bão Hư Không lên cơ thể con người và môi trường xung quanh khi tôi bước vào đó, rồi chuyển dữ liệu cho Spacetrek Collective. Một tia hy vọng cuối cùng của kẻ hèn nhát.
+Viện Hàn lâm sẽ sớm tìm thấy bức thư trong phòng tôi thôi. Đúng vậy, đây là một chuyến đi để chết. Tôi định để Bão Hư Không lấy đi mạng sống của mình.
 Có lẽ ai đó sẽ tìm thấy cuốn nhật ký này rất lâu sau khi tôi đã ra đi. Hãy để nó là lời từ biệt của tôi gửi đến cậu, người lạ ơi.
 Xin hãy tha thứ cho tôi vì đã ra đi mà không có lời tạm biệt đàng hoàng. Xin hãy hiểu cho, đây không phải là một quyết định bốc đồng, mà là sự thỏa hiệp cuối cùng sau một cuộc đấu tranh dài và đau đớn.
 Là một nhà nghiên cứu từng coi khoa học như tín ngưỡng, tôi tin rằng theo đuổi tri thức là sứ mệnh cao quý nhất của nền văn minh. Lĩnh vực của tôi từng cho tôi thấy vẻ đẹp sâu sắc của vũ trụ. Những phương trình tao nhã trên bảng đen dường như dẫn lối tôi mở ra cánh cửa tiến bộ.
@@ -3804,9 +3804,9 @@
 Rồi một đồng nghiệp liên lạc với tôi. Hắn nói có thể giúp tôi vượt qua những nút thắt kỹ thuật, nhưng mọi thứ phải được thực hiện trong bí mật. Sau này tôi mới phát hiện hắn là gián điệp Fractsidus. Ngày hắn bị bắt, hắn không hề tiết lộ sự hợp tác của chúng tôi. Hắn chỉ để lại cho tôi một nụ cười. Hắn cười cái gì? Rằng tôi là người tiếp theo? Hay rằng tôi không còn là con người như trước nữa? Trong công việc chung, tôi đã vượt qua những ranh giới vi phạm đạo đức khoa học.
 Sự thuần khiết của tri thức trong mắt tôi từ lâu đã bị ô uế. Mỗi lần nghe lời khen ngợi của đồng nghiệp trong các hội nghị học thuật, tôi cảm thấy dạ dày mình quặn thắt. Sự ngưỡng mộ của họ chính là bằng chứng cho sự phản bội khoa học của tôi.
 Giờ đây, cái chết là tất cả những gì còn lại cho tôi. Nhưng dù linh hồn đã vấy bẩn, tôi vẫn muốn để lại một điều nhỏ bé có giá trị trước khi ra đi.
-Void Storm. Không ai tình nguyện bước vào đó. Tôi tưởng tượng nếu có ai đó dám vào... Chắc chắn sẽ thu thập được dữ liệu vô giá.
+Bão Hư Không. Không ai tình nguyện bước vào đó. Tôi tưởng tượng nếu có ai đó dám vào... Chắc chắn sẽ thu thập được dữ liệu vô giá.
 Tôi không tìm kiếm sự tha thứ, cũng không mong được thấu hiểu. Tôi chỉ hy vọng sự ra đi của mình sẽ trở thành một dấu hỏi, vương vấn trong tâm trí những người vẫn còn tin vào sự thuần khiết của tri thức...
-Cái chết chỉ cho ta một cơ hội. Tôi không thể lãng phí nó. Trước tiên, tôi phải quan sát Void Storm. Có lẽ tôi sẽ ở lại với bộ tộc Roya cho đến khi sẵn sàng.</t>
+Cái chết chỉ cho ta một cơ hội. Tôi không thể lãng phí nó. Trước tiên, tôi phải quan sát Bão Hư Không. Có lẽ tôi sẽ ở lại với bộ tộc Roya cho đến khi sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>Thời gian với ta giờ chẳng còn ý nghĩa gì nữa. Nó chỉ còn là một chiếc đồng hồ đếm ngược.
-Ta chưa từng đối mặt với Void Storm, nhưng ta đã học được nhiều từ kho lưu trữ của Roya. Những ghi chép của họ kể về những người sống sót. Điều gì giúp họ vượt qua được cơn bão ấy? Lằn ranh nào quyết định thứ gì bị xóa sổ, thứ gì được giữ lại?
+Ta chưa từng đối mặt với Bão Hư Không, nhưng ta đã học được nhiều từ kho lưu trữ của Roya. Những ghi chép của họ kể về những người sống sót. Điều gì giúp họ vượt qua được cơn bão ấy? Lằn ranh nào quyết định thứ gì bị xóa sổ, thứ gì được giữ lại?
 Ugh... cơn sốt này vẫn chưa lui. Hôm nay ta nên gác những suy nghĩ nặng nề sang một bên.
 Sao mỗi khi ta thư giãn, lại nhớ đến những người bộ tộc Roya khi ta mới đặt chân đến đây?
 Ta đã thấy họ sống chung với Bầy Ký Sinh, lao động bằng những công cụ thô sơ. Ta thấy họ ngước nhìn bầu trời đêm và những hiện tượng kỳ lạ bằng chính đôi mắt mình, kiên nhẫn tính toán, từng bước một, tìm ra quy luật.
@@ -3895,7 +3895,7 @@
 Ta từng khinh thường cuộc đấu tranh "thiếu hiệu quả" ấy, xem đó là dấu hiệu của một xã hội không tiến bộ. Nhưng giờ đây, điều trỗi dậy trong lòng ta là... sự kính trọng.
 Cảm giác mâu thuẫn ấy như móng vuốt xé nát từ bên trong. "Khoa học thuần túy" mà ta theo đuổi cả đời, nếu cuối cùng dẫn ta đến phản bội và hư vô, thì đâu là sự thuần khiết của nó? Những người bộ tộc này, ban đầu chẳng biết gì về "khoa học", lại chứng minh một sự thuần khiết cơ bản hơn qua chính sự tồn tại của họ—ý chí đấu tranh và sống sót, dù bị vùi dập bao nhiêu lần.
 Giờ đây, ta—vị giáo sư cao ngạo—đã bị kéo xuống khỏi bệ ngồi. Ta bị đẩy đến bờ tự sát bởi "sự không thuần khiết" trong lý tưởng của mình, trong khi họ, với đôi bàn tay lấm bùn, vẫn chiến đấu để sống. Trong cuộc đấu tranh ấy, họ thể hiện sự thuần khiết đích thực của cuộc sống.
-Mưa ngoài kia càng lúc càng lớn, nghe như bài ca của họ… Ta sẽ rời đi khi cơn sốt lui. Ta cần đến gần Void Storm hơn, để hiểu rõ hơn về nó. Người bạn droid cũ của ta có thể đã hỏng, nhưng ta vẫn còn cách để ghi lại tất cả. Nếu ta nhớ không lầm, phía trước nên có một trại của những kẻ Bị Ruồng Bỏ.</t>
+Mưa ngoài kia càng lúc càng lớn, nghe như bài ca của họ… Ta sẽ rời đi khi cơn sốt lui. Ta cần đến gần Bão Hư Không hơn, để hiểu rõ hơn về nó. Người bạn droid cũ của ta có thể đã hỏng, nhưng ta vẫn còn cách để ghi lại tất cả. Nếu ta nhớ không lầm, phía trước nên có một trại của những kẻ Bị Ruồng Bỏ.</t>
         </is>
       </c>
     </row>
@@ -3977,9 +3977,9 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Đây có lẽ là bản ghi cuối cùng của ta. Ta vẫn chưa giới thiệu bản thân một cách chính thức. Ta là Sestan, giáo sư của Startorch Academy.
+          <t>Đây có lẽ là bản ghi cuối cùng của ta. Ta vẫn chưa giới thiệu bản thân một cách chính thức. Ta là Sestan, giáo sư của Học viện Startorch.
 Ta không biết điều gì đang chờ đợi mình...
-Ta đứng trên một vị trí cao, ghi lại dữ liệu về Void Storm. Trong lúc điều chỉnh thiết bị, ta thấy một con tuần lộc cơ khí, vô tình trôi quá gần rìa của vùng méo mó. Chầm chậm. Quá chậm. Ta biết một sức mạnh vô hình sẽ dập tắt sinh mạng mỏng manh ấy trong nháy mắt.
+Ta đứng trên một vị trí cao, ghi lại dữ liệu về Bão Hư Không. Trong lúc điều chỉnh thiết bị, ta thấy một con tuần lộc cơ khí, vô tình trôi quá gần rìa của vùng méo mó. Chầm chậm. Quá chậm. Ta biết một sức mạnh vô hình sẽ dập tắt sinh mạng mỏng manh ấy trong nháy mắt.
 Trong khoảnh khắc đó, tâm trí ta trống rỗng.
 Ta không cân nhắc giá trị của sinh mạng, không tính toán khả năng thành công, không hồi tưởng lại một đời đầy tội lỗi và hoang mang. Cơ thể ta đã hành động trước khi lý trí kịp can thiệp.
 Ta lao tới và đẩy con tuần lộc ra. Và chính ta bị kéo vào.
@@ -3991,9 +3991,9 @@
 ………………
 Hai mươi ba phút đã trôi qua...
 …………
-Hmm... Cái chết, liệu nó luôn tĩnh lặng như thế này? Ta từng nghĩ học trò của mình quá ồn ào. Nhưng giờ đây, haha, ta lại thấy nhớ tiếng ồn...
+Hừm... Cái chết, liệu nó luôn tĩnh lặng như thế này? Ta từng nghĩ học trò của mình quá ồn ào. Nhưng giờ đây, haha, ta lại thấy nhớ tiếng ồn...
 Âm thanh bên ngoài... đang tắt dần...
-Hmm... sau khi âm thanh biến mất, liệu ánh sáng có tiếp bước...?
+Hừm... sau khi âm thanh biến mất, liệu ánh sáng có tiếp bước...?
 Cuối cùng... ta đã về nhà...</t>
         </is>
       </c>
@@ -4077,7 +4077,7 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>Evans
-Nghề nghiệp: Viện Nghiên Cứu Spacetrek Collective - Trợ lý Nghiên cứu
+Nghề nghiệp: Viện Nghiên cứu Spacetrek Collective - Trợ lý Nghiên cứu
 Bí danh: Bóng Xám
 Vai trò: Truyền tải thông tin lịch trình nội bộ và phân công nhân sự
 Giao dịch gần nhất: ██████. Số tiền không rõ.
@@ -4167,14 +4167,14 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>&lt;b&gt;[KHẨN CẤP! MẤT THẺ HỌC SINH!!!]&lt;/b&gt;
-Hôm qua khoảng 4h30 chiều, tớ làm mất thẻ học sinh trên tàu. Nó có vỏ silicone mềm màu xanh dương, góc trên bên trái bị mẻ. Đây là lần thứ tư tớ mất thẻ trong năm nay rồi. Nghĩ đến cảnh giáo sư của tớ gào thét, ngã quỵ, rồi túm tóc mình mà giật lia lịa khi giúp tớ làm lại lần trước… Thật lòng, tớ không dám nhờ cô ấy nữa. Nếu ai tìm thấy, xin hãy liên lạc với tớ hoặc gửi lại phòng Lost and Found ở ga. CẢM ƠN RẤT NHIỀU!!!
+Hôm qua khoảng 4h30 chiều, tớ làm mất thẻ học sinh trên tàu. Nó có vỏ silicone mềm màu xanh dương, góc trên bên trái bị mẻ. Đây là lần thứ tư tớ mất thẻ trong năm nay rồi. Nghĩ đến cảnh giáo sư của tớ gào thét, ngã quỵ, rồi túm tóc mình mà giật lia lịa khi giúp tớ làm lại lần trước… Thật lòng, tớ không dám nhờ cô ấy nữa. Nếu ai tìm thấy, xin hãy liên lạc với tớ hoặc gửi lại phòng Đồ Thất Lạc ở ga. CẢM ƠN RẤT NHIỀU!!!
 [Người gửi: "ChangeTheWorldWithLightEnergySciences"]
 …Lại làm mất thẻ à? Còn cái đoạn "gào thét, ngã quỵ, giật tóc" là sao? Nghe ghê quá, từ khi nào cô lại làm thế?
 Đừng tìm nữa. Em còn có dự án phải làm. Cô đã yêu cầu cấp thẻ mới rồi. &lt;b&gt;Đây là lần cuối&lt;/b&gt;. Đến lấy đi.
 [Người gửi: LostStudentID]
 G-Giáo sư ơi?! Hay… để em đợi thêm vài ngày nữa? Biết đâu có người nhặt được… không cần phải phiền cô ạ…
 [Người gửi: "ChangeTheWorldWithLightEnergySciences"]
-Think again. Đến văn phòng cô. Ngay lập tức.</t>
+Nghĩ lại đi. Đến văn phòng cô. Ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -4259,9 +4259,9 @@
 [Người gửi: DoNotEatIt]
 …Không độc đâu. Tôi mất hơn một tháng để điều chế thứ đó, thêm hỗn hợp dinh dưỡng tùy chỉnh, và trong các thử nghiệm trên động vật trước đây, nó giúp kiểm soát cân nặng và tạm thời tăng cường thể chất. Nhưng hiệu suất tổng hợp cực thấp. Đó là ly duy nhất… và tôi định tự thử.
 [Người gửi: "FoodAndResearchAreMyLife"]
-À… I see. Xin lỗi, tôi đói quá sau một đêm thức trắng.
+À… Ra vậy. Xin lỗi, tôi đói quá sau một đêm thức trắng.
 [Người gửi: DoNotEatIt]
-Vậy chúc mừng, giờ cậu là đối tượng thử nghiệm rồi. Send dữ liệu cân nặng và lực nắm tay cho tôi mỗi 72 giờ.
+Vậy chúc mừng, giờ cậu là đối tượng thử nghiệm rồi. Gửi dữ liệu cân nặng và lực nắm tay cho tôi mỗi 72 giờ.
 [Người gửi: "FoodAndResearchAreMyLife"]
 Nhận lệnh.</t>
         </is>
@@ -4338,7 +4338,7 @@
           <t>&lt;b&gt;[MẤT BỘ NHỚ DỮ LIỆU!]&lt;/b&gt;
 Mất một bộ nhớ dữ liệu rồi! Hình như là ba ngày trước…? Tôi quên mất thời gian chính xác. Dù sao thì đó là một bộ nhớ bạc nhỏ chứa luận án của tôi. Ai tìm thấy vui lòng liên hệ nhé! Tôi sẽ tặng mười lon Đồ Hộp Bất Ngờ làm phần thưởng!
 [Từ "LahaiRoiTrekkingFanClub"]
-…Tôi có tìm thấy một thứ giống như mô tả của cậu khi đi bộ gần Đồng Bằng Khắc Họa. Nhưng đây là mục Tìm Lost and Found của ga… Cậu chắc là không làm mất trên tàu chứ?
+…Tôi có tìm thấy một thứ giống như mô tả của cậu khi đi bộ gần Đồng Bằng Khắc Họa. Nhưng đây là mục Tìm Đồ Thất Lạc của ga… Cậu chắc là không làm mất trên tàu chứ?
 [Từ LostMyDataMemory]
 À… Đồng Bằng Khắc Họa à? Thực ra tôi có đi khảo sát ở đó vài ngày trước. Có thể đã đánh rơi khi ở ngoài ấy.
 [Từ "LahaiRoiTrekkingFanClub"]
@@ -4507,7 +4507,7 @@
 A. Trình độ và Quy trình
 1. Cấm tiến hành công việc không được phép. Tất cả nhân viên phải tuân thủ hệ thống giấy phép làm việc.
 2. Không được vi phạm, vượt qua hoặc phá hoại quy trình khóa/mở an toàn.
-B. Thông tin và Report
+B. Thông tin và Báo cáo
 3. Không được che giấu, trì hoãn hoặc làm giả báo cáo về bất kỳ sự cố an toàn, bất thường hoặc sai lệch nào.
 C. Sức khỏe và Bảo hộ Cá nhân
 4. Không được vào khu vực nguy hiểm mà không có trang bị bảo hộ cá nhân phù hợp và hiệu quả.
@@ -4780,30 +4780,30 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Dự án: Mặt Trời Nhân Tạo - Helios [Giám sát tình trạng]&lt;/b&gt;
+          <t>&lt;b&gt;Dự án: Artificial Sun - Helios [Status Monitoring]&lt;/b&gt;
 Overview:
-&lt;b&gt;[Giai đoạn 1: Khởi động &amp; Ổn định sơ bộ 7-102-234]&lt;/b&gt;
-&lt;b&gt;Trưởng nhóm:&lt;/b&gt; Mornye
-&lt;b&gt;Độ ổn định lõi:&lt;/b&gt; 98,7%
-&lt;b&gt;Tình trạng hệ thống năng lượng:&lt;/b&gt; Thường
-&lt;b&gt;Mô-đun Voidmatter:&lt;/b&gt; Thường
-&lt;b&gt;[Giai đoạn 2: Phóng mô phỏng &amp; Test áp lực 8-045-234]&lt;/b&gt;
-&lt;b&gt;Trưởng nhóm:&lt;/b&gt; Warren
-&lt;b&gt;Độ ổn định lõi:&lt;/b&gt; 93,4%
-&lt;b&gt;Tình trạng hệ thống năng lượng:&lt;/b&gt; Thường
-&lt;b&gt;Mô-đun Voidmatter:&lt;/b&gt; Thường
-&lt;b&gt;Test rung động:&lt;/b&gt; Đạt. Cấu trúc ổn định, mọi chỉ số hoạt động bình thường.
-&lt;b&gt;Test Voidmatter môi trường:&lt;/b&gt; Đạt. Mô-đun hoạt động bình thường.
-&lt;b&gt;Test tương thích tần số:&lt;/b&gt; Phát hiện sóng dị thường không khớp với dự đoán.
-Ghi chú của Nhà nghiên cứu [Warren]: Core xuất hiện cộng hưởng cực yếu tại một số dải tần số cụ thể, không quan sát được trong mô phỏng. Cần theo dõi, nhưng hiện tại không có rủi ro.
-Ghi chú của Nhà nghiên cứu [Mornye]: Lên lịch test xác minh thứ cấp.
-&lt;b&gt;[Giai đoạn 3: Hiệu chỉnh cuối cùng 8-120-234 (Current)]&lt;/b&gt;
-&lt;b&gt;Trưởng nhóm:&lt;/b&gt; Mornye
-&lt;b&gt;Độ ổn định lõi:&lt;/b&gt; 99,4%
-&lt;b&gt;Tình trạng hệ thống năng lượng:&lt;/b&gt; Thường
-&lt;b&gt;Mô-đun Voidmatter:&lt;/b&gt; Thường
-&lt;b&gt;Test cuối cùng:&lt;/b&gt; In progress
-Ghi chú của Nhà nghiên cứu [Anslem]: Máy dò Hyvatia hiện đã vào vị trí và hoạt động.</t>
+&lt;b&gt;[Phase 1: Initiation &amp; Preliminary Stabilization 7-102-234]&lt;/b&gt;
+&lt;b&gt;Lead:&lt;/b&gt; Mornye
+&lt;b&gt;Core Stability:&lt;/b&gt; 98.7%
+&lt;b&gt;Energy System Status:&lt;/b&gt; Normal
+&lt;b&gt;Voidmatter Modules:&lt;/b&gt; Normal
+&lt;b&gt;[Phase 2: Simulated Launch &amp; Pressure Testing 8-045-234]&lt;/b&gt;
+&lt;b&gt;Lead:&lt;/b&gt; Warren
+&lt;b&gt;Core Stability:&lt;/b&gt; 93.4%
+&lt;b&gt;Energy System Status:&lt;/b&gt; Normal
+&lt;b&gt;Voidmatter Modules:&lt;/b&gt; Normal
+&lt;b&gt;Vibration Test:&lt;/b&gt; Pass. Structure stable, all performance metrics nominal.
+&lt;b&gt;Environmental Voidmatter Test:&lt;/b&gt; Pass. Modules functioning normally.
+&lt;b&gt;Frequency Compatibility Test:&lt;/b&gt; Detected anomalous waveforms inconsistent with predictions.
+Researcher [Warren] notes: Core exhibits extremely weak resonance at specific frequency bands, not observed in simulations. Requires monitoring, but currently no risk.
+Researcher [Mornye] notes: Schedule secondary verification test.
+&lt;b&gt;[Phase 3: Final Calibration 8-120-234 (Current)]&lt;/b&gt;
+&lt;b&gt;Lead:&lt;/b&gt; Mornye
+&lt;b&gt;Core Stability:&lt;/b&gt; 99.4%
+&lt;b&gt;Energy System Status:&lt;/b&gt; Normal
+&lt;b&gt;Voidmatter Modules:&lt;/b&gt; Normal
+&lt;b&gt;Final Testing:&lt;/b&gt; In progress
+Researcher [Anslem] notes: The Hyvatia Detector is now in position and operational.</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Kho Archive Bộ Nhớ Cassette Rabelle - Hồ sơ lưu trữ&lt;/b&gt;
+          <t>&lt;b&gt;Kho Lưu Trữ Bộ Nhớ Cassette Rabelle - Hồ sơ lưu trữ&lt;/b&gt;
 Đội thám hiểm Frostlands PEAK-3517
 Lô lưu trữ số: ARC-5617-07A
 Bộ phận / Phòng ban: Bộ phận Voidmatter
@@ -4890,7 +4890,7 @@
 Bộ phận / Phòng ban: Bộ phận Voidmatter
 Tình trạng: Lưu trữ xác nhận
 Lô lưu trữ số: ARC-5619-09C
-Bộ phận / Phòng ban: Viện Nghiên Cứu Spacetrek - Bộ phận Phát triển Chiến thuật
+Bộ phận / Phòng ban: Viện Nghiên cứu Spacetrek - Bộ phận Phát triển Chiến thuật
 Tình trạng: Mất dữ liệu nghiêm trọng
 ...
 Ghi chú của Nhân viên lưu trữ:
@@ -4969,15 +4969,7 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>&lt;b&gt;Tóm tắt&lt;/b&gt;
-Nghiên cứu của Spacetrek Collective xác nhận Reactor Drive là bộ phận cốt lõi của Exostrider. Tuy nhiên, hệ thống phòng thủ cực kỳ kiên cố và tính không thể tiếp cận của nó khiến việc thu thập theo phương pháp thông thường trở nên bất khả thi. Bài báo này đề xuất một sáng kiến chiến lược đột phá: Dự án Giải phóng Định hướng Năng lượng Hư không (Void Energy Directed Release Project).
-Cơ chế cốt lõi dựa trên mối liên kết phòng thủ cộng sinh giữa Reactor và điểm neo chính của nó—các Solistree tại Bjartr Woods. Chúng tôi chứng minh rằng việc triển khai chính xác các vật mang Voidmatter chuyên dụng vào vùng rễ của Solistree có thể làm tổn hại hiệu quả điểm neo sinh thái này. Sự ô nhiễm này sẽ kích hoạt phản ứng miễn dịch cấp cao nhất của Reactor Drive, buộc nó phải lệch khỏi quỹ đạo hiện tại và hạ cánh xuống khu vực được chỉ định dưới dạng vật lý, bước vào trạng thái có thể thu hồi.
-Bài báo trình bày chi tiết mô hình tương tác giữa Voidmatter và hệ sinh thái Solistree, ngưỡng kích hoạt cơ chế phản ứng khẩn cấp của Reactor Drive, quỹ đạo tác động dự kiến, và quy trình thu hồi nhanh chóng của Viện Nghiên Cứu Spacetrek Collective tại địa điểm được chỉ định. Chiến lược đề xuất cung cấp một con đường khả thi về mặt lý thuyết và mang tính quyết định chiến lược để thu thập Reactor Drive, một bước tiến quan trọng hướng tới việc kích hoạt cuối cùng của Exostrider.
-&lt;b&gt;Từ khóa:&lt;/b&gt; Năng lượng Hư không; Reactor; Cơ chế Phản ứng Khẩn cấp; Exostrider; Bjartr Woods; Solistree; Thu thập Chiến lược
-&lt;b&gt;Chương 1: Introduction&lt;/b&gt; 
-&lt;b&gt;Cái giá phải trả: Về sự tiến bộ của nền văn minh&lt;/b&gt;
-……
-Result đánh giá: Đề xuất Không được Phê duyệt
-Viện Nghiên Cứu Spacetrek Collective</t>
+Nghiên cứu của Tập đoàn Spacetrek xác nhận rằng Bộ phận Động cơ Phản ứng là thành phần cốt lõi của Exostrider. Tuy nhiên, hệ thống phòng thủ cực kỳ kiên cố cùng vị trí bất khả xâm phạm khiến việc chiếm đoạt theo cách thông thường là bất khả thi. Báo cáo này đề xuất một chiến lược đột phá: Dự án Giải phóng Năng lượng Hư không Định hướng.</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5045,7 @@
           <t>NỘI DUNG
 Chương 1: Chào mừng đến "Thiên Đường"! Bước xuống tàu là quỳ gối ngay lập tức!
 Chương 2: Một đêm trên Đại lộ Milton! Sẵn sàng khám phá những cảnh tượng bí ẩn trong tòa tháp văn phòng!
-Chương 3: Land Cơ Hội! Giàu sang và huyền thoại được tạo ra ở đây... có lẽ vậy?
+Chương 3: Vùng Đất Cơ Hội! Giàu sang và huyền thoại được tạo ra ở đây... có lẽ vậy?
 Chương 4: Cuồng mua tại Cung điện Mua sắm! Vào trong rồi, Shell Credit chẳng là gì cả!
 Chương 5: Nhìn lén giới thượng lưu! Một cái liếc trộm sẽ làm sụp đổ thế giới quan của ngươi!
 ...
@@ -5158,30 +5150,29 @@
 &lt;b&gt;Điều 2&lt;/b&gt;
 Học viện sẽ thiết lập và hoàn thiện hệ thống quản lý an toàn giao thông phối hợp. Các khoa và tổ chức sinh viên phải tham gia đánh giá tác động giao thông đối với các dự án xây dựng và nghiên cứu trong khuôn viên, đồng thời xây dựng kế hoạch quản lý an toàn cùng biện pháp thực hiện phù hợp.
 &lt;b&gt;Điều 3&lt;/b&gt;
-Bất kỳ cá nhân nào đăng ký quyền điều khiển phương tiện trong Học viện đều phải xuất trình giấy phép lái xe hợp lệ, nghiên cứu kỹ Quy định này và vượt qua bài test trực tuyến trong vòng ba tuần kể từ ngày đăng ký.
+Bất kỳ cá nhân nào đăng ký quyền điều khiển phương tiện trong Học viện đều phải xuất trình giấy phép lái xe hợp lệ, nghiên cứu kỹ Quy định này và vượt qua bài kiểm tra trực tuyến trong vòng ba tuần kể từ ngày đăng ký.
 &lt;b&gt;Điều 4&lt;/b&gt;
-Các hành vi sau đây bị nghiêm cấm khi điều khiển phương tiện:
-(1) Sử dụng Thiết bị đầu cuối cầm tay để gọi điện, gấp rút hoàn thành luận văn, xem bài giảng trực tuyến hoặc thực hiện bất kỳ hoạt động nào khác gây cản trở lái xe an toàn.
-(2) Để xe trôi dốc khi tắt máy hoặc ở số mo.
-(3) Tự ý vào khu vực bị ảnh hưởng bởi Void Storm.
-(4) Đỗ xe ngay trước cửa các tòa giảng đường.
-(5) Chuẩn bị hoặc ăn mì gói trên xe sidecar không có mái che.
-(6) Dùng nhiệt dư từ động cơ để hâm nóng thức ăn.
-(7) Cho ăn, khiêu khích hoặc tương tác với bầy Exoswarm hoang dã khi đang lái xe.
-&lt;b&gt;Điều 5&lt;/b&gt;
-Việc điều khiển phương tiện trong Học viện phải tuân thủ các quy tắc sau:
-(1) Tuân thủ giới hạn tốc độ 10 km/h. Người vi phạm sẽ bị tịch thu phương tiện và phải tham gia các buổi giảng về an toàn giao thông liên tục trong bảy ngày sau giờ học.
-(2) Không được điều khiển phương tiện trên đường dây cáp treo, ray trượt hoặc các tuyến đường cơ khí cố định khác.
-(3) Cấm lái xe sau 16 giờ làm việc hoặc học tập liên tục. Thời gian lái xe liên tục không được vượt quá 4 giờ vào ban ngày hoặc 2 giờ vào ban đêm.
-(4) Phải đội mũ bảo hiểm khi điều khiển xe máy thám hiểm.
-(5) Không được sử dụng Exoswarm chưa thuần hóa hoặc đang trong giai đoạn nghiên cứu để kéo, đẩy hoặc cưỡi song song với phương tiện.
-(6) Không được tháo bỏ các cấu trúc an toàn như cửa hoặc mái xe với lý do "cải thiện khí động học".
-(7) Cấm thiền định, luyện tập đồng bộ hóa hoặc bất kỳ hoạt động nào có khả năng làm suy giảm nhận thức cơ thể khi đang lái xe.
-(8) Nếu lõi năng lượng của phương tiện được biết là quá tải, người điều khiển phải báo cáo ngay lập tức và sơ tán khỏi khu vực. Chỉ dán biển "Nguy hiểm" là không đủ.
+Các hành vi sau đây bị nghiêm cấm khi điều khiển phương tiện: (1) Making calls on handheld Terminals, rushing to meet thesis deadlines, watching online courses, or engaging in any other activity that impedes safe driving.
+(2) Coasting downhill with the engine turned off or in neutral.
+(3) Entering areas affected by Void Storms without authorization.
+(4) Parking vehicles directly in front of academic halls.
+(5) Preparing or consuming cup noodles in an open sidecar.
+(6) Using residual engine heat to warm food.
+(7) Feeding, provoking, or otherwise interacting with wild Exoswarm while driving.
+&lt;b&gt;Article 5&lt;/b&gt;
+Vehicle operation within the Academy shall adhere to the following rules:
+(1) A speed limit of 10 km/h shall be observed. Violators will have their vehicles impounded and be required to attend traffic safety lectures for seven consecutive days after class.
+(2) Vehicles may not be operated on ropeways, slide rails, or other fixed mechanical paths.
+(3) Driving is prohibited after more than 16 consecutive hours of work or study. Continuous driving shall not exceed 4 hours during daytime or 2 hours at night.
+(4) Helmets must be worn when operating expedition motorbikes.
+(5) Untamed or research-stage Exoswarm may not be used for towing, pulling, or riding alongside vehicles.
+(6) Safety structures such as doors or roofs may not be removed in pursuit of "better aerodynamics."
+(7) Meditation, synchronization training, or any activity likely to impair physical awareness while driving is prohibited.
+(8) If a vehicle's energy core is known to be overloaded, operators must report it immediately and evacuate the area. Posting a "Danger" sign alone is not sufficient.
 ……
-&lt;b&gt;Các vi phạm sẽ được xử lý tùy theo mức độ nghiêm trọng và có thể dẫn đến cảnh cáo, tịch thu phương tiện tạm thời, đình chỉ quyền lái xe, thu hồi quyền tiếp cận thí nghiệm hoặc tài trợ, hoặc phân công làm "nhiệm vụ tình nguyện dọn dẹp đường phố". Các vi phạm nghiêm trọng sẽ bị xử lý kỷ luật theo quy định của Học viện.&lt;/b&gt;
-Lời nhắc từ S.I.G.M.A.:
-Hãy lưu ý rằng tất cả các vi phạm sẽ được ghi nhận là lỗi vi phạm và có thể được công khai trong Học viện. Đừng thử thách những quy định này. An toàn giao thông bắt đầu từ chính bạn.</t>
+&lt;b&gt;Violations will be handled according to their severity and may result in warnings, temporary vehicle confiscation, suspension of driving privileges, revocation of experimental access or funding, or assignment to "road-cleaning volunteer duty." Serious offenses will be subject to disciplinary action in accordance with Academy policies.&lt;/b&gt;
+Reminder from S.I.G.M.A.:
+Please be advised that all violations will be recorded as infractions and may be publicly listed within the Academy. Do not test these rules. Safe travel begins with you.</t>
         </is>
       </c>
     </row>
@@ -5508,20 +5499,20 @@
         <is>
           <t>Nhật Ký–Số 322 I
 Người ghi: Amur
-Không có Dị Quang, và nồng độ Void Storm vẫn trong ngưỡng bình thường. Tuy nhiên, một đợt bùng phát Void Storm vừa xảy ra, nuốt chửng trạm nghiên cứu của chúng tôi. Cơn bão bắt gặp hai nhân viên đang làm việc, cuốn cả hai đi. May mắn thay, họ đã kịp kích hoạt báo động khẩn cấp trong khoảnh khắc cuối cùng, giúp Tavia và tôi kịp thời sơ tán.
+Không có Dị Quang, và nồng độ Bão Hư Không vẫn trong ngưỡng bình thường. Tuy nhiên, một đợt bùng phát Bão Hư Không vừa xảy ra, nuốt chửng trạm nghiên cứu của chúng tôi. Cơn bão bắt gặp hai nhân viên đang làm việc, cuốn cả hai đi. May mắn thay, họ đã kịp kích hoạt báo động khẩn cấp trong khoảnh khắc cuối cùng, giúp Tavia và tôi kịp thời sơ tán.
 Cơn bão đã cuốn đi phương tiện của chúng tôi, và chỉ còn là vấn đề thời gian trước khi nó đuổi kịp chúng tôi.
-Haha, tôi nghe nói rất ít người sống sót sau Void Storm. Chúng tôi vừa gặp phải một đợt bùng phát Void Storm—thứ mà họ gọi là sự kiện một phần tỷ—vậy ai dám nói chúng tôi sẽ không gặp một đợt khác có thể cứu mạng mình? Kỳ nghỉ của tôi đáng lẽ bắt đầu sau hai ngày nữa... Tôi thậm chí còn định gọi cho mẹ.
-Cơn bão đang tiến gần, nhưng may mắn thay, tôi tìm thấy một chiếc xe trượt mà một nhà nghiên cứu nào đó đã tốt bụng để lại. Tôi sẽ đánh liều: nếu trượt xuống con dốc này, có lẽ chúng tôi sẽ thoát khỏi Void Storm. Tôi nghĩ cơ hội của chúng tôi khá cao—vì xác suất tìm thấy thứ như thế này ở vùng Roya Frostlands bị hạn chế ra vào là rất thấp, vậy nên có vẻ như vận may vẫn đang ở bên chúng tôi.
+Haha, tôi nghe nói rất ít người sống sót sau Bão Hư Không. Chúng tôi vừa gặp phải một đợt bùng phát Bão Hư Không—thứ mà họ gọi là sự kiện một phần tỷ—vậy ai dám nói chúng tôi sẽ không gặp một đợt khác có thể cứu mạng mình? Kỳ nghỉ của tôi đáng lẽ bắt đầu sau hai ngày nữa... Tôi thậm chí còn định gọi cho mẹ.
+Cơn bão đang tiến gần, nhưng may mắn thay, tôi tìm thấy một chiếc xe trượt mà một nhà nghiên cứu nào đó đã tốt bụng để lại. Tôi sẽ đánh liều: nếu trượt xuống con dốc này, có lẽ chúng tôi sẽ thoát khỏi Bão Hư Không. Tôi nghĩ cơ hội của chúng tôi khá cao—vì xác suất tìm thấy thứ như thế này ở vùng Roya Frostlands bị hạn chế ra vào là rất thấp, vậy nên có vẻ như vận may vẫn đang ở bên chúng tôi.
 Chúc con may mắn nhé, mẹ.
 Nhật Ký–Số 322 II
 Người ghi: Tavia
-Amur đã bị Void Storm cuốn đi. Tôi cũng sẽ sớm theo anh ấy.
-Chiếc xe trượt bị hỏng—đó là lý do nó bị bỏ lại. Chúng tôi đã mất quá nhiều thời gian kiểm tra nó và đánh mất thời gian quý báu. Nhưng dù không nhặt nó lên, Void Storm vẫn sẽ nuốt chửng chúng tôi sớm hay muộn. Thật không may khi chúng tôi đã đánh liều và thua cuộc.
-Void Storm đang mạnh dần. Tôi sợ mình không thể trụ được nữa. Dù vậy, tôi sẽ tiếp tục chạy để giảm thiểu sự nhiễm độc Vật Chất Hư Không cho FCR.
+Amur đã bị Bão Hư Không cuốn đi. Tôi cũng sẽ sớm theo anh ấy.
+Chiếc xe trượt bị hỏng—đó là lý do nó bị bỏ lại. Chúng tôi đã mất quá nhiều thời gian kiểm tra nó và đánh mất thời gian quý báu. Nhưng dù không nhặt nó lên, Bão Hư Không vẫn sẽ nuốt chửng chúng tôi sớm hay muộn. Thật không may khi chúng tôi đã đánh liều và thua cuộc.
+Bão Hư Không đang mạnh dần. Tôi sợ mình không thể trụ được nữa. Dù vậy, tôi sẽ tiếp tục chạy để giảm thiểu sự nhiễm độc Vật Chất Hư Không cho FCR.
 Hy vọng dữ liệu thu thập được sẽ hữu ích cho các nhà nghiên cứu tương lai.
 ...
 ...
-Nhiệt độ cơ thể đang hạ. Tôi không còn cảm giác ở tay chân nữa. Void Storm đang dần tan, nhưng tôi không thể đi xa hơn. Tôi sẽ đánh liều lần cuối và Dodgem FCR xuống dưới.
+Nhiệt độ cơ thể đang hạ. Tôi không còn cảm giác ở tay chân nữa. Bão Hư Không đang dần tan, nhưng tôi không thể đi xa hơn. Tôi sẽ đánh liều lần cuối và ném FCR xuống dưới.
 Nếu báo cáo này được thu hồi nguyên vẹn, thì tôi đã thắng ván cược cuối cùng của mình.
 Chúc tôi may mắn nhân danh chân lý và khoa học.</t>
         </is>
@@ -5595,7 +5586,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>3.11 Introduction về Trang bị 
+          <t>3.11 Giới thiệu về Trang bị 
 Trang phục tiêu chuẩn dành cho các nhà thám hiểm khoa học được lót lớp đệm composite cách nhiệt dày dặn. Thiết kế này giúp duy trì thân nhiệt trong thời gian dài ở môi trường cực lạnh và bảo vệ cơ thể nếu chẳng may ngã. Tuy nhiên, ngã trên băng vẫn có thể gây chấn thương cho những vùng không được bảo vệ (như đầu). Vì vậy, khi di chuyển qua địa hình băng giá, nên sử dụng đinh chống trượt.
 Ghi chú của nhà nghiên cứu: Đừng lo lắng quá, miễn là bạn biết cách ngã đúng kỹ thuật, khả năng bị thương là rất thấp. Tính năng bảo vệ của bộ đồ này không phải trò đùa, nhưng hãy nhớ bảo vệ đầu bằng tư thế đúng. À, đinh chống trượt không hiệu quả lắm trên bề mặt băng cứng, thậm chí có thể gây trầy xước hoặc thương tích nếu ngã. Không nên mang chúng mọi lúc.
 ……
@@ -5671,7 +5662,7 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>Thông Báo An Toàn Trạm Nghiên Cứu Vùng Cực:
-Dữ liệu giám sát gần đây cho thấy chỉ số Vật Chất Hư Không bất thường trong khu vực xung quanh, có thể dẫn đến lỗi liên lạc, nhiễu loạn thiết bị định vị và các cơn Void Storm quy mô nhỏ thường xuyên. Những hiện tượng trên tiềm ẩn nguy cơ đe dọa đến an toàn nhân sự và thiết bị.
+Dữ liệu giám sát gần đây cho thấy chỉ số Vật Chất Hư Không bất thường trong khu vực xung quanh, có thể dẫn đến lỗi liên lạc, nhiễu loạn thiết bị định vị và các cơn Bão Hư Không quy mô nhỏ thường xuyên. Những hiện tượng trên tiềm ẩn nguy cơ đe dọa đến an toàn nhân sự và thiết bị.
 Qua điều tra thực địa, chúng tôi xác nhận dị thường bắt nguồn từ một bộ phận vệ tinh bị ô nhiễm nặng nằm dưới lớp băng. Bộ phận này hiện đã được thu hồi và cách ly thành công.
 Chúng tôi xin gửi lời cảm ơn sâu sắc nhất tới Đội Trưởng Giáo Sư Atrod Scott của Đội 17, người đã báo cáo phát hiện này cho chúng tôi.</t>
         </is>
@@ -5741,8 +5732,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Thông Báo An Toàn Polar Nghiên cứu Outpost:
-Qua giám sát gần đây, chúng tôi phát hiện chỉ số Vật Chất Hư Không bất thường trong khu vực xung quanh. Những dị thường này có thể gây ra lỗi liên lạc, nhiễu loạn hệ thống định vị và các cơn Void Storm quy mô nhỏ thường xuyên. Những hiện tượng này tiềm ẩn nguy cơ đe dọa đến an toàn nhân sự và tính toàn vẹn thiết bị.
+          <t>Thông Báo An Toàn Trạm Nghiên Cứu Vùng Cực:
+Qua giám sát gần đây, chúng tôi phát hiện chỉ số Vật Chất Hư Không bất thường trong khu vực xung quanh. Những dị thường này có thể gây ra lỗi liên lạc, nhiễu loạn hệ thống định vị và các cơn Bão Hư Không quy mô nhỏ thường xuyên. Những hiện tượng này tiềm ẩn nguy cơ đe dọa đến an toàn nhân sự và tính toàn vẹn thiết bị.
 Qua điều tra thực địa, chúng tôi xác nhận nguồn gốc xuất phát từ một bộ phận vệ tinh bị ô nhiễm nặng nằm trong lớp băng. Bộ phận này hiện đã được thu hồi và cách ly thành công.
 Để đảm bảo an toàn cho tất cả nhân viên và thành công của nhiệm vụ thám hiểm, các thành viên được khuyến cáo tránh xa khu vực này trừ khi việc tiếp cận là cần thiết cho nhiệm vụ.</t>
         </is>
@@ -5815,13 +5806,13 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Tiến Độ Build
+          <t>Tiến Độ Xây Dựng
 42/100
-Tiến Độ Build
+Tiến Độ Xây Dựng
 43/100
 ...
-Hmph Lại mấy kẻ Vô Lại cứ rên rỉ rằng băng quá mỏng, rằng nó sẽ chẳng bao giờ chịu nổi ánh mặt trời. Đồ ngu! Các ngươi chỉ xứng làm việc với gỗ và da thú! Nhìn tảng băng tuyệt vời này đi! Trong tay ta, nó trở nên cứng cáp và trong veo, giam giữ từng tia sáng. Đây mới là uy quyền ta đòi hỏi: tinh khiết đến mức tàn nhẫn, băng trong đến nỗi mỗi kẻ quỳ dưới chân nó đều phải nhìn thấy bóng dáng nỗi kinh hoàng của chính mình!
-High hơn! Xây cao hơn nữa! High đến mức ta sẽ trị vì trong im lặng, khi ngay cả bóng tối cũng phải run rẩy dưới ánh mắt của ta!</t>
+Hừ! Lại mấy kẻ Vô Lại cứ rên rỉ rằng băng quá mỏng, rằng nó sẽ chẳng bao giờ chịu nổi ánh mặt trời. Đồ ngu! Các ngươi chỉ xứng làm việc với gỗ và da thú! Nhìn tảng băng tuyệt vời này đi! Trong tay ta, nó trở nên cứng cáp và trong veo, giam giữ từng tia sáng. Đây mới là uy quyền ta đòi hỏi: tinh khiết đến mức tàn nhẫn, băng trong đến nỗi mỗi kẻ quỳ dưới chân nó đều phải nhìn thấy bóng dáng nỗi kinh hoàng của chính mình!
+Cao hơn! Xây cao hơn nữa! Cao đến mức ta sẽ trị vì trong im lặng, khi ngay cả bóng tối cũng phải run rẩy dưới ánh mắt của ta!</t>
         </is>
       </c>
     </row>
@@ -5894,11 +5885,11 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>Lại một ngày kín lịch. Vẫn chưa hiểu nổi môn Quy Hoạch Lưới Năng Lượng. Phải xem lại thôi.
-Tomorrow sẽ vất vả đây: Tô-pô, Nghiên cứu Động lực học và Khoa học Vật liệu. Tốt nhất là chuẩn bị từ tối nay. À, còn bài thuyết trình trước giờ Khoa học Vật liệu nữa!
+Ngày mai sẽ vất vả đây: Tô-pô, Nghiên cứu Động lực học và Khoa học Vật liệu. Tốt nhất là chuẩn bị từ tối nay. À, còn bài thuyết trình trước giờ Khoa học Vật liệu nữa!
 Rồi còn bài kiểm tra ngày kia… phải bắt đầu ôn sớm thôi.
 ...
 Sao học hành khó thế nhỉ?
-Không sao đâu, Sigrika. Bạn've got this! Ai cũng bảo cậu sẽ là một trong những người kế tục Heliodic Six. Những môn này chẳng là gì với cậu cả!
+Không sao đâu, Sigrika. Cậu làm được mà! Ai cũng bảo cậu sẽ là một trong những người kế tục Heliodic Six. Những môn này chẳng là gì với cậu cả!
 ...
 Vậy sao mình vẫn thấy KHÓ ĐẾN THẾ?!</t>
         </is>
@@ -6045,7 +6036,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Tại một thị trấn nhỏ, một cựu lính đánh thuê của New Federation đang sống yên bình thì bị một Dodget bút của tập đoàn phá tan cuộc đời. Một loạt chính sách sói dữ đã xóa sạch khoản tiết kiệm của anh chỉ sau một đêm, khiến gia đình tan nát.
+          <t>Tại một thị trấn nhỏ, một cựu lính đánh thuê của Liên Bang Mới đang sống yên bình thì bị một nét bút của tập đoàn phá tan cuộc đời. Một loạt chính sách sói dữ đã xóa sạch khoản tiết kiệm của anh chỉ sau một đêm, khiến gia đình tan nát.
 Quyết trả thù tập đoàn tham nhũng, anh trở lại thủ đô, không còn là một người lính, mà là một thiên tài tài chính đang lên. Và thế là cuộc báo thù chấn động thủ đô bắt đầu...</t>
         </is>
       </c>
@@ -6245,7 +6236,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Từng là một Thợ Săn Discord huyền thoại, hắn từ bỏ bóng tối và thề nguyện thiêng liêng, cống hiến cuộc đời để chăm sóc những Echoes được ban tặng bởi ý chí thần thánh. Rồi Echoes trốn thoát. Những gì khởi đầu như một nhiệm vụ truy tìm đơn giản lại dẫn hắn đến một cơ sở bí mật, nơi đang tiến hành những thí nghiệm TD bị cấm. Âm mưu này sâu xa hơn nhiều, và hắn phải đưa ra lựa chọn...</t>
+          <t>Từng là một Thợ Săn Discord huyền thoại, hắn từ bỏ bóng tối và thề nguyện thiêng liêng, cống hiến cuộc đời để chăm sóc những Echo được ban tặng bởi ý chí thần thánh. Rồi Echo trốn thoát. Những gì khởi đầu như một nhiệm vụ truy tìm đơn giản lại dẫn hắn đến một cơ sở bí mật, nơi đang tiến hành những thí nghiệm TD bị cấm. Âm mưu này sâu xa hơn nhiều, và hắn phải đưa ra lựa chọn...</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6506,7 @@
 Tôi có cảm giác mình đang quay lại ngõ cụt cũ. Dù đi hướng nào, tôi vẫn không thấy ánh sáng đâu cả. Dữ liệu, công thức... giờ chẳng còn ý nghĩa gì với tôi nữa. Hướng đi đúng...? Có lẽ tôi nên lần theo những bản ghi trước. Tôi nhớ đã để chúng trong một căn phòng nào đó...
 [Nhật Ký Thí Nghiệm - 359]
 Giờ tôi mới thấy. Hướng đi của mình đã sai ngay từ đầu. Có lẽ tôi không nên ở đây nữa...
-Gần đây, tôi cứ nghe thấy những giai điệu kỳ lạ quanh Academy. Và tôi cũng liên tục thấy con thỏ kì quặc đó. Nó như đang cố chỉ cho tôi một hướng nào đó? Thỏ mà... Không ngờ mình lại đặt hy vọng vào một con thỏ...</t>
+Gần đây, tôi cứ nghe thấy những giai điệu kỳ lạ quanh Học Viện. Và tôi cũng liên tục thấy con thỏ kì quặc đó. Nó như đang cố chỉ cho tôi một hướng nào đó? Thỏ mà... Không ngờ mình lại đặt hy vọng vào một con thỏ...</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6581,7 @@
 Ta cảm giác như mình đang quay lại ngõ cụt cũ. Dù đi hướng nào, ánh sáng vẫn chẳng hiện ra. Dữ liệu, công thức... giờ chẳng còn ý nghĩa gì nữa. Hướng đi đúng...? Có lẽ ta nên lần lại những bản ghi trước. Ta nhớ đã để chúng trong một căn phòng nào đó...
 [Nhật Ký Thí Nghiệm - 359]
 Giờ ta mới hiểu. Ngay từ đầu, hướng đi của ta đã sai. Có khi ta chẳng nên ở đây nữa...
-Gần đây, ta cứ nghe thấy những giai điệu kỳ lạ quanh Academy. Và ta cũng liên tục thấy con thỏ kì quặc đó. Nó như đang cố chỉ cho ta một hướng nào đó? Thỏ ấy mà... Không ngờ ta lại đặt hy vọng vào một con thỏ...
+Gần đây, ta cứ nghe thấy những giai điệu kỳ lạ quanh Học Viện. Và ta cũng liên tục thấy con thỏ kì quặc đó. Nó như đang cố chỉ cho ta một hướng nào đó? Thỏ ấy mà... Không ngờ ta lại đặt hy vọng vào một con thỏ...
 [Nhật Ký Thí Nghiệm - ???]
 Ta tìm thấy rồi. Ta tìm thấy rồi! Nó vẫn ở đó từ đầu!</t>
         </is>
@@ -6661,7 +6652,7 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>Thời tiết: Nắng
-Log: Hệ thống bình thường
+Nhật ký: Hệ thống bình thường
 Tôi không giỏi viết mấy cái này. Nhưng tháng trước, khi tôi không nộp... cô ấy có vẻ buồn.
 Chắc thế này là đủ số từ rồi. Mọi thứ đều ổn. Đừng lo, tôi sẽ đảm bảo mọi thứ vẫn ổn.</t>
         </is>
@@ -6825,10 +6816,10 @@
 Cho đến ngày tôi gặp họ. Lúc đó, tôi mới nhận ra Lahai-Roi cũng có những hiệp sĩ của riêng mình.
 Bảy lần họ cứu tôi. Bảy lần món nợ ân tình đè nặng trong lòng. Tất cả những gì tôi khao khát... chỉ là trở thành hiệp sĩ bảo vệ họ. Chỉ một lần thôi.
 ...
-Giờ đây, cơ hội đó đã đến. Các thầy giáo nói về một cơn Void Storm đang đến gần, một tai họa có thể cuốn phăng họ đi trong nháy mắt.
+Giờ đây, cơ hội đó đã đến. Các thầy giáo nói về một cơn Bão Hư Không đang đến gần, một tai họa có thể cuốn phăng họ đi trong nháy mắt.
 Tôi cố đưa họ đến nơi an toàn... nhưng chính tôi lại bị cơn bão nuốt chửng.
 Đây có phải là nơi hành trình của tôi kết thúc? Một cái kết thích đáng cho câu chuyện của tôi, có lẽ vậy.
-Nhưng then... Hogarth, Đại Chỉ huy thứ Mười Bảy, xuất hiện.
+Nhưng rồi... Hogarth, Đại Chỉ huy thứ Mười Bảy, xuất hiện.
 Dù nhỏ bé, cậu ấy đã kéo tôi vào bên trong khung xương rỗng của mình—con tàu "thùng rác" của cậu ấy—và bằng tất cả sức lực, leo lên vùng đất cao.
 "Joljotra, kỳ nghỉ hè của cậu kết thúc hôm nay với tư cách là Đại Chỉ huy thứ Mười Bảy thực thụ. Cậu sẽ bắt đầu một học kỳ mới huy hoàng cho chính mình... còn ta sẽ đảm nhận vai trò Đại Chỉ huy đi theo sau."
 Cậu ấy đã tuyên bố như thế.</t>
@@ -6941,19 +6932,19 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[Hệ thống Trên Tàu BC-1412 - Truy Xuất Nhật Ký]
-Nguồn Data: Bộ phận nghiên cứu bên ngoài (mẫu cũ)
-Status: Hư hại một phần/ghi đè theo chu kỳ
+          <t>[Hệ Thống Trên Tàu BC-1412 - Truy Xuất Nhật Ký]
+Nguồn Dữ Liệu: Bộ phận nghiên cứu bên ngoài (mẫu cũ)
+Trạng Thái: Hư hại một phần/ghi đè theo chu kỳ
 Ghi Chú: Các nhật ký sau đây ghi lại nhiệm vụ xác minh thực địa, không phải cứu hộ hay giải cứu.
 Mảnh Nhật Ký 001 - Định Nghĩa Nhiệm Vụ
 Số Nhiệm Vụ: &lt;color=Highlight&gt;ICE-Δ-013&lt;/color&gt;
 Nhân Sự Liên Quan: &lt;color=Highlight&gt;DAN-013, AMU-013, WEG-013&lt;/color&gt;
-Objective Nhiệm Vụ: Xác minh lại các dị thường theo mùa
-Đối Tượng Objective (tên gọi không chính thức): &lt;color=Highlight&gt;Trầm Tích Cobalt, Vật Chất Xanh Trơ, Lớp Pha Xanh&lt;/color&gt;
+Mục Tiêu Nhiệm Vụ: Xác minh lại các dị thường theo mùa
+Đối Tượng Mục Tiêu (tên gọi không chính thức): &lt;color=Highlight&gt;Trầm Tích Cobalt, Vật Chất Xanh Trơ, Lớp Pha Xanh&lt;/color&gt;
 Mô Tả: Đối tượng chỉ hiện hữu theo thời gian. Không thể quan sát quanh năm.
 Hạn Chế Chính: Hiện tượng chỉ xuất hiện trong giai đoạn ấm lên. &lt;color=Highlight&gt;Thời gian quan sát hiệu quả ước tính không quá 72 giờ mỗi năm&lt;/color&gt;.
 Mảnh Nhật Ký 002 - Kích Hoạt Thực Địa
-Phương Tiện BC-1412: Activated
+Phương Tiện BC-1412: Đã kích hoạt
 Thông Số Di Chuyển: Điều chỉnh thủ công
 Thời Tiết: Ổn định
 Ghi Chú: Nhiệm vụ này nhằm xác minh lại. Không phải lần đầu tiếp cận khu vực mục tiêu.
@@ -6963,7 +6954,7 @@
 Cảnh Báo Rủi Ro: Nếu bỏ lỡ lần xác minh này, cơ hội tiếp theo sẽ phải đợi &lt;color=Highlight&gt;một chu kỳ năm đầy đủ&lt;/color&gt;.
 Mảnh Nhật Ký 004 - Nhật Ký Tranh Cãi Lần 1
 Tóm Tắt Cuộc Hội Thoại (bản ghi):
-DAN-013: Conditions đang tiến gần ngưỡng. Tiếp tục trì hoãn cũng rủi ro như tiến hành.
+DAN-013: Điều kiện đang tiến gần ngưỡng. Tiếp tục trì hoãn cũng rủi ro như tiến hành.
 AMU-013: Mức độ phơi nhiễm chưa đủ. Tiến vào quá vội sẽ chỉ làm tăng số biến số không kiểm soát được.
 WEG-013: Các chỉ số từ module bên ngoài bất thường. Đề nghị tạm dừng nhiệm vụ để kiểm tra thiết bị.
 Kết Luận: Chưa đạt được đồng thuận
@@ -6972,10 +6963,10 @@
 Tóm Tắt Cuộc Hội Thoại (bản ghi):
 DAN-013: Đây là cơ hội của chúng ta. Nếu bỏ lỡ, sẽ không có lần sau.
 AMU-013: Chúng ta không có kế hoạch giải cứu dự phòng. Nếu đi bộ, chúng ta sẽ không quay về được.
-WEG-013: Mô-đun đang tự ghi dữ liệu. Nếu tiếp tục, phương tiện có thể không thể thu hồi.
+WEG-013: Module đang tự ghi dữ liệu. Nếu tiếp tục, phương tiện có thể không thể thu hồi.
 Kết Luận: Vẫn chưa đạt được đồng thuận
 Mảnh Nhật Ký 006 - Nhật Ký Hành Động
-Status Phương Tiện: Chế độ chờ. Mô-đun bên ngoài vẫn hoạt động
+Trạng Thái Phương Tiện: Chế độ chờ. Module bên ngoài vẫn hoạt động
 Kết Luận Hành Động: Cả ba nhân sự đã rời đi bằng đường bộ
 Hướng Di Chuyển Ghi Lại: &lt;color=Highlight&gt;Độ lệch về phía Bắc&lt;/color&gt;. Lý do cho hành động này chưa được ghi chép đầy đủ
 Ghi Chú: Di chuyển bằng đường bộ được đánh dấu là "rủi ro cao nhưng chính đáng"
@@ -6984,9 +6975,9 @@
 Thông Số Môi Trường Hợp Lệ Cuối Cùng: Xu hướng ấm lên vẫn tiếp diễn. Tỷ lệ phơi nhiễm trầm tích xanh vẫn tăng.
 Mảnh Nhật Ký 008 - &lt;color=Highlight&gt;Vòng Lặp Yêu Cầu (Vẫn Hoạt Động)&lt;/color&gt;
 Yêu Cầu Xác Minh: Phơi nhiễm hoàn toàn trầm tích xanh trong giai đoạn ấm lên
-Status: Chưa đạt
-Hành Vi Hệ thống: Chế độ chờ, lặp lại vòng thử nghiệm
-[End Nhật Ký]</t>
+Trạng Thái: Chưa đạt
+Hành Vi Hệ Thống: Chế độ chờ, lặp lại vòng thử nghiệm
+[Kết Thúc Nhật Ký]</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7070,7 @@
 Tôi đã bảo họ dừng lại và chờ đợi.
 Đi bộ không khả thi. Lớp Pha Xanh lộ ra nhiều hơn dự kiến, và khả năng định hướng của chúng tôi bắt đầu có sai lệch.
 Daniel nhất quyết tiến lên. Gọi đó là "trực giác của nhà nghiên cứu."
-Tôi không tin vào điều đó. Intuition không thay thế được một kế hoạch khai thác chắc chắn.
+Tôi không tin vào điều đó. Trực giác không thay thế được một kế hoạch khai thác chắc chắn.
 [Wegener - Ghi chú 1]
 Ghi nhận một hiện tượng bất thường.
 Lớp Pha Xanh đang ảnh hưởng đến nhận thức của chúng tôi, nhưng không phải dưới dạng ảo giác. Nó bóp méo cách chúng tôi cảm nhận sự hiện diện của người khác.
@@ -7302,7 +7293,7 @@
 Có thứ gì đó đang bắt chước giọng hắn? Ngươi là ai?
 ...Ta không viết dòng trên.
 Ngươi đã quay lại.
-(Final Ghi chú - Không Ký Tên)
+(Ghi Chú Cuối - Không Ký Tên)
 Ta đã thấy nó. Ta đã thấy nó. Ta đã thấy nó.
 Ta không điên. Ta không điên. Ta không điên.
 %▇ ...#** ...▇ ...&amp;!
@@ -7446,7 +7437,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Dodgep mình trong góc khuất yên tĩnh của vùng đất cằn cỗi là "xưởng bí mật" của Luuk Herssen tại Lahai-Roi.
+          <t>Nép mình trong góc khuất yên tĩnh của vùng đất cằn cỗi là "xưởng bí mật" của Luuk Herssen tại Lahai-Roi.
 Nơi đây tuyệt đối an toàn và đáng tin cậy.
 Giống như chính chủ nhân của nó vậy.</t>
         </is>
@@ -7517,7 +7508,7 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>["Tảng đá khắc họa hình một chú Fluffguin, một Kronapuff và một Toskr Lemming. Chúng quây quần vui vẻ bên một cô bé Roya đang khắc tượng bằng con dao nhỏ.]
-[Dù chỉ là những Dodget khắc đơn sơ, nhưng chi tiết lại rất rõ ràng: Toskr Lemming đeo một thiết bị nghe giống như tai nghe, Fluffguin ôm bát cá, còn Kronapuff ngậm một bông hoa trong miệng.]
+[Dù chỉ là những nét khắc đơn sơ, nhưng chi tiết lại rất rõ ràng: Toskr Lemming đeo một thiết bị nghe giống như tai nghe, Fluffguin ôm bát cá, còn Kronapuff ngậm một bông hoa trong miệng.]
 Gửi những người bạn thân nhất của ta: Fenrir, người yêu thích khiêu vũ. Dallas, người mê ăn cá. Và Bori, người yêu hoa.
 Ta khắc các ngươi lên tảng đá này, để chúng ta mãi mãi bên nhau. Mãi mãi.</t>
         </is>
@@ -7789,30 +7780,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>[Nhiều phần trong cuốn sổ tay không thể đọc được, bị ăn mòn bởi một lực lượng bí ẩn nào đó. Từ những mảnh còn sót lại, bạn suy ra đây là nhật ký của một cô gái Roya tên là Lotta.]
-...
-...
-Mọi thứ đã biến mất. Tất cả.
-Tôi đã tìm kiếm rất lâu nơi ngôi làng từng tồn tại. Tất cả những gì tôi tìm thấy chỉ là một mảnh lông cháy sém, một nhúm lông vũ... và nửa chiếc mỏ. Bố. Mẹ... mọi người trong làng... bạn bè của tôi... tất cả đều đã biến mất.
-Có thứ gì đó đang theo dõi tôi. Tôi không muốn chạy nữa.
-...
-Tôi đã mất rất, rất lâu để học lại cách nói. Lâu hơn nữa để tìm lại can đảm mở cuốn nhật ký này.
-Người phụ nữ đã cứu tôi khỏi những con quái vật tự xưng là giáo sư đến từ Startorch Academy. Bà ấy rất xinh đẹp, nhưng không giống bất kỳ ai trong làng tôi. Bà ấy nói tôi sở hữu một loại Forte hiếm, thứ khiến tôi trở thành "Synchronist tiềm năng".
-Tôi kể cho bà ấy nghe mọi chuyện đã xảy ra với ngôi làng. Tôi hỏi bà ấy: đây có phải là phước lành từ &lt;ano=the Exostrider&gt;Baldur&lt;/ano&gt;? Hay là lời nguyền tàn nhẫn nhất mà &lt;ano=the Threnodian&gt;Hvedrungr&lt;/ano&gt; từng tạo ra?
-Bà ấy im lặng một lúc. Rồi bà ấy kể rằng quê hương của bà cũng đã bị nuốt chửng bởi một thảm họa tương tự. Bà ấy đã vượt qua một đại dương rộng lớn đến mức tôi không thể tưởng tượng nổi, tất cả chỉ để tìm cách giải thoát thế giới khỏi số phận này. Bà ấy mời tôi gia nhập Học viện. Bà ấy nói rằng dù sức mạnh của tôi là phước lành hay lời nguyền, nó có thể là chìa khóa mở ra cánh cửa tương lai của chúng ta.
-...Nhưng tôi chẳng còn gì nữa. Dù &lt;ano=the Exostrider&gt;Baldur&lt;/ano&gt; có đang đợi sau cánh cửa đó, nó cũng không thể trả lại những gì tôi đã mất.
-...
-Tôi quay lại chỗ bà để chào tạm biệt và cảm ơn bà vì tất cả. Tôi nói với bà rằng tôi sắp rời đi để đến Học viện.
-"Chúng ta, người Roya, khắc lời nói lên đá," bà ấy nói, giọng vẫn dịu dàng như xưa, "để &lt;ano=the Threnodian&gt;Hvedrungr&lt;/ano&gt; không thể xóa bỏ sự tồn tại của chúng ta. Còn những đứa trẻ ở Học viện dùng thứ gọi là 'Cassette' để làm điều tương tự. Với bà, con chỉ đang đi đến một nơi khác... để khắc bức tượng thuộc về riêng con."
-"Chừng nào ký ức còn, linh hồn vẫn còn."
-Sau khi đến Học viện, tôi đọc lại cuốn sổ này từ trang đầu đến trang cuối. Bố, mẹ, Fenrir, Dallas, Bori... Bà đã đúng. Họ vẫn sống ở đây, trong những trang giấy này, và sâu thẳm trong tâm trí tôi. Có lẽ, dù không nhận ra, tôi đã trở thành một bức tượng sống, được khắc tên của tất cả họ.
-Tôi sẽ mang linh hồn của họ bên mình, dù đi đến bất cứ đâu. Tôi hứa.
-...
-Bão Hư không. Ngay cả cái tên cũng đã đủ đáng sợ.
-Tôi đã dành cả cuộc đời để chạy trốn khỏi cái bóng của nó. Đó là một trong những xúc tu độc ác của &lt;ano=the Threnodian&gt;Hvedrungr&lt;/ano&gt;, kéo mọi thứ tôi yêu thương vào hư vô. Tôi từng nghĩ... tôi đã học được cách phớt lờ nó.
-Nhưng khi nhìn thấy nó xuất hiện lần nữa, tôi nhận ra điều gì đó. Tất cả những năm tháng học tập... chỉ là sự chuẩn bị cho khoảnh khắc này. Hết lần này đến lần khác, tôi đã đẩy Forte của mình đến giới hạn, đến bờ vực của Overclocking. Và giờ đây, cuối cùng tôi đã hiểu. Tôi đã sẵn sàng.
-Giống như giáo sư đã nói, chỉ có tôi, chỉ có Forte của tôi, mới có thể cứu ngôi làng đó khỏi bị xóa sổ. Ngày ấy, tôi không thể cứu được quê hương của mình. Nhưng lần này, tôi sẽ không đứng nhìn bóng tối lấy đi những người tôi yêu thương.
-Đã đến lúc lên đường.</t>
+          <t>["Nhiều phần trong cuốn sổ đã không thể đọc được, bị ăn mòn bởi một thế lực bí ẩn nào đó. Từ những mảnh còn sót lại, cậu đoán đây là nhật ký của một cô bé Roya tên là Lotta.]</t>
         </is>
       </c>
     </row>
@@ -7895,12 +7863,12 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu Tập thể Spacetrek - Report Thực địa (Lưu trữ)
-Chủ đề Nghiên cứu: Đặc tính Động lực của Discord "Inferno Rider" và Phương tiện của nó
+          <t>Viện Nghiên cứu Tập thể Spacetrek - Báo cáo Thực địa (Lưu trữ)
+Chủ đề Nghiên cứu: Đặc tính Động lực của Tacet Discord "Inferno Rider" và Phương tiện của nó
 Địa điểm Nghiên cứu: Huanglong - Thành phố Cảng Guixu
 Dự án Liên quan: Nghiên cứu &amp; Phát triển Lặp lại Mẫu Xe Máy Thám hiểm Nguyên mẫu
 I. Bối cảnh
-Một Discord cực mạnh, được định danh là "Inferno Rider", đã xuất hiện gần Thành phố Cảng Guixu ở Huanglong. Phương tiện mà nó sử dụng vận hành với độ ổn định đáng kinh ngạc trong môi trường hậu-Lament. Thiết kế cấu trúc và mô hình di chuyển của nó được kỳ vọng sẽ cung cấp những điểm tham chiếu quan trọng cho việc phát triển mẫu xe máy thám hiểm nguyên mẫu của chúng ta.
+Một Tacet Discord cực mạnh, được định danh là "Inferno Rider", đã xuất hiện gần Thành phố Cảng Guixu ở Huanglong. Phương tiện mà nó sử dụng vận hành với độ ổn định đáng kinh ngạc trong môi trường hậu-Lament. Thiết kế cấu trúc và mô hình di chuyển của nó được kỳ vọng sẽ cung cấp những điểm tham chiếu quan trọng cho việc phát triển mẫu xe máy thám hiểm nguyên mẫu của chúng ta.
 II. Ghi chép Thực địa
 Địa điểm: Thành phố Cảng Guixu - Tàn tích Cầu vượt
 Bằng cách triển khai các cảm biến để thu thập dữ liệu động học, chúng tôi xác định được rằng "Inferno Rider" vượt trội hơn mức trung bình ở các khía cạnh sau:
@@ -7911,7 +7879,7 @@
 ……………………
 &lt;b&gt;Ghi chú viết tay của Nhà nghiên cứu:&lt;/b&gt;
 &lt;b&gt;Nguyên mẫu đã hoàn thành. Tôi không ngờ công nghệ cũ từ quê hương mình bao năm trước lại có thể hồi sinh trong một chiếc xe máy thám hiểm.&lt;/b&gt;
-&lt;b&gt;Ngay cả bây giờ, cái tên "Inferno Rider" vẫn khiến người ta khiếp sợ. Tôi không thể xóa đi bóng tối mà Discord ấy đã gieo rắc, cũng chẳng thể thực sự an ủi những linh hồn đã khuất từ lâu. Nhưng ít ra, nguyên mẫu này chứng minh rằng tổ tiên chúng ta đã để lại không chỉ nỗi đau và sự kinh hoàng.&lt;/b&gt;
+&lt;b&gt;Ngay cả bây giờ, cái tên "Inferno Rider" vẫn khiến người ta khiếp sợ. Tôi không thể xóa đi bóng tối mà Tacet Discord ấy đã gieo rắc, cũng chẳng thể thực sự an ủi những linh hồn đã khuất từ lâu. Nhưng ít ra, nguyên mẫu này chứng minh rằng tổ tiên chúng ta đã để lại không chỉ nỗi đau và sự kinh hoàng.&lt;/b&gt;
 &lt;b&gt;Họ còn mang theo hy vọng cho tương lai.&lt;/b&gt;
 &lt;b&gt;Chiếc xe này sẽ tiếp nối ý chí của họ, bảo vệ con đường cho những ai dám khám phá.&lt;/b&gt;</t>
         </is>
@@ -8757,7 +8725,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Họ là những đội cuối cùng rời khỏi Viện Nghiên Cứu.
+          <t>Họ là những đội cuối cùng rời khỏi Viện Nghiên cứu.
 Chắc hẳn họ đã nghĩ đến chuyện từ bỏ không biết bao nhiêu lần. Nhưng rồi, hết lần này đến lần khác, họ lại tìm lại được dũng khí.
 Dù sao, họ vẫn còn đứng đây, phải không?</t>
         </is>
@@ -9106,7 +9074,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Họ là những đội đầu tiên rời khỏi Viện Nghiên Cứu.
+          <t>Họ là những đội đầu tiên rời khỏi Viện Nghiên cứu.
 Đừng lo cho họ. Họ biết rõ mình đang bước vào điều gì.
 Nếu chỉ muốn một cuộc sống yên bình, họ đã chẳng bao giờ đặt chân đến Lahai-Roi ngay từ đầu.</t>
         </is>
@@ -9190,7 +9158,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>(Dodget chữ nguệch ngoạc như trẻ con, rất khó đọc. May mà mỗi lá thư không quá dài.)
+          <t>(Nét chữ nguệch ngoạc như trẻ con, rất khó đọc. May mà mỗi lá thư không quá dài.)
 Lá thư thứ nhất</t>
         </is>
       </c>
@@ -9270,13 +9238,13 @@
 Đơn vị cung cấp: Cửa hàng Mahe
 Mặt hàng:
 Ớt khô: 10 thùng
-Vinegar: 10 thùng
+Giấm: 10 thùng
 Gia vị lẩu: 10 thùng
 Dầu mè cao cấp: 10 thùng
-Rice: 50 bao
+Gạo: 50 bao
 Trứng: 50 thùng
-Address giao hàng: Ký túc xá học viên, Startorch Academy
-&lt;b&gt;Liên kết cùng Lollo Logistics, Cửa hàng Mahe tự hào cam kết giao hàng trong vòng 30 ngày kể từ khi đặt. Chúng tôi cung cấp đa dạng các loại đồ ăn vặt, gia vị và dụng cụ bếp đặc sản Huanglong—lý tưởng cho học viên Startorch Academy! Đặt hàng ngay khi còn hàng. Buy càng nhiều, tiết kiệm càng nhiều.&lt;/b&gt;</t>
+Địa chỉ giao hàng: Ký túc xá học viên, Học viện Startorch
+&lt;b&gt;Liên kết cùng Lollo Logistics, Cửa hàng Mahe tự hào cam kết giao hàng trong vòng 30 ngày kể từ khi đặt. Chúng tôi cung cấp đa dạng các loại đồ ăn vặt, gia vị và dụng cụ bếp đặc sản Huanglong—lý tưởng cho học viên Học viện Startorch! Đặt hàng ngay khi còn hàng. Mua càng nhiều, tiết kiệm càng nhiều.&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9309,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Mạng lưới đường đi của Lahai-Roi, cùng với Đài quan sát Spacetrek từng theo dõi và ghi chép địa hình, hệ sinh thái và khí hậu, đã bị cơn Void Storm tàn phá. Đã đến lúc phải xây dựng lại tất cả!</t>
+          <t>Mạng lưới đường đi của Lahai-Roi, cùng với Đài quan sát Spacetrek từng theo dõi và ghi chép địa hình, hệ sinh thái và khí hậu, đã bị cơn Bão Hư Không tàn phá. Đã đến lúc phải xây dựng lại tất cả!</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9374,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Shui đang hăng hái tìm kiếm thành viên mới cho Câu lạc bộ Overdash danh giá. Có vẻ như khả năng overdash nhanh như điện sẽ mang lại phần thưởng béo bở. Nếu cậu quan tâm, hãy đến trò chuyện với cậu ấy nhé.</t>
+          <t>Thủy đang hăng hái tìm kiếm thành viên mới cho Câu lạc bộ Overdash danh giá. Có vẻ như khả năng overdash nhanh như điện sẽ mang lại phần thưởng béo bở. Nếu cậu quan tâm, hãy đến trò chuyện với cậu ấy nhé.</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9439,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Lollo Campaign đang đối mặt với khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp anh ấy xác minh độ tin cậy của Lollo Campaign!</t>
+          <t>Chiến dịch Lollo đang đối mặt với khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp anh ấy xác minh độ tin cậy của Chiến dịch Lollo!</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9504,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Lollo Campaign đang đối mặt với khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp anh ấy xác minh độ tin cậy của Lollo Campaign!</t>
+          <t>Chiến dịch Lollo đang đối mặt với khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp anh ấy xác minh độ tin cậy của Chiến dịch Lollo!</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9571,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Trải nghiệm Nhiệm Vụ Chính mới "Dawn Ù Lì Trên Vùng Đất Hoang" tại khu vực mới - Thành Phố Chronorift.
+          <t>Trải nghiệm Nhiệm Vụ Chính mới "Bình Minh Ù Lì Trên Vùng Đất Hoang" tại khu vực mới - Thành Phố Chronorift.
 Resonator Chisa đã sẵn sàng gia nhập đội của bạn.
 Nhận phần thưởng trong Sự Kiện Người Trở Về. Solaris-3 đang chờ đón bạn trở lại. Chương mới của bạn bắt đầu ngay bây giờ!</t>
         </is>
@@ -9671,7 +9639,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>&lt;color=HighLight&gt;Trong Peaks of Prestige: Rekindled Duel, các Challenges Duelist mới đã xuất hiện trên Bề mặt Frostlands, cùng với phần thưởng bổ sung.&lt;/color&gt;
+          <t>&lt;color=HighLight&gt;Trong Peaks of Prestige: Rekindled Duel, các Thử Thách Duelist mới đã xuất hiện trên Bề mặt Frostlands, cùng với phần thưởng bổ sung.&lt;/color&gt;
 Kể từ khi Peaks of Prestige trở nên nổi tiếng ở Lahai-Roi, nơi đây và vùng đất băng giá Roya Frostlands đã trở thành bãi thử cho nhiều đấu sĩ tài ba. Hãy thách đấu hoặc đón nhận thử thách để giành lấy chiến thắng và vinh quang!</t>
         </is>
       </c>
@@ -9997,7 +9965,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Nằm ở góc xa xôi của Fabricatorium là một bãi chôn Echoes, ẩn sâu trong những hẻm núi dưới lòng biển. Nơi đây, đống Brooder bỏ đi chất đầy sàn. Những Echoes đã ngừng hoạt động xếp hàng chờ bị tháo dỡ và thiêu hủy trong xưởng. Tần số của chúng sẽ được tái chế và chuyển hướng khắp Fabricatorium, nuôi dưỡng sự ra đời của những Echoes mới.</t>
+          <t>Nằm ở góc xa xôi của Fabricatorium là một bãi chôn Echo, ẩn sâu trong những hẻm núi dưới lòng biển. Nơi đây, đống Brooder bỏ đi chất đầy sàn. Những Echo đã ngừng hoạt động xếp hàng chờ bị tháo dỡ và thiêu hủy trong xưởng. Tần số của chúng sẽ được tái chế và chuyển hướng khắp Fabricatorium, nuôi dưỡng sự ra đời của những Echo mới.</t>
         </is>
       </c>
     </row>
@@ -10063,8 +10031,8 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khu vực trung tâm trong Xưởng Dệt Vải của Vực Sâu, nơi phát triển các Cộng Hưởng Common. Hàng loạt Máy Ấp Cộng Hưởng xếp san sát, ấp ủ những Cộng Hưởng chờ tái sinh.
-Là nền tảng của hệ thống Cộng Hưởng Common, địa điểm này được Hội đầu tư mạnh vào an ninh và nghiên cứu.</t>
+          <t>Khu vực trung tâm trong Xưởng Dệt Vải của Vực Sâu, nơi phát triển các Cộng Hưởng Thường. Hàng loạt Máy Ấp Cộng Hưởng xếp san sát, ấp ủ những Cộng Hưởng chờ tái sinh.
+Là nền tảng của hệ thống Cộng Hưởng Thường, địa điểm này được Hội đầu tư mạnh vào an ninh và nghiên cứu.</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10298,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Một con đèo tự nhiên với nền đá vững chắc, được đánh dấu bởi những vách đá lởm chởm và những stone pillar cao chót vót. Là cửa ngõ dẫn vào Cao nguyên Sanguis, nơi đây đã chứng kiến biết bao thế hệ Kẻ Chiến Đấu lên đường thực hiện cuộc săn thiêng, tất cả đều dưới ánh mắt lặng lẽ của tượng đá khổng lồ Atilius, Hero of Heroes.</t>
+          <t>Một con đèo tự nhiên với nền đá vững chắc, được đánh dấu bởi những vách đá lởm chởm và những cột đá cao chót vót. Là cửa ngõ dẫn vào Cao nguyên Sanguis, nơi đây đã chứng kiến biết bao thế hệ Kẻ Chiến Đấu lên đường thực hiện cuộc săn thiêng, tất cả đều dưới ánh mắt lặng lẽ của tượng đá khổng lồ Atilius, Anh Hùng Trong Các Anh Hùng.</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10623,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Đỉnh núi cao nhất Sanguis Plateaus, được đặt tên theo đỉnh núi độc đáo và ba Hero of Heroes từng đứng tại đó. Với các Chiến Binh, đây là vùng đất thiêng. Truyền thuyết kể rằng mỗi Hero of Heroes đều đối mặt với thử thách cuối cùng tại đây, và chỉ khi đó, họ mới chinh phục được số phận và khoác lên mình vinh quang.</t>
+          <t>Đỉnh núi cao nhất Cao Nguyên Sanguis, được đặt tên theo đỉnh núi độc đáo và ba Anh Hùng Trong Các Anh Hùng từng đứng tại đó. Với các Chiến Binh, đây là vùng đất thiêng. Truyền thuyết kể rằng mỗi Anh Hùng Trong Các Anh Hùng đều đối mặt với thử thách cuối cùng tại đây, và chỉ khi đó, họ mới chinh phục được số phận và khoác lên mình vinh quang.</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11078,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Đặt theo tên thanh đại kiếm Exostrider khổng lồ nâng đỡ mái vòm ngầm, vùng nước tối tăm nơi đây như một cánh cổng dẫn đến thế giới khác. Là một trong số ít khu vực được che chắn khỏi Void Storm, nó đã trở thành nền tảng cho Starward Riseway của Spacetrek Collective - một thang máy leo theo sống lưng thanh kiếm, nối liền ốc đảo ngầm này với vùng đất băng giá Roya Frostlands.</t>
+          <t>Đặt theo tên thanh đại kiếm Exostrider khổng lồ nâng đỡ mái vòm ngầm, vùng nước tối tăm nơi đây như một cánh cổng dẫn đến thế giới khác. Là một trong số ít khu vực được che chắn khỏi Bão Hư Không, nó đã trở thành nền tảng cho Starward Riseway của Spacetrek Collective - một thang máy leo theo sống lưng thanh kiếm, nối liền ốc đảo ngầm này với vùng đất băng giá Roya Frostlands.</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11338,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Startorch Academy thuộc Tập đoàn Spacetrek: một cộng đồng khoa học không biên giới, cống hiến cho việc theo đuổi tri thức thuần túy. Cái tên của nó thể hiện tinh thần: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Trong thành phố học thuật rộng lớn này, tri thức được trao đổi tự do, các nền văn hóa giao thoa hòa quyện.</t>
+          <t>Học viện Startorch thuộc Tập đoàn Spacetrek: một cộng đồng khoa học không biên giới, cống hiến cho việc theo đuổi tri thức thuần túy. Cái tên của nó thể hiện tinh thần: "giữ ngọn lửa tìm tòi và thắp sáng ngọn đuốc văn minh". Trong thành phố học thuật rộng lớn này, tri thức được trao đổi tự do, các nền văn hóa giao thoa hòa quyện.</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11403,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Một sinh vật kinh hoàng sinh ra từ ảnh hưởng của Threnody, thường xuất hiện ở vùng hoang mạc phía sau Lahai-Roi, được gọi là "Mawburrow Desert". Nguồn sức mạnh và điểm yếu chí mạng của nó nằm ở các Bộ Điều Tiết Vật Chất Hư Không trên đầu. Bất cứ nơi nào nó đi qua, sự sống đều bị dập tắt, chỉ còn lại hư vô theo sau.</t>
+          <t>Một sinh vật kinh hoàng sinh ra từ ảnh hưởng của Threnody, thường xuất hiện ở vùng hoang mạc phía sau Lahai-Roi, được gọi là "Sa Mạc Mawburrow". Nguồn sức mạnh và điểm yếu chí mạng của nó nằm ở các Bộ Điều Tiết Vật Chất Hư Không trên đầu. Bất cứ nơi nào nó đi qua, sự sống đều bị dập tắt, chỉ còn lại hư vô theo sau.</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11468,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Một phương tiện di chuyển đa địa hình nhẹ, đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật Chất Hư Không của Startorch Academy. Là công cụ không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của sinh viên và giảng viên.</t>
+          <t>Một phương tiện địa hình nhẹ được đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật chất Hư không của Học viện Startorch. Không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của giảng viên và sinh viên.</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11598,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Một thiên đường ấm áp và ẩm ướt dưới lòng đất vùng Roya Frostlands. Sau một sự dịch chuyển cực cổ xưa, khu vực này trở thành cực mới của Solaris, buộc tộc Roya phải di cư xuống lòng đất. Tại đây, Spacetrek Collective đã thành lập Startorch Academy. Ngày nay, thành phố học thuật không biên giới này đã trở thành cái nôi của vô số học giả trẻ tài năng.</t>
+          <t>Một thiên đường ấm áp và ẩm ướt dưới lòng đất vùng Roya Frostlands. Sau một sự dịch chuyển cực cổ xưa, khu vực này trở thành cực mới của Solaris, buộc tộc Roya phải di cư xuống lòng đất. Tại đây, Spacetrek Collective đã thành lập Học viện Startorch. Ngày nay, thành phố học thuật không biên giới này đã trở thành cái nôi của vô số học giả trẻ tài năng.</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12198,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Một dạng thử thách cực kỳ khó trong Tidal Defense Simulator.
+          <t>Một dạng thử thách cực kỳ khó trong Mô Phỏng Phòng Thủ Thủy Triều.
 Ở Chế Độ Bẫy Chết, người tham gia phải dựa vào Giao Thức Viễn Thính và hỗ trợ hậu cần nâng cao để chống lại những đợt tấn công tiến hóa của Tacet Discord.</t>
         </is>
       </c>
@@ -12426,7 +12394,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Với sứ mệnh cốt lõi là bồi dưỡng những "Đồng Bộ Giả" có khả năng Resonance Tăng Cường với Exostrider, Startorch Academy đã thành lập Rabelle College. Nghiên cứu của trường dựa trên ba lĩnh vực: nghiên cứu Exostrider, Void Storm và năng lượng Reactor Drive, từ đó hình thành nên các khoa Kỹ thuật Exostrider, Khoa học Vật chất Hư Không và Khoa học Năng lượng Ánh sáng. Trong đó, Bộ phận Bảo tồn Sinh thái, gắn bó mật thiết với công việc của Exo Genesis Labs, được gọi thân mật là "Cánh Nông học".</t>
+          <t>Với sứ mệnh cốt lõi là bồi dưỡng những "Đồng Bộ Giả" có khả năng Cộng Hưởng Tăng Cường với Exostrider, Học viện Startorch đã thành lập Rabelle College. Nghiên cứu của trường dựa trên ba lĩnh vực: nghiên cứu Exostrider, Bão Hư Không và năng lượng Reactor Drive, từ đó hình thành nên các khoa Kỹ thuật Exostrider, Khoa học Vật chất Hư Không và Khoa học Năng lượng Ánh sáng. Trong đó, Bộ phận Bảo tồn Sinh thái, gắn bó mật thiết với công việc của Exo Genesis Labs, được gọi thân mật là "Cánh Nông học".</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12459,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Cơ sở thử nghiệm hỏa lực dành cho vũ khí chiến thuật và các cấu trúc cơ giới hóa, do Phòng Phát triển Chiến thuật thuộc Department Kỹ thuật Exostrider vận hành. Nơi đây hỗ trợ kiểm định vũ khí quy mô lớn và thử nghiệm thiết bị, đồng thời mở cửa cho toàn bộ giảng viên và học viên Học viện.</t>
+          <t>Cơ sở thử nghiệm hỏa lực dành cho vũ khí chiến thuật và các cấu trúc cơ giới hóa, do Phòng Phát triển Chiến thuật thuộc Cục Kỹ thuật Exostrider vận hành. Nơi đây hỗ trợ kiểm định vũ khí quy mô lớn và thử nghiệm thiết bị, đồng thời mở cửa cho toàn bộ giảng viên và học viên Học viện.</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12719,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Các trưởng lão Roya được tổ chức thành Lục Giác—ba cặp đôi nắm giữ các vai trò như Mắt, Người Buộc, và Người Định Hình. Mỗi cặp được giao phó một chức năng cốt lõi: quan sát, lưu trữ và dự đoán. Họ cư ngụ trong Solisylum, kết nối ý thức với Heliogyre để theo dõi quỹ đạo của Lò Phản Ứng và dự báo Void Storm. Để tối đa hóa hiệu quả, chỉ một trong Lục Giác thức tỉnh mỗi chu kỳ để giám sát công việc hàng ngày. Khi mỗi mùa kết thúc, các Người Chăn Cừu từ khắp các khu định cư sẽ tập hợp tại Bjartr Woods để trình báo dữ liệu đã ghi chép, sau đó Lục Giác sẽ thảo luận để vạch ra tương lai.</t>
+          <t>Các trưởng lão Roya được tổ chức thành Lục Giác—ba cặp đôi nắm giữ các vai trò như Mắt, Người Buộc, và Người Định Hình. Mỗi cặp được giao phó một chức năng cốt lõi: quan sát, lưu trữ và dự đoán. Họ cư ngụ trong Solisylum, kết nối ý thức với Heliogyre để theo dõi quỹ đạo của Lò Phản Ứng và dự báo Bão Hư Không. Để tối đa hóa hiệu quả, chỉ một trong Lục Giác thức tỉnh mỗi chu kỳ để giám sát công việc hàng ngày. Khi mỗi mùa kết thúc, các Người Chăn Cừu từ khắp các khu định cư sẽ tập hợp tại Bjartr Woods để trình báo dữ liệu đã ghi chép, sau đó Lục Giác sẽ thảo luận để vạch ra tương lai.</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12784,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu Chính thức thuộc Tập đoàn Spacetrek: Viện Nghiên Cứu Spacetrek là một phần của sáng kiến nghiên cứu không biên giới cùng tên với Startorch Academy. Nhiệm vụ của viện là khai thác và ứng dụng các công nghệ tiên tiến. Nằm ngay trên đỉnh lưỡi kiếm khổng lồ, viện kết nối trực tiếp với Starward Riseway, như một vì sao bảo vệ mang tên Stargram, canh giữ Lahai-Roi từ trên cao.</t>
+          <t>Viện Nghiên cứu Chính thức thuộc Tập đoàn Spacetrek: Viện Nghiên cứu Spacetrek là một phần của sáng kiến nghiên cứu không biên giới cùng tên với Học viện Startorch. Nhiệm vụ của viện là khai thác và ứng dụng các công nghệ tiên tiến. Nằm ngay trên đỉnh lưỡi kiếm khổng lồ, viện kết nối trực tiếp với Starward Riseway, như một vì sao bảo vệ mang tên Stargram, canh giữ Lahai-Roi từ trên cao.</t>
         </is>
       </c>
     </row>
@@ -13344,7 +13312,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Tháp liên lạc cao vút này từng là biểu tượng cho khát vọng kết nối của con người qua sóng vô tuyến. Nhưng cuối cùng, chính tại đây, Lament đã bắt đầu. Giờ đây, trong trái tim hỗn loạn của nó, tháp tái hiện những mảnh ký ức quen thuộc, như thể đang dụ dỗ người khác bước sâu hơn vào bên trong…</t>
+          <t>Tháp liên lạc cao vút này từng là biểu tượng cho khát vọng kết nối của con người qua sóng vô tuyến. Nhưng cuối cùng, chính tại đây, Lời Than Vãn đã bắt đầu. Giờ đây, trong trái tim hỗn loạn của nó, tháp tái hiện những mảnh ký ức quen thuộc, như thể đang dụ dỗ người khác bước sâu hơn vào bên trong…</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13378,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Quá khứ, hiện thực, Nỗi Bi Ai... Đó là khung cảnh nhìn từ đỉnh Neon Tower. Hãy nhìn chúng. Đối mặt với chúng. Đương đầu với chúng.
+          <t>Quá khứ, hiện thực, Nỗi Bi Ai... Đó là khung cảnh nhìn từ đỉnh Tháp Neon. Hãy nhìn chúng. Đối mặt với chúng. Đương đầu với chúng.
 Bước vào ngày mai. Không gì có thể cản bước ngươi.</t>
         </is>
       </c>
@@ -13476,7 +13444,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Khi mật độ Vật Chất Hư Không đạt ngưỡng tới hạn, Ánh Sáng Lấp Lánh sẽ giáng xuống từ trời cao và mặt đất rung chuyển dữ dội—Void Storm theo sau, thảm họa tàn khốc nhất của Lahai-Roi. Vạn vật tan biến vào hư vô, trong khi bầy Exoswarm bị nhiễm độc đột biến thành những Voidworm khổng lồ, phủ bóng thèm khát nuốt chửng khắp mặt đất.</t>
+          <t>Khi mật độ Vật Chất Hư Không đạt ngưỡng tới hạn, Ánh Sáng Lấp Lánh sẽ giáng xuống từ trời cao và mặt đất rung chuyển dữ dội—Bão Hư Không theo sau, thảm họa tàn khốc nhất của Lahai-Roi. Vạn vật tan biến vào hư vô, trong khi bầy Exoswarm bị nhiễm độc đột biến thành những Voidworm khổng lồ, phủ bóng thèm khát nuốt chửng khắp mặt đất.</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13509,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Khi sức mạnh tinh thần và Forte của một Resonators bị đẩy đến giới hạn trong thời gian dài, họ có thể rơi vào trạng thái hiếm gặp gọi là "Quá Tải". Dù tình trạng này có thể kiểm soát, nhưng không có cách chữa trị vĩnh viễn. Trong trường hợp nghiêm trọng, Tacet Field có thể mở rộng mất kiểm soát, nuốt chửng mọi thứ xung quanh, biến Resonators Quá Tải thành một Discord của Tacet Field.</t>
+          <t>Khi sức mạnh tinh thần và Forte của một Resonator bị đẩy đến giới hạn trong thời gian dài, họ có thể rơi vào trạng thái hiếm gặp gọi là "Quá Tải". Dù tình trạng này có thể kiểm soát, nhưng không có cách chữa trị vĩnh viễn. Trong trường hợp nghiêm trọng, Tổ Tacet có thể mở rộng mất kiểm soát, nuốt chửng mọi thứ xung quanh, biến Resonator Quá Tải thành một Tacet Discord của Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13641,7 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>Điều biến là quá trình điều chỉnh tần số. Trên Solaris-3, tần số là công cụ tối quan trọng để khám phá chân lý về thực tại. Bằng cách thay đổi những tần số này, ta có thể đi sâu vào cốt lõi của sự tồn tại.
-Tại Black Shores, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Black Shores, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Modulator".</t>
+Tại Bờ Biển Đen, việc điều biến Ma Trận Sao là bước then chốt để truy vết và phân tích Lament. Suốt lịch sử Bờ Biển Đen, chỉ duy nhất một cá nhân từng được tôn vinh với danh hiệu "Điều Biến Giả".</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13836,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Một hiện tượng Waveworn bản địa của Rinascita. Nó tụ lại trên bầu trời rồi đổ sập xuống như thác nước, trút cơn mưa xối xả. Nơi nào Sóng Đen tràn tới, Tacet Discord sẽ xuất hiện, và vùng đất quanh điểm khởi nguồn sẽ biến thành một Tacet Field mới. Theo ghi chép của Order of the Deep, hai đợt Sóng Đen lớn trong lịch sử đã lần lượt bị chặn đứng bởi Napoli đệ Nhị và Thánh Nữ Fleurdelys.</t>
+          <t>Một hiện tượng Waveworn bản địa của Rinascita. Nó tụ lại trên bầu trời rồi đổ sập xuống như thác nước, trút cơn mưa xối xả. Nơi nào Sóng Đen tràn tới, Tacet Discord sẽ xuất hiện, và vùng đất quanh điểm khởi nguồn sẽ biến thành một Tổ Tacet mới. Theo ghi chép của Order of the Deep, hai đợt Sóng Đen lớn trong lịch sử đã lần lượt bị chặn đứng bởi Napoli đệ Nhị và Thánh Nữ Fleurdelys.</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13901,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Nhờ Genesis Nexus, Echoes của Rinascita có thể tồn tại mà không cần Reserved Terminals. Người dân Ragunna tôn thờ Common Echoes như món quà thiêng liêng từ Sentinel Imperator và coi chúng như bạn bè, đồng minh đáng tin cậy. Được quản lý bởi Order of the Deep, Common Echoes đã hòa nhập vào mọi mặt của cuộc sống hàng ngày, trở thành biểu tượng khiến Rinascita được mệnh danh là "Land Của Những Âm Vang".</t>
+          <t>Nhờ Genesis Nexus, Echoes của Rinascita có thể tồn tại mà không cần Reserved Terminals. Người dân Ragunna tôn thờ Common Echoes như món quà thiêng liêng từ Sentinel Imperator và coi chúng như bạn bè, đồng minh đáng tin cậy. Được quản lý bởi Order of the Deep, Common Echoes đã hòa nhập vào mọi mặt của cuộc sống hàng ngày, trở thành biểu tượng khiến Rinascita được mệnh danh là "Vùng Đất Của Những Âm Vang".</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13966,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Trung tâm Nexus Resonance của Rinascita, còn gọi là Genesis Nexus. Theo truyền thuyết, Imperator đã tiết lộ bí mật của Genesis Nexus cho người Rinascita, cho phép họ xây dựng những công trình vĩ đại khác như biểu tượng cho quyền lực và chủ quyền của Sentinel. Trong phạm vi của Genesis Nexus, Echoes có thể tồn tại dưới dạng vật lý mà không cần dựa vào Thiết bị đầu cuối.</t>
+          <t>Trung tâm Nexus Cộng Hưởng của Rinascita, còn gọi là Genesis Nexus. Theo truyền thuyết, Imperator đã tiết lộ bí mật của Genesis Nexus cho người Rinascita, cho phép họ xây dựng những công trình vĩ đại khác như biểu tượng cho quyền lực và chủ quyền của Sentinel. Trong phạm vi của Genesis Nexus, Echo có thể tồn tại dưới dạng vật lý mà không cần dựa vào Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -14063,7 +14031,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Nhân dịp lễ hội đặc biệt năm nay và Triển lãm Văn hóa Roya cùng tham gia, Hội Student đã giành được hai tầng đầu của Rabelle College nhờ sự hỗ trợ của một số điều phối viên tài năng. Những phòng học từng bị hạn chế nghiêm ngặt giờ đã biến thành không gian trưng bày sôi động của các câu lạc bộ.</t>
+          <t>Nhân dịp lễ hội đặc biệt năm nay và Triển lãm Văn hóa Roya cùng tham gia, Hội Học sinh đã giành được hai tầng đầu của Rabelle College nhờ sự hỗ trợ của một số điều phối viên tài năng. Những phòng học từng bị hạn chế nghiêm ngặt giờ đã biến thành không gian trưng bày sôi động của các câu lạc bộ.</t>
         </is>
       </c>
     </row>
@@ -14129,8 +14097,8 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Mỗi năm, sau kỳ thi cuối kỳ là mùa triển lãm câu lạc bộ của Startorch Academy—cơ hội hoàn hảo để sinh viên giải phóng năng lượng dồn Dodgen.
-Với việc Core Phản Ứng được khôi phục và New Solar Ceremony thành công, Ban Điều Hành Học viện đã thông báo rằng triển lãm năm nay sẽ được đồng tổ chức với Roya. Với chủ đề "New Solar Ceremony", sự kiện nhằm thắt chặt tình hữu nghị giữa hai dân tộc.</t>
+          <t>Mỗi năm, sau kỳ thi cuối kỳ là mùa triển lãm câu lạc bộ của Học viện Startorch—cơ hội hoàn hảo để sinh viên giải phóng năng lượng dồn nén.
+Với việc Lõi Phản Ứng được khôi phục và Lễ Hội Mặt Trời Mới thành công, Ban Điều Hành Học viện đã thông báo rằng triển lãm năm nay sẽ được đồng tổ chức với Roya. Với chủ đề "Lễ Hội Mặt Trời Mới", sự kiện nhằm thắt chặt tình hữu nghị giữa hai dân tộc.</t>
         </is>
       </c>
     </row>
@@ -14332,9 +14300,9 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>New Moon, nơi ánh sáng tìm về khởi đầu mới.
-Một trong những Lunar Giai đoạn tiên tri của Septimont. New Moon báo hiệu sự khởi đầu của chu kỳ mặt trăng, khi bề mặt của nó hoàn toàn chìm trong bóng tối.
-New Moon tượng trưng cho sự tái sinh và khởi đầu mới:
+          <t>Trăng Non, nơi ánh sáng tìm về khởi đầu mới.
+Một trong những Pha Mặt Trăng tiên tri của Septimont. Trăng Non báo hiệu sự khởi đầu của chu kỳ mặt trăng, khi bề mặt của nó hoàn toàn chìm trong bóng tối.
+Trăng Non tượng trưng cho sự tái sinh và khởi đầu mới:
 Sau hành trình dài trên bầu trời, mặt trăng quay về điểm xuất phát, được làm mới và sẵn sàng bắt đầu lại từ đầu.</t>
         </is>
       </c>
@@ -14403,9 +14371,9 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Crescent Moon, nơi ánh sáng bắt đầu lan tỏa.
-Một trong những Lunar Giai đoạn tiên tri của Septimont. Sau New Moon, bóng tối dần rút lui, và một vệt sáng mỏng manh xuất hiện trên bầu trời.
-Crescent Moon tượng trưng cho sự sinh trưởng và hy vọng:
+          <t>Trăng Lưỡi Liềm, nơi ánh sáng bắt đầu lan tỏa.
+Một trong những Pha Mặt Trăng tiên tri của Septimont. Sau Trăng Non, bóng tối dần rút lui, và một vệt sáng mỏng manh xuất hiện trên bầu trời.
+Trăng Lưỡi Liềm tượng trưng cho sự sinh trưởng và hy vọng:
 Vòng cung ánh sáng mong manh ấy mỗi đêm lại tròn đầy hơn trong mắt những ai ngước nhìn lên.</t>
         </is>
       </c>
@@ -14474,7 +14442,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>First Quarter, nơi một cánh cung ánh sáng vẽ lên bức màn đêm.
+          <t>Trăng bán nguyệt đầu tiên, nơi một cánh cung ánh sáng vẽ lên bức màn đêm.
 Một trong những giai đoạn Mặt Trăng tiên tri của Septimont. Đó là vầng trăng nửa sáng, rực rỡ bên phải, nơi ánh sáng và bóng tối chia đôi bề mặt.
 Trăng bán nguyệt tượng trưng cho hành động và thử thách:
 Sau đợi chờ dài lâu, giờ là lúc bước về phía ánh sáng tròn đầy.</t>
@@ -14545,9 +14513,9 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Waxing Gibbous, nơi đợi chờ sự thăng hoa.
-Một trong những Lunar Giai đoạn tiên tri của Septimont. Đây là thời khắc Trăng Rằm sắp đến, bóng tối dần tan, ánh trăng soi sáng màn đêm.
-Waxing Gibbous tượng trưng cho sự điều chỉnh và chuẩn bị:
+          <t>Trăng Tròn Dần, nơi đợi chờ sự thăng hoa.
+Một trong những Pha Mặt Trăng tiên tri của Septimont. Đây là thời khắc Trăng Rằm sắp đến, bóng tối dần tan, ánh trăng soi sáng màn đêm.
+Trăng Tròn Dần tượng trưng cho sự điều chỉnh và chuẩn bị:
 Bước chuyển mình đầy bất ổn đòi hỏi ta phải tự điều chỉnh để đạt được đột phá.</t>
         </is>
       </c>
@@ -14687,9 +14655,9 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Waning Gibbous, nơi ánh sáng dần tắt nhưng vẫn còn vương vấn.
-Một trong những giai đoạn Mặt Trăng tiên tri của Septimont. Sau Full Moon, bóng tối trở lại, và ánh sáng bắt đầu rút lui trong lặng lẽ.
-Waning Gibbous tượng trưng cho sự suy ngẫm và sẻ chia:
+          <t>Trăng Khuyết Suy, nơi ánh sáng dần tắt nhưng vẫn còn vương vấn.
+Một trong những giai đoạn Mặt Trăng tiên tri của Septimont. Sau Trăng Tròn, bóng tối trở lại, và ánh sáng bắt đầu rút lui trong lặng lẽ.
+Trăng Khuyết Suy tượng trưng cho sự suy ngẫm và sẻ chia:
 Vạn vật đều có lúc thịnh suy, niềm vui và nỗi buồn đan xen theo quy luật tự nhiên.</t>
         </is>
       </c>
@@ -14758,9 +14726,9 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Last Quarter, nơi bóng tối đòi lại phần của mình.
-Một trong những Lunar Giai đoạn tiên tri của Septimont. Đó là vầng trăng nửa sáng, sáng bên trái, nơi ánh sáng và bóng tối chia đều bề mặt mặt trăng.
-Last Quarter tượng trưng cho sự giải thoát và quyết định:
+          <t>Trăng Khuyết Cuối, nơi bóng tối đòi lại phần của mình.
+Một trong những Pha Mặt Trăng tiên tri của Septimont. Đó là vầng trăng nửa sáng, sáng bên trái, nơi ánh sáng và bóng tối chia đều bề mặt mặt trăng.
+Trăng Khuyết Cuối tượng trưng cho sự giải thoát và quyết định:
 Giữa những con sóng đổi thay, những thủy thủ lão luyện biết khi nào nên buông tay.</t>
         </is>
       </c>
@@ -14829,9 +14797,9 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Waning Crescent, nơi chỉ còn le lói một tia sáng.
+          <t>Trăng Khuyết Tàn, nơi chỉ còn le lói một tia sáng.
 Một trong những giai đoạn Mặt Trăng tiên tri của Septimont. Giai đoạn cuối cùng của chu kỳ, khi chỉ còn một vệt sáng mờ bám vào rìa bóng tối.
-Waning Crescent tượng trưng cho sự nghỉ ngơi và an định:
+Trăng Khuyết Tàn tượng trưng cho sự nghỉ ngơi và an định:
 Dù hành trình vĩ đại đến đâu, cũng cần dừng chân để lấy lại hơi thở.</t>
         </is>
       </c>
@@ -14900,9 +14868,9 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Twin Moons, nơi hai sinh mệnh đan xen. 
+          <t>Song Nguyệt, nơi hai sinh mệnh đan xen. 
 Một Pha Trăng độc đáo và khó đoán tại Septimont. Hai vầng trăng lưỡi liềm mọc nối đuôi nhau trong sự tĩnh lặng đối xứng.
-Twin Moons tượng trưng cho niềm tin và tình bạn:
+Song Nguyệt tượng trưng cho niềm tin và tình bạn:
 Với một đồng minh kiên định bên cạnh, ngay cả đêm dài nhất cũng không còn đáng sợ.</t>
         </is>
       </c>
@@ -14971,9 +14939,9 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Rippled Moon, nơi mọi thay đổi trở về một.
-Một Pha Trăng độc đáo và khó lường tại Septimont. Vầng Rippled Moon lấp lánh với những lớp ánh sáng như sóng chảy tràn trên bề mặt.
-Rippled Moon tượng trưng cho vĩnh cửu và biến đổi:
+          <t>Trăng Gợn Sóng, nơi mọi thay đổi trở về một.
+Một Pha Trăng độc đáo và khó lường tại Septimont. Vầng Trăng Gợn Sóng lấp lánh với những lớp ánh sáng như sóng chảy tràn trên bề mặt.
+Trăng Gợn Sóng tượng trưng cho vĩnh cửu và biến đổi:
 Trong thế giới này, chỉ có vòng xoáy của sự thay đổi bất tận mới trường tồn mãi mãi.</t>
         </is>
       </c>
@@ -15448,8 +15416,8 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Tâm Ảnh Cốt Core sở hữu sức mạnh chiến đấu và hiệu ứng mạnh mẽ. Chúng chính là chìa khóa để giành chiến thắng.
-- Khác với Tâm Ảnh Thường, Tâm Ảnh Cốt Core không tốn Năng Lượng để Triển khai và chỉ có thể Triển khai khi đáp ứng các điều kiện cụ thể.</t>
+          <t>Tâm Ảnh Cốt Lõi sở hữu sức mạnh chiến đấu và hiệu ứng mạnh mẽ. Chúng chính là chìa khóa để giành chiến thắng.
+- Khác với Tâm Ảnh Thường, Tâm Ảnh Cốt Lõi không tốn Năng Lượng để Triển Khai và chỉ có thể Triển Khai khi đáp ứng các điều kiện cụ thể.</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15484,7 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>Italo là du học sinh đến từ Ragunna. Dù đã chứng kiến những kỳ quan công nghệ ở Lahai-Roi, cậu vẫn tin rằng không gì mạnh hơn một Echo.
-Đặc điểm Đấu Thủ: None</t>
+Đặc điểm Đấu Thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -15649,8 +15617,8 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Luanquan nhận ra mình đã bỏ quên một vật phẩm quan trọng trên đường đến vùng đất băng giá. Sai lầm này đã phủ bóng đen lên chuyến thám hiểm khoa học của cô.
-Đặc tính Chiến Binh: None</t>
+          <t>Loan Tuyền nhận ra mình đã bỏ quên một vật phẩm quan trọng trên đường đến vùng đất băng giá. Sai lầm này đã phủ bóng đen lên chuyến thám hiểm khoa học của cô.
+Đặc tính Chiến Binh: Không có</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15685,7 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>Người Roya tin rằng thức ăn ngon nhất chỉ có ở những nơi khắc nghiệt nhất. Cá pecca cũng không ngoại lệ.
-Đặc tính Kẻ Đấu: Một trong các Echoes của kẻ đấu sẽ nhận thêm 1 STR và CON mỗi khi triển khai Echoes.</t>
+Đặc tính Kẻ Đấu: Một trong các Echo của kẻ đấu sẽ nhận thêm 1 STR và CON mỗi khi triển khai Echo.</t>
         </is>
       </c>
     </row>
@@ -15783,8 +15751,8 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Varr đang ngươi mò tìm ý tưởng cho một cuốn tiểu thuyết hấp dẫn. Nguồn cảm hứng của cậu chủ yếu đến từ truyền thuyết về Exostrider.
-Đặc tính Đấu Sĩ: Khi đối thủ sử dụng Active Skill, Echoes trên chiến trường của đối thủ sẽ mất 1 Sức Mạnh và Thể Trạng.</t>
+          <t>Varr đang mày mò tìm ý tưởng cho một cuốn tiểu thuyết hấp dẫn. Nguồn cảm hứng của cậu chủ yếu đến từ truyền thuyết về Exostrider.
+Đặc tính Đấu Sĩ: Khi đối thủ sử dụng Kỹ Năng Chủ Động, Echo trên chiến trường của đối thủ sẽ mất 1 Sức Mạnh và Thể Trạng.</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15886,7 @@
       <c r="M209" t="inlineStr">
         <is>
           <t>"Dự án không chính thức nghĩa là gì vậy?
-Đặc điểm Duelist: None"</t>
+Đặc điểm Duelist: Không có"</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15953,7 @@
       <c r="M210" t="inlineStr">
         <is>
           <t>"Đây đều là những khoản chi cần thiết mà!
-Đặc tính Đấu Thủ: None"</t>
+Đặc tính Đấu Thủ: Không có"</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16020,7 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>Liệu Tard-E Units có mơ về những boong điện tử?
-Đặc tính Đấu Thủ: None</t>
+Đặc tính Đấu Thủ: Không có</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16487,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>"Đây là bức tượng Namipon lớn nhất ở Honami City. Đối với người dân địa phương, việc có nhiều Namipon như vậy còn đáng tự hào hơn cả việc thành phố là trung tâm kinh tế."</t>
+          <t>"Đây là bức tượng Namipon lớn nhất ở Thành Phố Honami. Đối với người dân địa phương, việc có nhiều Namipon như vậy còn đáng tự hào hơn cả việc thành phố là trung tâm kinh tế."</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16618,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Một cơ sở ngầm ẩn sâu dưới lòng biển. Đây là trung tâm phân phối các Echo Thông Common. Ít ai thực sự hiểu hết mục đích của nó.
+          <t>Một cơ sở ngầm ẩn sâu dưới lòng biển. Đây là trung tâm phân phối các Tiếng Vọng Thông Thường. Ít ai thực sự hiểu hết mục đích của nó.
 Dưới sự bình yên là cơn điên loạn, và cuối cơn điên loạn ấy là tập hợp những khát khao chưa thành, vương vấn không dứt.</t>
         </is>
       </c>
@@ -16717,7 +16685,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Sanguis Plateaus vừa là bãi săn của người Septimont, vừa là tuyến phòng thủ đầu tiên chống lại Dark Tide. Trên vùng cao nguyên hùng vĩ mà u ám này, đám mây Blightcloud lơ lửng phía trên không ngừng khuấy động.
+          <t>Cao Nguyên Sanguis vừa là bãi săn của người Septimont, vừa là tuyến phòng thủ đầu tiên chống lại Dark Tide. Trên vùng cao nguyên hùng vĩ mà u ám này, đám mây Blightcloud lơ lửng phía trên không ngừng khuấy động.
 Nơi đây, quyền lực và vinh quang đạt đến đỉnh cao, rồi nhường chỗ cho máu và cái chết.</t>
         </is>
       </c>
@@ -16849,7 +16817,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sau thất bại của Kẻ Giả Mạo Quân Chủ, Rinascita tạm thời được hưởng một khoảng bình yên ngắn ngủi. Để mở Nang Văn Minh mà Imperator để lại, cậu và Abby chuẩn bị cho Ragunna tìm kiếm Cartethyia, nhưng lại phát hiện người dân nơi đây đang bị ám ảnh bởi những cơn ác mộng. Trong khi đó, tại Inverted Tower, Avinoleum, Kẻ Sát Discord trở về đã nổ súng vào Nữ Thánh Được Ban Phước xưa kia...
+          <t>Sau thất bại của Kẻ Giả Mạo Quân Chủ, Rinascita tạm thời được hưởng một khoảng bình yên ngắn ngủi. Để mở Nang Văn Minh mà Imperator để lại, cậu và Abby chuẩn bị cho Ragunna tìm kiếm Cartethyia, nhưng lại phát hiện người dân nơi đây đang bị ám ảnh bởi những cơn ác mộng. Trong khi đó, tại Tháp Đảo Ngược, Avinoleum, Kẻ Sát Discord trở về đã nổ súng vào Nữ Thánh Được Ban Phước xưa kia...
 Với cái "chết" của Cartethyia, "câu chuyện" của Fractsidus tại Rinascita sắp đi đến hồi kết. Leviathan đã tái sinh từ Viên Ngọc, và Thiên Đường Lang Thang trong lời tiên tri bắt đầu hạ xuống. Dù không còn Thần tính nào hiện diện trên mảnh đất này, những gương mặt quen thuộc đã bắt đầu hành động để ngăn chặn ngày tận thế của Rinascita. Mang theo ý chí của mọi người, cậu quyết tâm bước vào Bóng Tối Thủy Triều...</t>
         </is>
       </c>
@@ -16981,8 +16949,8 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Second Coming of Solaris&lt;/i&gt;, tác phẩm của Karl đến từ New Federation, đã trở nên phổ biến rộng rãi và tiếp tục bán chạy trên toàn cầu. Cuốn sách không chỉ giàu trí tưởng tượng mà còn cung cấp những hiểu biết quý giá về địa lý và lịch sử, mang đến một thế giới quan chặt chẽ.
-Pioneer Association gần đây đã giành được quyền chuyển thể game cho &lt;i&gt;Second Coming of Solaris&lt;/i&gt;, nhưng dường như họ đang gặp khó khăn và cần sự trợ giúp của anh.</t>
+          <t>&lt;i&gt;Sự Trở Lại Của Solaris&lt;/i&gt;, tác phẩm của Karl đến từ Liên Bang Mới, đã trở nên phổ biến rộng rãi và tiếp tục bán chạy trên toàn cầu. Cuốn sách không chỉ giàu trí tưởng tượng mà còn cung cấp những hiểu biết quý giá về địa lý và lịch sử, mang đến một thế giới quan chặt chẽ.
+Hiệp Hội Tiên Phong gần đây đã giành được quyền chuyển thể game cho &lt;i&gt;Sự Trở Lại Của Solaris&lt;/i&gt;, nhưng dường như họ đang gặp khó khăn và cần sự trợ giúp của anh.</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17080,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Sau khi khu vực phức tạp của Khu Phố Cổ Septimont được tiết lộ nhờ công tác thoát nước gần đây, thành phố chính thức công bố một sự kiện hấp dẫn—Cuộc Săn Discord Giả Lập! Các Chiến Binh dũng cảm, hãy bước tới! Tham gia cuộc săn và tự mình khắc ghi con đường vinh quang chiến thắng!</t>
+          <t>Sau khi khu vực phức tạp của Khu Phố Cổ Septimont được tiết lộ nhờ công tác thoát nước gần đây, thành phố chính thức công bố một sự kiện hấp dẫn—Cuộc Săn Tacet Discord Giả Lập! Các Chiến Binh dũng cảm, hãy bước tới! Tham gia cuộc săn và tự mình khắc ghi con đường vinh quang chiến thắng!</t>
         </is>
       </c>
     </row>
@@ -17311,9 +17279,9 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Round 1 hoàn tất!
+          <t>Vòng 1 hoàn tất!
 Cậu đã nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17380,9 +17348,9 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Round 10 hoàn tất!
+          <t>Vòng 10 hoàn tất!
 Cậu đã nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17449,9 +17417,9 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Round 11 hoàn tất!
+          <t>Vòng 11 hoàn tất!
 Cậu đã nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17518,9 +17486,9 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Round 12 hoàn tất!
+          <t>Vòng 12 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17587,9 +17555,9 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Round 2 hoàn tất!
+          <t>Vòng 2 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17656,9 +17624,9 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Round 3 hoàn tất!
+          <t>Vòng 3 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17725,9 +17693,9 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Round 4 hoàn tất!
+          <t>Vòng 4 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Bonus Cube kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Thưởng Khối Lập Phương kích hoạt: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17794,9 +17762,9 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Round 5 hoàn tất!
+          <t>Vòng 5 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Phát động Tăng Cường Cube: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Phát động Tăng Cường Khối Lập Phương: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17863,9 +17831,9 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Round 6 hoàn tất!
+          <t>Vòng 6 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Phát động Tăng Cường Cube: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Phát động Tăng Cường Khối Lập Phương: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -17932,9 +17900,9 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Round 7 hoàn tất!
+          <t>Vòng 7 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Phát động Tăng Cường Cube: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Phát động Tăng Cường Khối Lập Phương: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -18001,9 +17969,9 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Round 8 hoàn tất!
+          <t>Vòng 8 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Phát động Tăng Cường Cube: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Phát động Tăng Cường Khối Lập Phương: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -18070,9 +18038,9 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Round 9 hoàn tất!
+          <t>Vòng 9 hoàn tất!
 Bạn nhận được sự trợ giúp từ {0}.
-Xúc xắc ra: {1}. Phát động Tăng Cường Cube: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
+Xúc xắc ra: {1}. Phát động Tăng Cường Khối Lập Phương: &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}.</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18105,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Huanglong là một quốc gia với lịch sử hàng nghìn năm. Lịch sử lâu đời đã hun đúc nên một nền văn hóa đặc sắc và truyền thống cho dân tộc này. Dù Vết Nứt Than Thở đã làm gián đoạn sự phát triển, nhưng người dân nơi đây vẫn không ngừng chiến đấu và nỗ lực kế thừa những gì còn sót lại của đất nước. Trong kỷ nguyên Phục Hưng, ngành công nghiệp Echo của Huanglong đã mang lại sức sống mới cho quốc gia này. Nhờ nhu cầu không ngừng về Echo, nền kinh tế Huanglong chưa bao giờ ngừng bùng nổ.</t>
+          <t>Huanglong là một quốc gia với lịch sử hàng nghìn năm. Lịch sử lâu đời đã hun đúc nên một nền văn hóa đặc sắc và truyền thống cho dân tộc này. Dù Vết Nứt Than Thở đã làm gián đoạn sự phát triển, nhưng người dân nơi đây vẫn không ngừng chiến đấu và nỗ lực kế thừa những gì còn sót lại của đất nước. Trong kỷ nguyên Phục Hưng, ngành công nghiệp Tổ Tacet của Huanglong đã mang lại sức sống mới cho quốc gia này. Nhờ nhu cầu không ngừng về Tổ Tacet, nền kinh tế Huanglong chưa bao giờ ngừng bùng nổ.</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18302,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Trái tim của Đại Khổ Nạn, nơi các Chiến Binh và Echoes chiến đấu bên nhau. Với những trang thiết bị tối tân, đấu trường tổ chức những giải đấu sôi động với mọi quy mô, được truyền hình trực tiếp khắp Solaris. Ở đây, không khí luôn ngập tràn tiếng hò reo cuồng nhiệt của đám đông, xé tan bầu không khí tĩnh lặng của màn đêm quanh năm. Đó là nơi máu của ngươi sôi lên khi chứng kiến mồ hôi, nước mắt và cả máu của các Chiến Binh chiến đấu vì vinh quang.</t>
+          <t>Trái tim của Đại Khổ Nạn, nơi các Chiến Binh và Echo chiến đấu bên nhau. Với những trang thiết bị tối tân, đấu trường tổ chức những giải đấu sôi động với mọi quy mô, được truyền hình trực tiếp khắp Solaris. Ở đây, không khí luôn ngập tràn tiếng hò reo cuồng nhiệt của đám đông, xé tan bầu không khí tĩnh lặng của màn đêm quanh năm. Đó là nơi máu của ngươi sôi lên khi chứng kiến mồ hôi, nước mắt và cả máu của các Chiến Binh chiến đấu vì vinh quang.</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18367,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Một khu vực dưới chân Capitoline Hill, gần Pháo đài Borderline. Những đàn gia súc thong dong gặm cỏ trên những đồng cỏ tươi tốt, và những ngôi làng nhỏ nằm rải rác giữa những tàn tích cổ xưa. Dù trong sự yên bình ấy, những đấu trường nhỏ vẫn là một phần không thể thiếu của cuộc sống.</t>
+          <t>Một khu vực dưới chân Đồi Capitoline, gần Pháo đài Borderline. Những đàn gia súc thong dong gặm cỏ trên những đồng cỏ tươi tốt, và những ngôi làng nhỏ nằm rải rác giữa những tàn tích cổ xưa. Dù trong sự yên bình ấy, những đấu trường nhỏ vẫn là một phần không thể thiếu của cuộc sống.</t>
         </is>
       </c>
     </row>
@@ -18659,7 +18627,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ngày xưa, một con rồng đã chết tại vùng Border Mountains, thu hút vô số tần số bất hòa. Qua năm tháng, khu vực này tràn ngập Tacet Discord và những sinh vật hung dữ. Những người Septimontian tiên phong coi đây là bãi thử thách cho các chiến binh chứng tỏ bản lĩnh, để lại vô số huyền thoại hào hùng. Điều này tiếp diễn cho đến khi làn Sóng Hắc Ám đầu tiên ập đến, tàn phá nơi thánh địa thử thách này và chôn vùi danh dự của nó dưới Hắc Triều.</t>
+          <t>Ngày xưa, một con rồng đã chết tại vùng Núi Biên Giới, thu hút vô số tần số bất hòa. Qua năm tháng, khu vực này tràn ngập Tacet Discord và những sinh vật hung dữ. Những người Septimontian tiên phong coi đây là bãi thử thách cho các chiến binh chứng tỏ bản lĩnh, để lại vô số huyền thoại hào hùng. Điều này tiếp diễn cho đến khi làn Sóng Hắc Ám đầu tiên ập đến, tàn phá nơi thánh địa thử thách này và chôn vùi danh dự của nó dưới Hắc Triều.</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18693,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Được biết đến với tên gọi chính thức là "Khối Dư Âm", đây là những trí tuệ nhân tạo tiên tiến được tạo ra cho Second Coming of Solaris, sử dụng khả năng của Encore và sự hỗ trợ vi xử lý từ Tethys.
+          <t>Được biết đến với tên gọi chính thức là "Khối Dư Âm", đây là những trí tuệ nhân tạo tiên tiến được tạo ra cho Sự Trở Lại Của Solaris, sử dụng khả năng của Encore và sự hỗ trợ vi xử lý từ Tethys.
 Khối Dư Âm khác biệt với nguyên bản ở mức độ từ tinh tế đến rõ ràng. Nguyên nhân của những biến thể này vẫn chưa rõ ràng. Liệu đó là do người dùng đóng vai trò điểm neo, sự hỗ trợ quét dữ liệu của Tethys, hay sự tự do sáng tạo của Encore với tư cách là nghệ nhân bậc thầy?</t>
         </is>
       </c>
@@ -18794,7 +18762,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro của Ciaccona, được tạo ra từ nhận thức của cô về những giai điệu và tiếng vọng.
+          <t>Sonoro Sphere của Ciaccona, được tạo ra từ nhận thức của cô về những giai điệu và tiếng vọng.
 Những ký ức và câu chuyện mà giai điệu mang theo hiện lên ở đây như những hình ảnh tĩnh lặng, đông cứng.
 Nhưng qua sự điều chỉnh của Ciaccona, những câu chuyện và ký ức ấy kết hợp lại thành những nốt nhạc trên bản nhạc.
 Khi những nốt nhạc vang lên, hình ảnh bắt đầu chuyển động và trỗi dậy.</t>
@@ -18998,7 +18966,7 @@
       <c r="M255" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Ta rất vui khi thấy ngươi trở lại bờ biển này."
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Main: Chương I Act VIII "Tận Cùng Bờ Vực" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính: Chương I Hồi VIII "Tận Cùng Bờ Vực" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19065,7 +19033,7 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; "Hoa khao khát ánh sáng và nước. Đó là bản năng của chúng."
-&lt;color=#ffd12f&gt;[Prerequisite Quest]&lt;/color&gt; Hoàn thành Nhiệm vụ Main: Chương I Act VIII "Tận Cùng Bờ Biển" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiên quyết]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính: Chương I Hồi VIII "Tận Cùng Bờ Biển" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19100,7 @@
       <c r="M257" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Này, ừm... sao cậu không gia nhập Đoàn Kẻ Ngốc nhỉ?"
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19167,7 @@
       <c r="M258" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Còn tùy vào lúc nào cuộc phiêu lưu tiếp theo gọi tên! Cậu biết mà, tớ sẽ sẵn sàng sát cánh cùng cậu ngay khi cậu lên tiếng."
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19266,7 +19234,7 @@
       <c r="M259" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; "Nhưng ta sẽ giữ cái biệt danh này cho cậu, Mắt Mèo - thành viên đầu tiên và duy nhất nhận được lời mời đặc biệt từ ta."
-&lt;color=#ffd12f&gt;[Prerequisite Quest]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiên quyết]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19333,7 +19301,7 @@
       <c r="M260" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Ta, Cantarella Fisalia, xin trao tặng ngươi toàn bộ gia sản của gia tộc—mọi loại thuốc tiên và bí mật thâm sâu nhất."
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act IV "Thiếu Nữ, Kẻ Nổi Loạn, Người Rao Tin Tử Thần" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi IV "Thiếu Nữ, Kẻ Nổi Loạn, Người Rao Tin Tử Thần" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19368,7 @@
       <c r="M261" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; "Tạm biệt, Nhà Thơ!"
-&lt;color=#ffd12f&gt;[Prerequisite Quest]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiên quyết]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19502,7 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Gửi những vị khách từ phương xa..."
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Main Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành Nhiệm vụ Chính Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Sẽ Cất Lên Tiếng Ca" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19569,7 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Câu chuyện vẫn tiếp diễn. Phần hay nhất vẫn còn ở phía trước."
-&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành "Nhiệm vụ Abbowser" trong Event "Cube, Cubic n Cubie" để mở khóa.</t>
+&lt;color=#ffd12f&gt;[Nhiệm vụ tiền đề]&lt;/color&gt; Hoàn thành "Nhiệm vụ Abbowser" trong Sự kiện "Cube, Cubic n Cubie" để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -19731,7 +19699,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>"Người dân Septimont sẽ không bao giờ quên những chiến công của các anh hùng. Nơi đây đứng sừng sững bức tượng vĩ đại của Hero of Heroes, ánh mắt Người là ngọn hải đăng bất diệt thúc đẩy chúng ta tiến về phía trước."</t>
+          <t>"Người dân Septimont sẽ không bao giờ quên những chiến công của các anh hùng. Nơi đây đứng sừng sững bức tượng vĩ đại của Anh Hùng Trong Các Anh Hùng, ánh mắt Người là ngọn hải đăng bất diệt thúc đẩy chúng ta tiến về phía trước."</t>
         </is>
       </c>
     </row>
@@ -19929,8 +19897,8 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>“Vì vinh quang, không sợ chết.” Like Ragunna, Septimont là một thành bang của Rinascita, nhưng người dân nơi đây tôn thờ không phải thần linh, mà là những anh hùng bằng xương bằng thịt.
-Nổi tiếng với các Võ Sĩ Giác Đấu, Thành Phố Glory này đang đăng cai Đại Hội Agon—một giải đấu hoành tráng được tổ chức bốn năm một lần.”</t>
+          <t>“Vì vinh quang, không sợ chết.” Giống như Ragunna, Septimont là một thành bang của Rinascita, nhưng người dân nơi đây tôn thờ không phải thần linh, mà là những anh hùng bằng xương bằng thịt.
+Nổi tiếng với các Võ Sĩ Giác Đấu, Thành Phố Vinh Quang này đang đăng cai Đại Hội Agon—một giải đấu hoành tráng được tổ chức bốn năm một lần.”</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20032,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Cartethyia biến mất trong Inverted Tower. Theo dấu vết nàng để lại, cậu đến Septimont, một trong những thành bang của Rinascita, nơi ngập tràn vinh quang và nổi tiếng với truyền thống đấu sĩ. Thành phố đang tổ chức Đại Hội Agon—một giải đấu lớn diễn ra bốn năm một lần. Nhưng dưới vẻ hào nhoáng đó, bóng tối đang nhen nhóm. Nhiều thế lực hoạt động trong bí mật, mỗi bên đều có âm mưu riêng. Để vén màn sự thật, cậu tạm liên minh với Đấu Thủ Lupa. Cùng nhau, hai người hướng đến ngôi vị vô địch...</t>
+          <t>Cartethyia biến mất trong Tháp Đảo Ngược. Theo dấu vết nàng để lại, cậu đến Septimont, một trong những thành bang của Rinascita, nơi ngập tràn vinh quang và nổi tiếng với truyền thống đấu sĩ. Thành phố đang tổ chức Đại Hội Agon—một giải đấu lớn diễn ra bốn năm một lần. Nhưng dưới vẻ hào nhoáng đó, bóng tối đang nhen nhóm. Nhiều thế lực hoạt động trong bí mật, mỗi bên đều có âm mưu riêng. Để vén màn sự thật, cậu tạm liên minh với Đấu Thủ Lupa. Cùng nhau, hai người hướng đến ngôi vị vô địch...</t>
         </is>
       </c>
     </row>
@@ -20264,8 +20232,8 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Dù Terminal là công cụ quan trọng của Resonators, mọi thứ lại hoàn toàn khác ở Rinascita...
-(Đính kèm trang là bức ảnh do Alannah mang đến, chụp một Terminal ở Ragunna.)</t>
+          <t>Dù Thiết bị đầu cuối là công cụ quan trọng của Resonator, mọi thứ lại hoàn toàn khác ở Rinascita...
+(Đính kèm trang là bức ảnh do Alannah mang đến, chụp một Thiết bị đầu cuối ở Ragunna.)</t>
         </is>
       </c>
     </row>
@@ -20666,8 +20634,8 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dù Terminal là công cụ thiết yếu của Resonators, Terminal Dự phòng lại là cảnh tượng hiếm thấy ở Ragunna.
-(Đính kèm trang là bức ảnh do Alannah mang đến, chụp một Terminal ở Ragunna.)</t>
+          <t>Dù Thiết bị đầu cuối là công cụ thiết yếu của Resonator, Thiết bị đầu cuối Dự phòng lại là cảnh tượng hiếm thấy ở Ragunna.
+(Đính kèm trang là bức ảnh do Alannah mang đến, chụp một Thiết bị đầu cuối ở Ragunna.)</t>
         </is>
       </c>
     </row>
@@ -20733,8 +20701,8 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Khác với cư dân Jinzhou đã quen với các phương tiện nhân tạo, phương tiện di chuyển ở Rinascita chủ yếu là Echoes.
-(Đính kèm là bức ảnh Alannah mang về, chụp chiếc Gondola Echoes đặc biệt ở Ragunna.)</t>
+          <t>Khác với cư dân Jinzhou đã quen với các phương tiện nhân tạo, phương tiện di chuyển ở Rinascita chủ yếu là Echo.
+(Đính kèm là bức ảnh Alannah mang về, chụp chiếc Gondola Echo đặc biệt ở Ragunna.)</t>
         </is>
       </c>
     </row>
@@ -20996,7 +20964,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Một cơ sở lưu giữ bộ sưu tập nghệ thuật và những Echoes hiếm có từ khắp nơi trên thế giới, thậm chí còn bao gồm cả những hiện vật sống sót qua Lament và Echoes từ thời cổ đại. Sự kết hợp của vô vàn bộ sưu tập rực rỡ này tạo nên cấu trúc của chính "nghệ thuật".</t>
+          <t>Một cơ sở lưu giữ bộ sưu tập nghệ thuật và những Echo hiếm có từ khắp nơi trên thế giới, thậm chí còn bao gồm cả những hiện vật sống sót qua Lament và Echo từ thời cổ đại. Sự kết hợp của vô vàn bộ sưu tập rực rỡ này tạo nên cấu trúc của chính "nghệ thuật".</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21094,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Sau New Solar Ceremony, cuộc sống học đường của bạn bắt đầu. Trong lớp, bạn gặp một "cô gái ma" tên Aemeath, một Synchronist được cho là đã chết hơn một thập kỷ trước. Tại sao cô ấy vẫn còn ở Học Viện? Mối liên hệ giữa cô ấy và bạn là gì? Để tìm hiểu sự thật về cô ấy và nguyên nhân khiến tần số của bạn dần phai nhạt, bạn và Aemeath lên đường đến Roya Frostlands, nơi Exostrider đang yên giấc.</t>
+          <t>Sau Lễ Hội Mặt Trời Mới, cuộc sống học đường của bạn bắt đầu. Trong lớp, bạn gặp một "cô gái ma" tên Aemeath, một Đồng Bộ Giả được cho là đã chết hơn một thập kỷ trước. Tại sao cô ấy vẫn còn ở Học Viện? Mối liên hệ giữa cô ấy và bạn là gì? Để tìm hiểu sự thật về cô ấy và nguyên nhân khiến tần số của bạn dần phai nhạt, bạn và Aemeath lên đường đến Roya Frostlands, nơi Exostrider đang yên giấc.</t>
         </is>
       </c>
     </row>
@@ -21191,7 +21159,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Khi New Solar Celebration bắt đầu, không khí lễ hội tràn ngập Học Viện Startorch. Nhưng bên dưới bề mặt ấy, những tần số bất thường đang âm ỉ trong Dark Side - chiều không gian tiềm thức sinh ra từ cảm xúc của học sinh. Theo yêu cầu của Hiệu Trưởng Lucilla, cậu bước vào thế giới tâm linh này và gặp Sigrika - một học sinh ưu tú được ca ngợi là người kế vị tương lai của Heliodic Six. Khi tiến sâu hơn, cậu sớm nhận ra những lời thì thầm và bí ẩn ám ảnh Dark Side ẩn chứa một âm mưu đen tối hơn nhiều...</t>
+          <t>Khi Lễ Hội Mặt Trời Mới bắt đầu, không khí lễ hội tràn ngập Học Viện Startorch. Nhưng bên dưới bề mặt ấy, những tần số bất thường đang âm ỉ trong Dark Side - chiều không gian tiềm thức sinh ra từ cảm xúc của học sinh. Theo yêu cầu của Hiệu Trưởng Lucilla, cậu bước vào thế giới tâm linh này và gặp Sigrika - một học sinh ưu tú được ca ngợi là người kế vị tương lai của Heliodic Six. Khi tiến sâu hơn, cậu sớm nhận ra những lời thì thầm và bí ẩn ám ảnh Dark Side ẩn chứa một âm mưu đen tối hơn nhiều...</t>
         </is>
       </c>
     </row>
@@ -21256,7 +21224,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Sau khi sự cố Mặt Tối của Học Viện được giải quyết, cuộc truy tìm Fractsidus đã đưa cậu chạm mặt ngắn ngủi với một vị miko tóc trắng lạnh lùng, tay cầm lưỡi kiếm. Nhưng trước khi Kẻ Đi Ngoài Hành Tinh có thể thức tỉnh, những Tacet Discord ở vùng đồng bằng ngầm Dimmr Plains bắt đầu bùng phát với tần số đáng báo động, buộc Spacetrek Collective phải cân nhắc kế hoạch sơ tán khẩn cấp khỏi Lahai-Roi. Để giữ cho kế hoạch về Kẻ Đi Ngoài Hành Tinh không bị đổ vỡ, cậu lập tức hành động. Và khi Void Storm lan rộng, "vỏ bọc" im lặng của Aemeath dường như đang thì thầm một mình...</t>
+          <t>Sau khi sự cố Mặt Tối của Học Viện được giải quyết, cuộc truy tìm Fractsidus đã đưa cậu chạm mặt ngắn ngủi với một vị miko tóc trắng lạnh lùng, tay cầm lưỡi kiếm. Nhưng trước khi Kẻ Đi Ngoài Hành Tinh có thể thức tỉnh, những Tacet Discord ở vùng đồng bằng ngầm Dimmr Plains bắt đầu bùng phát với tần số đáng báo động, buộc Spacetrek Collective phải cân nhắc kế hoạch sơ tán khẩn cấp khỏi Lahai-Roi. Để giữ cho kế hoạch về Kẻ Đi Ngoài Hành Tinh không bị đổ vỡ, cậu lập tức hành động. Và khi Bão Hư Không lan rộng, "vỏ bọc" im lặng của Aemeath dường như đang thì thầm một mình...</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21549,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Sonoro Sphere có Dodget tương đồng với Tacet Field, nhưng mang những đặc điểm rõ rệt hơn. Nó được cấu thành từ Resonators bị quá tải. Sonoro Sphere này nằm trong đống đổ nát của một thành phố thuộc Cảng Guixu. Phân tích Tần số cho thấy nó được tạo ra vào thời Chiến tranh Threnody bởi một vị tướng quân. Xét về thời gian và danh tính, bên trong Sonoro Sphere này ẩn chứa rủi ro cực cao.</t>
+          <t>Khối Sonoro có nét tương đồng với Tổ Tacet, nhưng mang những đặc điểm rõ rệt hơn. Nó được cấu thành từ các Resonator bị quá tải. Khối Sonoro này nằm trong đống đổ nát của một thành phố thuộc Cảng Guixu. Phân tích Tần số cho thấy nó được tạo ra vào thời Chiến tranh Threnody bởi một vị tướng quân. Xét về thời gian và danh tính, bên trong Khối Sonoro này ẩn chứa rủi ro cực cao.</t>
         </is>
       </c>
     </row>
@@ -21711,7 +21679,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Sonoro Sphere có Dodget tương đồng với Tacet Field, nhưng mang những đặc điểm rõ rệt hơn. Nó được cấu thành từ Resonators bị quá tải. Khối cầu này ẩn mình trong Rừng Mù. Tương truyền, nó thuộc về một Resonators tinh thông thuật trị thương. Nhưng dù vậy, phân tích vẫn cho thấy bên trong chứa đựng rủi ro cực cao.</t>
+          <t>Khối Sonoro có nét tương đồng với Tổ Tacet, nhưng mang những đặc điểm rõ rệt hơn. Nó được cấu thành từ các Resonator bị quá tải. Khối cầu này ẩn mình trong Rừng Mù. Tương truyền, nó thuộc về một Resonator tinh thông thuật trị thương. Nhưng dù vậy, phân tích vẫn cho thấy bên trong chứa đựng rủi ro cực cao.</t>
         </is>
       </c>
     </row>
@@ -21841,7 +21809,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Pioneer Association đã xây dựng Căn Cứ Tiền Tuyến mô phỏng theo giếng tháp Tower of Adversity. Tất cả nhân sự phải hoàn thành huấn luyện thích ứng tại đây trước khi được cấp phép thám hiểm.</t>
+          <t>Hiệp Hội Tiên Phong đã xây dựng Căn Cứ Tiền Tuyến mô phỏng theo giếng tháp Tháp Nghịch Cảnh. Tất cả nhân sự phải hoàn thành huấn luyện thích ứng tại đây trước khi được cấp phép thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21874,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Pioneer Association đã xây dựng Căn Cứ Tiền Tuyến mô phỏng theo giếng tháp Tower of Adversity. Tất cả nhân sự phải hoàn thành huấn luyện thích ứng tại đây trước khi được cấp phép thám hiểm.</t>
+          <t>Hiệp Hội Tiên Phong đã xây dựng Căn Cứ Tiền Tuyến mô phỏng theo giếng tháp Tháp Nghịch Cảnh. Tất cả nhân sự phải hoàn thành huấn luyện thích ứng tại đây trước khi được cấp phép thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22200,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Hiệp hội Tiên Phong, ban đầu có tên là Hiệp hội Geography Toàn cầu, là tổ chức khoa học và giáo dục được thành lập trước Sự Than Thở.
+          <t>Hiệp hội Tiên Phong, ban đầu có tên là Hiệp hội Địa lý Toàn cầu, là tổ chức khoa học và giáo dục được thành lập trước Sự Than Thở.
 Sau Đại Thủy Triều, Hiệp hội đã hợp tác với các nhà khoa học, nhiếp ảnh gia và nhà báo để tiếp tục khám phá thế giới bí ẩn sau thảm họa, chia sẻ những phát hiện với công chúng qua tạp chí, bản đồ, sách, các dự án trải nghiệm giải trí thực địa và truyền thông tương tác, thu hút lượng lớn người hâm mộ tại sáu khu vực.</t>
         </is>
       </c>
@@ -22558,7 +22526,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>The Black Shores là một tổ chức bí ẩn cống hiến cho việc cứu thế giới khỏi diệt vong. Họ đi đến những nơi nguy hiểm nhất, chiêu mộ những đồng minh dũng cảm và không bao giờ đánh mất nhiệt huyết lý tưởng của mình. Những ai gia nhập hoặc được mời đến hòn đảo của họ sẽ đeo biểu tượng Hoa Blake như một dấu hiệu của thành viên.</t>
+          <t>Bờ Biển Đen là một tổ chức bí ẩn cống hiến cho việc cứu thế giới khỏi diệt vong. Họ đi đến những nơi nguy hiểm nhất, chiêu mộ những đồng minh dũng cảm và không bao giờ đánh mất nhiệt huyết lý tưởng của mình. Những ai gia nhập hoặc được mời đến hòn đảo của họ sẽ đeo biểu tượng Hoa Blake như một dấu hiệu của thành viên.</t>
         </is>
       </c>
     </row>
@@ -22688,7 +22656,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Sức mạnh của Vòng Lặp Tang Tóc gây ra những đợt sóng hủy diệt trên mảnh đất Solaris. Những hiện tượng như "Tacet Field", "Bùng phát Discord" và khoáng vật bí ẩn "Tacetite" đều thuộc nhóm hiện tượng gọi chung là "Hiện tượng Dư Âm".</t>
+          <t>Sức mạnh của Vòng Lặp Tang Tóc gây ra những đợt sóng hủy diệt trên mảnh đất Solaris. Những hiện tượng như "Tổ Tacet", "Bùng phát Tacet Discord" và khoáng vật bí ẩn "Tacetite" đều thuộc nhóm hiện tượng gọi chung là "Hiện tượng Dư Âm".</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22786,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>"Tacet Field" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu hiệu Tacet hình chữ thập sâu thẳm dưới mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một Sợi Resonance Cord trắng. Những khu vực này thu hút sự tụ tập của các Tacet Discord.</t>
+          <t>"Tổ Tacet" được cho là nơi khởi nguồn của mọi Tacet Discord. Những địa điểm này có bầu trời là biển đảo ngược và một dấu hiệu Tacet hình chữ thập sâu thẳm dưới mặt đất. Âm vang tràn ngập không khí, kết nối thế giới của chúng ta với một không gian bí ẩn thông qua một Sợi Dây Cộng Hưởng trắng. Những khu vực này thu hút sự tụ tập của các Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -22883,7 +22851,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Những cá nhân có khả năng cộng hưởng với một số vật thể và điều khiển tần số của chúng được gọi là "Resonators". Những người này thể hiện "Năng Lực Resonance" độc đáo, hay còn gọi là "Thế Mạnh" của họ, thông qua "Tacet Mark" trên cơ thể. Theo các chuyên gia, năng lực của Resonators thường chịu ảnh hưởng bởi trải nghiệm quá khứ và tiềm thức của họ.</t>
+          <t>Những cá nhân có khả năng cộng hưởng với một số vật thể và điều khiển tần số của chúng được gọi là "Resonator". Những người này thể hiện "Năng Lực Cộng Hưởng" độc đáo, hay còn gọi là "Thế Mạnh" của họ, thông qua "Dấu Tacet" trên cơ thể. Theo các chuyên gia, năng lực của Resonator thường chịu ảnh hưởng bởi trải nghiệm quá khứ và tiềm thức của họ.</t>
         </is>
       </c>
     </row>
@@ -22948,7 +22916,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tacet Discord, sinh ra từ Waveworn Phenomena, là những thực thể nguy hiểm với hình dạng bất định, luôn biến đổi. Chúng sở hữu "Lõi Tacet" và hấp thụ các tần số khác để duy trì sự ổn định cũng như tiến hóa. Những sinh vật này bắt chước khả năng, hình dáng và hành vi của con mồi, phụ thuộc vào loại tần số mà chúng tiêu thụ.</t>
+          <t>Tacet Discord, sinh ra từ Hiện Tượng Sóng Mòn, là những thực thể nguy hiểm với hình dạng bất định, luôn biến đổi. Chúng sở hữu "Lõi Tacet" và hấp thụ các tần số khác để duy trì sự ổn định cũng như tiến hóa. Những sinh vật này bắt chước khả năng, hình dáng và hành vi của con mồi, phụ thuộc vào loại tần số mà chúng tiêu thụ.</t>
         </is>
       </c>
     </row>
@@ -23014,8 +22982,8 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Một loại tần số đặc biệt có thể được Terminal thu thập để tái tạo khả năng của Tacet Discord.
-Khi bị tiêu diệt, Tacet Discord có thể để lại "Dư Âm", sau đó được chuyển hóa thành "Echoes" thông qua Data Bank của Terminal, mang lại lợi thế hữu ích trong trận chiến.</t>
+          <t>Một loại tần số đặc biệt có thể được Thiết bị đầu cuối thu thập để tái tạo khả năng của Tacet Discord.
+Khi bị tiêu diệt, Tacet Discord có thể để lại "Dư Âm", sau đó được chuyển hóa thành "Echo" thông qua Ngân Hàng Dữ Liệu của Thiết bị đầu cuối, mang lại lợi thế hữu ích trong trận chiến.</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23113,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Jinzhou, một thành phố pháo đài ở vùng biên giới, đứng vững trước cuộc khủng hoảng Discord đang đe dọa. Là một trong sáu khu vực lớn của Huanglong, nó gánh vác trách nhiệm này với tư cách là thủ phủ cấp tỉnh trẻ nhất. Đội Midnight Rangers bảo vệ biên giới phía bắc mà không chút do dự.</t>
+          <t>Jinzhou, một thành phố pháo đài ở vùng biên giới, đứng vững trước cuộc khủng hoảng Tacet Discord đang đe dọa. Là một trong sáu khu vực lớn của Huanglong, nó gánh vác trách nhiệm này với tư cách là thủ phủ cấp tỉnh trẻ nhất. Đội Midnight Rangers bảo vệ biên giới phía bắc mà không chút do dự.</t>
         </is>
       </c>
     </row>
@@ -23210,7 +23178,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Threnodian là những sinh vật đáng sợ sinh ra từ Nỗi Than Khóc, mang sức mạnh hủy diệt tinh thần con người và nuôi dưỡng bản thân bằng ý chí sụp đổ của họ. Nếu nền văn minh đại diện cho ý chí tập thể của nhân loại, thì Threnodian chính là hiện thân của nỗi sợ hãi và những đấu tranh của chúng ta. Chúng xuất hiện như những thảm họa Discord hủy diệt, lan tràn khắp hành tinh.</t>
+          <t>Threnodian là những sinh vật đáng sợ sinh ra từ Nỗi Than Khóc, mang sức mạnh hủy diệt tinh thần con người và nuôi dưỡng bản thân bằng ý chí sụp đổ của họ. Nếu nền văn minh đại diện cho ý chí tập thể của nhân loại, thì Threnodian chính là hiện thân của nỗi sợ hãi và những đấu tranh của chúng ta. Chúng xuất hiện như những thảm họa Tacet Discord hủy diệt, lan tràn khắp hành tinh.</t>
         </is>
       </c>
     </row>
@@ -23342,7 +23310,7 @@
       <c r="M321" t="inlineStr">
         <is>
           <t>Một dạng năng lượng thuần khiết với tần số hoàn chỉnh. Thông tin mà nó mang theo vượt qua thời gian và không gian, tồn tại trong trạng thái ổn định và bất biến.
-Trong quá trình nghiên cứu Waveworn Phenomena, các nhà khoa học đã phát hiện ra "Tacetite"—một chất có thể lưu giữ Năng Lượng Tàn Dư vĩnh viễn. Tacetite có thể được chế tạo thành vũ khí mạnh mẽ cho Resonators chống lại Tacet Discord. Những không gian đa chiều nơi Năng Lượng Tàn Dư dồi dào được gọi là Sonoro Spheres.</t>
+Trong quá trình nghiên cứu Hiện Tượng Sóng Mòn, các nhà khoa học đã phát hiện ra "Tacetite"—một chất có thể lưu giữ Năng Lượng Tàn Dư vĩnh viễn. Tacetite có thể được chế tạo thành vũ khí mạnh mẽ cho Resonator chống lại Tacet Discord. Những không gian đa chiều nơi Năng Lượng Tàn Dư dồi dào được gọi là Sonoro Spheres.</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23700,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Khi một giai điệu lạc điệu trôi qua bầu trời đêm, những ngọn đuốc từng soi sáng các vì sao giờ đây lại nuốt chửng chúng trong biển lửa đỏ thẫm. Hãy lắng nghe tiếng kêu thật sự ẩn giấu trong Lament, và đối mặt với chúng bằng lòng dũng cảm không lay chuyển. Hy vọng sẽ được tái sinh.</t>
+          <t>Khi một giai điệu lạc điệu trôi qua bầu trời đêm, những ngọn đuốc từng soi sáng các vì sao giờ đây lại nuốt chửng chúng trong biển lửa đỏ thẫm. Hãy lắng nghe tiếng kêu thật sự ẩn giấu trong Lời Than Vãn, và đối mặt với chúng bằng lòng dũng cảm không lay chuyển. Hy vọng sẽ được tái sinh.</t>
         </is>
       </c>
     </row>
@@ -23797,7 +23765,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Khi một giai điệu lạc điệu trôi qua bầu trời đêm, những ngọn đuốc từng soi sáng các vì sao giờ đây lại nuốt chửng chúng trong biển lửa đỏ thẫm. Hãy lắng nghe tiếng kêu thật sự ẩn giấu trong Lament, và đối mặt với chúng bằng lòng dũng cảm không lay chuyển. Hy vọng sẽ được tái sinh.</t>
+          <t>Khi một giai điệu lạc điệu trôi qua bầu trời đêm, những ngọn đuốc từng soi sáng các vì sao giờ đây lại nuốt chửng chúng trong biển lửa đỏ thẫm. Hãy lắng nghe tiếng kêu thật sự ẩn giấu trong Lời Than Vãn, và đối mặt với chúng bằng lòng dũng cảm không lay chuyển. Hy vọng sẽ được tái sinh.</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24025,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Khu vườn nằm sâu trong lòng thiên hà ngầm, vừa là thấu kính quan sát vũ trụ bao la, vừa là nơi ở của Shorekeeper trong thời gian bị Tethys Hệ thống giam cầm. Người ta nói khu vườn đã tồn tại từ trước khi Black Shores được thành lập, như con mắt dõi theo những vì sao. Nhưng những gì con mắt nhìn thấy có thể trái tim vẫn không hay biết. Những chân lý nào ẩn sau những khái niệm tối cao này?</t>
+          <t>Khu vườn nằm sâu trong lòng thiên hà ngầm, vừa là thấu kính quan sát vũ trụ bao la, vừa là nơi ở của Shorekeeper trong thời gian bị Tethys System giam cầm. Người ta nói khu vườn đã tồn tại từ trước khi Black Shores được thành lập, như con mắt dõi theo những vì sao. Nhưng những gì con mắt nhìn thấy có thể trái tim vẫn không hay biết. Những chân lý nào ẩn sau những khái niệm tối cao này?</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24091,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Một thị trấn cổ yên bình Dodgep mình trong vòng tay tĩnh lặng của Núi Firmament. Những công trình thanh lịch điểm xuyết giữa lá đỏ và tuyết trắng tạo nên khung cảnh đẹp đến nao lòng.
+          <t>Một thị trấn cổ yên bình nép mình trong vòng tay tĩnh lặng của Núi Firmament. Những công trình thanh lịch điểm xuyết giữa lá đỏ và tuyết trắng tạo nên khung cảnh đẹp đến nao lòng.
 Qua nhiều thế kỷ, người dân Hongzhen tôn thờ Người Canh Gác bảo vệ thị trấn như thần linh, thành kính cầu nguyện cho sự thịnh vượng và trường thọ. Dù tuyết phủ quanh năm trên Núi Firmament, những dòng suối nóng từ núi cùng sức sống mãnh liệt của dân làng khiến cái lạnh chẳng còn là nỗi lo.</t>
         </is>
       </c>
@@ -24465,7 +24433,7 @@
         <is>
           <t>Tương lai ngoài Hệ thống này nằm ngoài tầm mắt.
 Sự sụp đổ của nó sẽ mở ra sự diệt vong không thể tránh khỏi của thế giới.
-Frozen, xé nát, thiêu đốt trong biển lửa... Vậy thì, hãy chiêm ngưỡng sự kết thúc của thế giới.</t>
+Đóng băng, xé nát, thiêu đốt trong biển lửa... Vậy thì, hãy chiêm ngưỡng sự kết thúc của thế giới.</t>
         </is>
       </c>
     </row>
@@ -24530,7 +24498,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Mảnh đất chìm trong biển lửa, trong khi Necrostar nuốt chửng bầu trời. Hố đen trên đỉnh Port City of Guixu đánh dấu sự khởi đầu và kết thúc của sự hủy diệt. Nó cũng nắm giữ chìa khóa cứu rỗi... Hay chỉ là một lời dối trá.</t>
+          <t>Mảnh đất chìm trong biển lửa, trong khi Necrostar nuốt chửng bầu trời. Hố đen trên đỉnh Thành Phố Cảng Guixu đánh dấu sự khởi đầu và kết thúc của sự hủy diệt. Nó cũng nắm giữ chìa khóa cứu rỗi... Hay chỉ là một lời dối trá.</t>
         </is>
       </c>
     </row>
@@ -24666,7 +24634,7 @@
       <c r="M341" t="inlineStr">
         <is>
           <t>Một quốc gia gồm các thành bang độc lập nằm rải rác trên quần đảo rộng lớn, không có trung tâm hành chính tập trung. Truyền thuyết kể về những người khai phá Rinascita, họ đã rời bỏ quê hương, vượt biển đến những hòn đảo này để thoát khỏi Lament.
-Người Rinascita, với "Echo Chung" độc đáo, đã hòa nhập Echo vào mọi mặt của cuộc sống. Đó là lý do quốc gia này được gọi là "Land of Echoes."</t>
+Người Rinascita, với "Tiếng Vọng Chung" độc đáo, đã hòa nhập Tiếng Vọng vào mọi mặt của cuộc sống. Đó là lý do quốc gia này được gọi là "Vùng Đất Tiếng Vọng."</t>
         </is>
       </c>
     </row>
@@ -24993,7 +24961,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Được xây dựng bởi gia tộc Montelli, Kho Averardo sừng sững như một pháo đài kiên cố ở ngoại ô thành phố. Bên trong những bức tường ấy là kho báu khổng lồ của gia tộc, bao gồm kim loại quý, tác phẩm nghệ thuật và những Echoes hiếm có. Kho này còn cung cấp dịch vụ công cộng như lưu trữ an toàn đồ vật giá trị, thẩm định và mua bán các bộ sưu tập quý hiếm.</t>
+          <t>Được xây dựng bởi gia tộc Montelli, Kho Averardo sừng sững như một pháo đài kiên cố ở ngoại ô thành phố. Bên trong những bức tường ấy là kho báu khổng lồ của gia tộc, bao gồm kim loại quý, tác phẩm nghệ thuật và những Echo hiếm có. Kho này còn cung cấp dịch vụ công cộng như lưu trữ an toàn đồ vật giá trị, thẩm định và mua bán các bộ sưu tập quý hiếm.</t>
         </is>
       </c>
     </row>
@@ -25319,8 +25287,8 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Averardo Bank sử dụng hệ thống tàu Echo để vận chuyển bộ sưu tập của khách hàng và nhân viên đến và đi từ Averardo Vault.
-Khi tàu Echo đến ga ngầm của Averardo Vault, các bộ sưu tập sẽ được phân loại lần hai trước khi chuyển đến các kho lưu trữ chuyên dụng.</t>
+          <t>Ngân Hàng Averardo sử dụng hệ thống tàu Echo để vận chuyển bộ sưu tập của khách hàng và nhân viên đến và đi từ Kho Tàng Averardo.
+Khi tàu Echo đến ga ngầm của Kho Tàng Averardo, các bộ sưu tập sẽ được phân loại lần hai trước khi chuyển đến các kho lưu trữ chuyên dụng.</t>
         </is>
       </c>
     </row>
@@ -25385,7 +25353,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Một cơ sở lưu giữ bộ sưu tập các tác phẩm nghệ thuật và Echoes hiếm từ khắp nơi trên thế giới, thậm chí còn bao gồm cả những hiện vật còn sót lại từ Lời Than Thở và Echoes từ thời cổ đại.</t>
+          <t>Một cơ sở lưu giữ bộ sưu tập các tác phẩm nghệ thuật và Echo hiếm từ khắp nơi trên thế giới, thậm chí còn bao gồm cả những hiện vật còn sót lại từ Lời Than Thở và Echo từ thời cổ đại.</t>
         </is>
       </c>
     </row>
@@ -25980,7 +25948,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonators** lẫn vũ khí.</t>
+          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonator** lẫn vũ khí.</t>
         </is>
       </c>
     </row>
@@ -26045,7 +26013,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonators** lẫn vũ khí.</t>
+          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonator** lẫn vũ khí.</t>
         </is>
       </c>
     </row>
@@ -26244,7 +26212,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Những kẻ vô tri cản trở tiến bộ, trong khi những người vô tội phải gánh chịu thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xôi, được tiếp sức bởi hoàn cảnh hiện tại, thắp lên nỗi đau quá khứ của Scar và sự tái sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
+          <t>Kẻ ngu muội cản trở tiến bộ, còn người vô tội phải gánh chịu những thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xưa, được thổi bùng bởi hoàn cảnh hiện tại, đốt cháy nỗi đau quá khứ của Scar và sự hồi sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
         </is>
       </c>
     </row>
@@ -26309,7 +26277,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonators** lẫn vũ khí.</t>
+          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonator** lẫn vũ khí.</t>
         </is>
       </c>
     </row>
@@ -26374,7 +26342,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonators** lẫn vũ khí.</t>
+          <t>Một biến thể độc đáo của **Sonoro Sphere**, lưu giữ khoảnh khắc thời gian. Bên trong nó, cậu sẽ tìm thấy những sản phẩm phụ của **Waveworn**, có thể tăng cường sức mạnh cho cả **Resonator** lẫn vũ khí.</t>
         </is>
       </c>
     </row>
@@ -26506,7 +26474,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kho tàng do gia tộc Montelli kiểm soát lưu giữ bộ sưu tập Echoes quý hiếm và tác phẩm nghệ thuật tuyệt đẹp. Được bao quanh bởi những bức tường thiên nhiên và nằm trên địa thế cao, nơi đây mang đến tầm nhìn tuyệt đẹp về Nimbus Sanctum.</t>
+          <t>Kho tàng do gia tộc Montelli kiểm soát lưu giữ bộ sưu tập Echo quý hiếm và tác phẩm nghệ thuật tuyệt đẹp. Được bao quanh bởi những bức tường thiên nhiên và nằm trên địa thế cao, nơi đây mang đến tầm nhìn tuyệt đẹp về Nimbus Sanctum.</t>
         </is>
       </c>
     </row>
@@ -26638,7 +26606,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Điểm sâu nhất của Averardo Vault. Những nhân viên cấp thấp thậm chí còn không biết đến sự tồn tại của nơi này. Truyền thuyết kể rằng kẻ xâm nhập sẽ phải đối mặt với số phận của mình dưới tay của Echo Guard, từ trên cao lao xuống để thi hành án.</t>
+          <t>Điểm sâu nhất của Hầm Averardo. Những nhân viên cấp thấp thậm chí còn không biết đến sự tồn tại của nơi này. Truyền thuyết kể rằng kẻ xâm nhập sẽ phải đối mặt với số phận của mình dưới tay của Echo Guard, từ trên cao lao xuống để thi hành án.</t>
         </is>
       </c>
     </row>
@@ -26902,7 +26870,7 @@
       <c r="M375" t="inlineStr">
         <is>
           <t>Lễ hội thường niên ở Thị trấn Egla để tưởng nhớ những người đã khuất.
-Khi màn đêm buông xuống, dân làng đeo mặt nạ và hóa trang thành hồn ma để tham dự buổi tưởng niệm. Theo truyền thuyết, vào Night Tưởng Nhớ, những linh hồn oán hận sẽ trở về cõi trần. Ai dám chắc kẻ đang vui chơi bên cạnh ngươi là người... hay thứ gì khác?</t>
+Khi màn đêm buông xuống, dân làng đeo mặt nạ và hóa trang thành hồn ma để tham dự buổi tưởng niệm. Theo truyền thuyết, vào Đêm Tưởng Nhớ, những linh hồn oán hận sẽ trở về cõi trần. Ai dám chắc kẻ đang vui chơi bên cạnh ngươi là người... hay thứ gì khác?</t>
         </is>
       </c>
     </row>
@@ -26967,7 +26935,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Một Discord cực mạnh xuất hiện tại Thành phố Cảng Guixu. Theo lời nhân chứng, chuyển động của nó khác biệt so với các Discord khác, cần nghiên cứu thêm để có thông tin chi tiết.</t>
+          <t>Một Tacet Discord cực mạnh xuất hiện tại Thành phố Cảng Guixu. Theo lời nhân chứng, chuyển động của nó khác biệt so với các Tacet Discord khác, cần nghiên cứu thêm để có thông tin chi tiết.</t>
         </is>
       </c>
     </row>
@@ -27032,7 +27000,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Một Discord cực mạnh trú ngụ sâu trong lòng Hố Hổ. Rất ít báo cáo về việc nhìn thấy nó, và những người từng thấy đều nói rằng nó giống côn trùng.</t>
+          <t>Một Tacet Discord cực mạnh trú ngụ sâu trong lòng Hố Hổ. Rất ít báo cáo về việc nhìn thấy nó, và những người từng thấy đều nói rằng nó giống côn trùng.</t>
         </is>
       </c>
     </row>
@@ -27097,7 +27065,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Một Discord được phát hiện tại Central Plains. Chỉ có duy nhất một báo cáo từ Rover về sự xuất hiện của nó. Không có ghi chép chi tiết về hình dáng đầy đủ, nhưng dựa vào mức năng lượng, nó được đánh giá là cực kỳ nguy hiểm.</t>
+          <t>Một Tacet Discord được phát hiện tại Central Plains. Chỉ có duy nhất một báo cáo từ Rover về sự xuất hiện của nó. Không có ghi chép chi tiết về hình dáng đầy đủ, nhưng dựa vào mức năng lượng, nó được đánh giá là cực kỳ nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27198,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Rover thân mến:
+          <t>Vận Mệnh Giả thân mến:
 Sau khi hoàn tất hoàn tiền, phần thưởng bạn nhận được từ sự kiện Moonlit Path sẽ bị thu hồi sau &lt;color=highlight&gt;{0}&lt;/color&gt;. Hãy thu thập đủ số Moonlit Rings cần thiết trước &lt;color=highlight&gt;{0}&lt;/color&gt; để giữ lại những phần thưởng này.
 Nếu có bất kỳ thắc mắc nào, vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.
 Cảm ơn sự ủng hộ và thông cảm của bạn dành cho Wuthering Waves!</t>
@@ -27301,7 +27269,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Gửi Rover:
+          <t>Gửi Vận Mệnh Giả:
 Sau khi hoàn trả đơn hàng của bạn, phần thưởng Đường Ánh Trăng tương ứng đã bị thu hồi.
 Nếu có bất kỳ thắc mắc nào, hãy liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.
 Cảm ơn bạn đã luôn ủng hộ và thông cảm cho Wuthering Waves!</t>
@@ -27971,7 +27939,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Thân vệ của Chúa Dragon lạnh lẽo như băng tuyết.
+          <t>Thân vệ của Chúa Rồng lạnh lẽo như băng tuyết.
 Trong mắt nàng, mọi thứ trên thế giới đều méo mó thành những hình thù kỳ lạ, chỉ có vài thứ còn giữ được vẻ thuần khiết và bình thường.</t>
         </is>
       </c>
@@ -28038,7 +28006,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Thân vệ của Chúa Dragon lạnh lẽo như băng tuyết.
+          <t>Thân vệ của Chúa Rồng lạnh lẽo như băng tuyết.
 Trong mắt nàng, mọi thứ trên thế giới đều méo mó thành những hình thù kỳ lạ, chỉ có vài thứ còn giữ được vẻ thuần khiết và bình thường.</t>
         </is>
       </c>
@@ -28105,7 +28073,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Thân vệ của Chúa Dragon lạnh lẽo như băng tuyết.
+          <t>Thân vệ của Chúa Rồng lạnh lẽo như băng tuyết.
 Trong mắt nàng, mọi thứ trên thế giới đều méo mó thành những hình thù kỳ lạ, chỉ có vài thứ còn giữ được vẻ thuần khiết và bình thường.</t>
         </is>
       </c>
@@ -28171,7 +28139,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Tacet Field mức độ rủi ro trung bình. Nhiều Tacet Discord ẩn náu bên trong, mang đến những mối nguy hiểm nhất định. Dựa trên dữ liệu hiện có, Rover có 99,6% khả năng vượt qua Tổ an toàn. Nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Tổ Tacet mức độ rủi ro trung bình. Nhiều Tacet Discord ẩn náu bên trong, mang đến những mối nguy hiểm nhất định. Dựa trên dữ liệu hiện có, Vận Mệnh Giả có 99,6% khả năng vượt qua Tổ an toàn. Nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28236,7 +28204,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tacet Field này nằm phía tây Thành phố Cảng Guixu, là mối nguy hiểm đáng kể do tính chất rủi ro cao và dao động bất thường của năng lượng Fusion. Cuộc điều tra ban đầu thất bại, dẫn đến thông tin chi tiết vẫn còn chưa rõ.</t>
+          <t>Tổ Tacet này nằm phía tây Thành phố Cảng Guixu, là mối nguy hiểm đáng kể do tính chất rủi ro cao và dao động bất thường của năng lượng Fusion. Cuộc điều tra ban đầu thất bại, dẫn đến thông tin chi tiết vẫn còn chưa rõ.</t>
         </is>
       </c>
     </row>
@@ -28301,7 +28269,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Một Discord được quan sát thấy ở Central Plains, chỉ có một báo cáo nhìn thấy TD này từ Rover. Không có ghi chép chi tiết về diện mạo đầy đủ của nó, và nó được đánh giá là cực kỳ nguy hiểm dựa trên mức năng lượng.</t>
+          <t>Một Tacet Discord được quan sát tại Central Plains, chỉ có duy nhất một báo cáo nhìn thấy từ Rover. Không có ghi chép chi tiết về hình dáng đầy đủ của nó, nhưng dựa trên mức năng lượng, nó được đánh giá là cực kỳ nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28334,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28431,7 +28399,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28496,7 +28464,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28561,7 +28529,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28626,7 +28594,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28691,7 +28659,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28756,7 +28724,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28821,7 +28789,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Một Tacet Field có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
+          <t>Một Tổ Tacet có mức độ nguy hiểm trung bình. Những Tacet Discord ẩn nấp bên trong có thể gây ra mối đe dọa nhất định cho bất kỳ ai dám thách thức. Dù dữ liệu hiện tại cho thấy Rover có 99,6% khả năng vượt qua Tổ này mà không hề hấn gì, nhưng hãy nhớ lời dạy của Huanglong: "Cẩn thận dẫn đến hoàn hảo."</t>
         </is>
       </c>
     </row>
@@ -28887,7 +28855,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
 Số lượng tối đa của vật phẩm tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -28954,8 +28922,8 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Tiêu diệt Tacet Discord sẽ nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Tiêu diệt Tacet Discord sẽ nhận thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits.</t>
         </is>
       </c>
     </row>
@@ -29021,8 +28989,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Mỗi lần mua vật phẩm hoặc Chiến Thuật, bạn nhận được &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Mỗi lần mua vật phẩm hoặc Chiến Thuật, bạn nhận được &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits.</t>
         </is>
       </c>
     </row>
@@ -29088,8 +29056,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Shop KU-Money cần ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits để làm mới.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
+Cửa Hàng KU-Money cần ít hơn &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credit để làm mới.</t>
         </is>
       </c>
     </row>
@@ -29155,8 +29123,8 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Nimbus Wraith rơi thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; Lucky Coin.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Nimbus Wraith rơi thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; Đồng Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -29222,8 +29190,8 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Độ Bền còn lại của Energy Matrix giảm xuống &lt;color=Highlight&gt;{0}&lt;/color&gt;, và bạn nhận được &lt;color=Highlight&gt;{1}&lt;/color&gt; Sim Creditss.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Độ Bền còn lại của Energy Matrix giảm xuống &lt;color=Highlight&gt;{0}&lt;/color&gt;, và bạn nhận được &lt;color=Highlight&gt;{1}&lt;/color&gt; Sim Credits.</t>
         </is>
       </c>
     </row>
@@ -29289,7 +29257,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
 Số lượng tối đa của vật phẩm tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, giới hạn ở &lt;color=Highlight&gt;{1}&lt;/color&gt; lớp.</t>
         </is>
       </c>
@@ -29356,8 +29324,8 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Mỗi lần Shop KU-Money làm mới, sẽ có thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; vật phẩm được hiển thị.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/SapTag&gt;
+Mỗi lần Cửa Hàng KU-Money làm mới, sẽ có thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/color&gt;&lt;/color&gt; vật phẩm được hiển thị.</t>
         </is>
       </c>
     </row>
@@ -29423,8 +29391,8 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Shop KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/SapTag&gt;
+Cửa Hàng KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/color&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}.</t>
         </is>
       </c>
     </row>
@@ -29490,8 +29458,8 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Silver Bullet&lt;/te&gt;]&lt;/color&gt;
-Sau mỗi đợt sóng, bạn nhận được tiền lãi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss hiện có.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Đạn Bạc&lt;/te&gt;]&lt;/color&gt;
+Sau mỗi đợt sóng, bạn nhận được tiền lãi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits hiện có.</t>
         </is>
       </c>
     </row>
@@ -29557,8 +29525,8 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Silver Bullet&lt;/te&gt;]&lt;/color&gt;
-Sau mỗi đợt sóng, bạn nhận được tiền lãi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss hiện có.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750029&gt;Viên Đạn Bạc&lt;/te&gt;]&lt;/color&gt;
+Sau mỗi đợt sóng, bạn nhận được tiền lãi bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits hiện có.</t>
         </is>
       </c>
     </row>
@@ -29624,8 +29592,8 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Lucky Coin mang lại thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss. Có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất nhân đôi số Sim Creditss nhận được từ Lucky Coin.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Đồng Xu May Mắn mang lại thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits. Có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất nhân đôi số Sim Credits nhận được từ Đồng Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -29691,8 +29659,8 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Lucky Coin mang lại thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss. Có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất nhân đôi số Sim Creditss nhận được từ Lucky Coin.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Đồng Xu May Mắn mang lại thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits. Có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất nhân đôi số Sim Credits nhận được từ Đồng Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -29759,9 +29727,9 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Shop KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}. Chi phí vật phẩm và chiến thuật giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.
-Chiến thuật này sẽ kích hoạt vào lần xuất hiện tiếp theo của Shop KU-Money.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/SapTag&gt;
+Cửa Hàng KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/color&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}. Chi phí vật phẩm và chiến thuật giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.
+Chiến thuật này sẽ kích hoạt vào lần xuất hiện tiếp theo của Cửa Hàng KU-Money.</t>
         </is>
       </c>
     </row>
@@ -29828,9 +29796,9 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Shop KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}. Chi phí vật phẩm và chiến thuật giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.
-Chiến thuật này sẽ kích hoạt vào lần xuất hiện tiếp theo của Shop KU-Money.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/SapTag&gt;
+Cửa Hàng KU-Money có thể làm mới &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/color&gt;&lt;/color&gt; {Cus:Sap,S=lần nữa P=lần nữa SapTag=0}. Chi phí vật phẩm và chiến thuật giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.
+Chiến thuật này sẽ kích hoạt vào lần xuất hiện tiếp theo của Cửa Hàng KU-Money.</t>
         </is>
       </c>
     </row>
@@ -29896,8 +29864,8 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Sau khi mua vật phẩm hoặc Tactics tại Shop KU-Money, &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss đã tiêu sẽ được hoàn lại sau &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; lượt.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
+Sau khi mua vật phẩm hoặc Chiến Thuật tại Cửa Hàng KU-Money, &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits đã tiêu sẽ được hoàn lại sau &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; lượt.</t>
         </is>
       </c>
     </row>
@@ -29963,8 +29931,8 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Shop KU-Money&lt;/te&gt;]&lt;/color&gt;
-Sau khi mua vật phẩm hoặc Tactics tại Shop KU-Money, &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Creditss đã tiêu sẽ được hoàn lại sau &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; lượt.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750027&gt;Cửa Hàng KU-Money&lt;/te&gt;]&lt;/color&gt;
+Sau khi mua vật phẩm hoặc Chiến Thuật tại Cửa Hàng KU-Money, &lt;color=Highlight&gt;{0}&lt;/color&gt; Sim Credits đã tiêu sẽ được hoàn lại sau &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; lượt.</t>
         </is>
       </c>
     </row>
@@ -30030,8 +29998,8 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Sau khi tiêu diệt &lt;color=Highlight&gt;{0}&lt;/color&gt; Tacet Discord, &lt;color=Highlight&gt;{1}&lt;/color&gt; đống Lucky Coin sẽ xuất hiện gần đó.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Sau khi tiêu diệt &lt;color=Highlight&gt;{0}&lt;/color&gt; Tacet Discord, &lt;color=Highlight&gt;{1}&lt;/color&gt; đống Đồng Xu May Mắn sẽ xuất hiện gần đó.</t>
         </is>
       </c>
     </row>
@@ -30097,8 +30065,8 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Lucky Coin&lt;/te&gt;]&lt;/color&gt;
-Sau khi tiêu diệt &lt;color=Highlight&gt;{0}&lt;/color&gt; Tacet Discord, &lt;color=Highlight&gt;{1}&lt;/color&gt; đống Lucky Coin sẽ xuất hiện gần đó.</t>
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750026&gt;Đồng Xu May Mắn&lt;/te&gt;]&lt;/color&gt;
+Sau khi tiêu diệt &lt;color=Highlight&gt;{0}&lt;/color&gt; Tacet Discord, &lt;color=Highlight&gt;{1}&lt;/color&gt; đống Đồng Xu May Mắn sẽ xuất hiện gần đó.</t>
         </is>
       </c>
     </row>
@@ -30165,7 +30133,7 @@
       <c r="M424" t="inlineStr">
         <is>
           <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Aero xung quanh Máy Combat &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Attack Speed của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+Mỗi Máy Chiến Đấu Kiểu Aero xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Tốc Độ Tấn Công của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -30232,7 +30200,7 @@
       <c r="M425" t="inlineStr">
         <is>
           <t>&lt;color=#e8aa32&gt;[&lt;te href=750033&gt;Trường Tăng Cường&lt;/te&gt;]&lt;/color&gt;
-Mỗi Máy Combat Kiểu Aero xung quanh Máy Combat &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Attack Speed của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
+Mỗi Máy Chiến Đấu Kiểu Aero xung quanh Máy Chiến Đấu &lt;color=Highlight&gt;Kiểu Echo&lt;/color&gt; sẽ tăng Tốc Độ Tấn Công của nó thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -30297,7 +30265,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt;, &lt;color=#8c7e51&gt;{1}&lt;/color&gt; và &lt;color=#8c7e51&gt;{2}&lt;/color&gt; Echoes. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
+          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt;, &lt;color=#8c7e51&gt;{1}&lt;/color&gt; và &lt;color=#8c7e51&gt;{2}&lt;/color&gt; Echo. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30330,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt; và &lt;color=#8c7e51&gt;{1}&lt;/color&gt; Echoes. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
+          <t>Vật liệu đã chọn bao gồm &lt;color=#8c7e51&gt;{0}&lt;/color&gt; và &lt;color=#8c7e51&gt;{1}&lt;/color&gt; Echo. Phần EXP dư thừa sẽ được chuyển đổi thành vật liệu sau. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -30696,7 +30664,7 @@
         <is>
           <t>Thời gian vẫn trôi trên
 Núi Thiên Cung.
-Trong lúc dạo bước qua Hồng Trấn sôi động nhưng yên bình và lắng nghe những câu chuyện thú vị về Núi Thiên Cung, ngươi đã gặp một thính giả bất ngờ.
+Trong lúc dạo bước qua Hongzhen sôi động nhưng yên bình và lắng nghe những câu chuyện thú vị về Núi Thiên Cung, ngươi đã gặp một thính giả bất ngờ.
 Vị Hướng Đạo Giả dịu dàng nhưng bí ẩn này đã gửi đến ngươi một lời mời khá đặc biệt...</t>
         </is>
       </c>
@@ -30829,7 +30797,7 @@
       <c r="M434" t="inlineStr">
         <is>
           <t>Shilang đang tiến hành nghiên cứu tối ưu hóa tính chất hợp kim.
-Gần đây xuất hiện một Sonoro Sphere độc đáo, và Shilang phát hiện ra rằng các hợp kim ông rèn có khả năng đặc biệt trong lĩnh vực này.</t>
+Gần đây, một Sonoro Sphere độc đáo đã xuất hiện, và Shilang phát hiện ra rằng những hợp kim anh rèn có khả năng đặc biệt trong lĩnh vực này.</t>
         </is>
       </c>
     </row>
@@ -31284,7 +31252,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Ta là Zani, nhân viên kho Averardo. Ngươi là khách hàng của ta à? Nếu vậy, ta sẽ là kiếm và khiên của ngươi. Cứ ra lệnh đi. Nếu xong việc mà ngươi để lại đánh giá tốt, ta sẽ rất biết ơn đấy.</t>
+          <t>Tao là Zani, nhân viên kho Averardo. Mày là khách hàng của tao à? Nếu vậy, tao sẽ là kiếm và khiên của mày. Cứ ra lệnh đi. Nếu xong việc mà mày để lại đánh giá tốt, tao sẽ rất biết ơn đấy.</t>
         </is>
       </c>
     </row>
@@ -31609,7 +31577,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -31953,8 +31921,8 @@
           <t>Một chương trình mô phỏng chiến đấu bí ẩn đang lan truyền chóng mặt trên Huaxu Hive của Học viện. Nhà nghiên cứu Lizhu, một người dùng tích cực, dường như có những hiểu biết sâu sắc về chương trình thú vị này...
 ——————————
 [Chia Sẻ Kiến Thức] Phiên bản mới nhất đã ra mắt. Ai biết thì biết.
-Đăng bởi: Người dùng Anonymous
-Địa chỉ IP: Jinzhou</t>
+Đăng bởi: Anonymous User
+IP address: Jinzhou</t>
         </is>
       </c>
     </row>
@@ -32028,8 +31996,8 @@
 Có vẻ như Lizhu quyết tâm tạm dừng việc lướt mạng để tập trung vào nghiên cứu. Trong lúc cậu thay cô ấy quản lý, có lẽ cũng thú vị nếu tự mình trải nghiệm xem chương trình mô phỏng mới này "đột phá hỗ trợ chế độ hai đội" có gì hot.
 ——————————
 [Chia Sẻ Kiến Thức] Thông báo cho mọi người biết là bản vá mới đã ra rồi nhé.
-Đăng bởi: Liz-HU (Offline)
-Địa chỉ IP: Jinzhou</t>
+Đăng bởi: Liz-HU (Unplugged)
+IP address: Jinzhou</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32070,7 @@
 ——————————
 [Chia Sẻ Kiến Thức] Bản vá mới đã bổ sung dữ liệu từ các khu vực khác!
 Đăng bởi: Anonymous
-Địa chỉ IP: Jinzhou</t>
+IP address: Jinzhou</t>
         </is>
       </c>
     </row>
@@ -32174,8 +32142,8 @@
           <t>Một chương trình mô phỏng chiến đấu bí ẩn đang gây sốt trên Huaxu Hive của Học viện. Lizhu, người từng hoạt động cực kỳ tích cực trên mạng, đã giao phó tài khoản Huaxu Hive của mình cho cậu để tập trung vào nghiên cứu. Để đảm bảo cô ấy hoàn thành công trình mà không bị gián đoạn, có lẽ cậu nên giữ tài khoản của cô ấy thêm một thời gian nữa...
 ——————————
 [Chia Sẻ Kiến Thức] Sắp xong luận án rồi. Bản vá mới đang chờ!
-Đăng bởi: Liz_HU (sẽ sớm trở lại)
-Địa chỉ IP: Jinzhou</t>
+Đăng bởi: Liz_HU (coming back soon)
+IP address: Jinzhou</t>
         </is>
       </c>
     </row>
@@ -32699,7 +32667,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Bộ trang phục của các nhà nghiên cứu Huaxu Academy. Ngọn lửa trong Lông Đỏ vẫn cháy dữ dội như xưa, nhưng giờ đây hắn đã tìm thấy điểm tựa, điều mà hắn nguyện cống hiến cả đời.</t>
+          <t>Bộ trang phục của các nhà nghiên cứu Học viện Huaxu. Ngọn lửa trong Lông Đỏ vẫn cháy dữ dội như xưa, nhưng giờ đây hắn đã tìm thấy điểm tựa, điều mà hắn nguyện cống hiến cả đời.</t>
         </is>
       </c>
     </row>
@@ -33875,7 +33843,7 @@
       <c r="M480" t="inlineStr">
         <is>
           <t>Có vẻ như Bãi Đen đã đạt được bước đột phá với Hộp Cát Thực Tế Vô Hạn, mang đến môi trường sống động hơn và những trận chiến gay cấn hơn. Lần này, mô phỏng diễn ra tại Penitent's End, một hòn đảo hoang tàn nơi vô số linh hồn bị lưu đày phải đón nhận số phận của mình.
-&lt;color=Highlight&gt;Sự kiện này cung cấp Resonators thử nghiệm.&lt;/color&gt;</t>
+&lt;color=Highlight&gt;Sự kiện này cung cấp Resonator thử nghiệm.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -34271,7 +34239,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Một trong những trạm vũ trụ gần quỹ đạo mà nhân loại xây dựng trước khi Etheric Sea phong tỏa Solaris. Những nhiễu loạn từ trường từ Lament đã khiến nó rơi xuống, nhưng vẫn còn nguyên vẹn phần lớn. Tàn tích của nó từng là nơi trú ẩn cho Roya khỏi cái lạnh và đóng vai trò như một tiền đồn thám hiểm.</t>
+          <t>Một trong những trạm vũ trụ gần quỹ đạo mà nhân loại xây dựng trước khi Biển Ether phong tỏa Solaris. Những nhiễu loạn từ trường từ Lament đã khiến nó rơi xuống, nhưng vẫn còn nguyên vẹn phần lớn. Tàn tích của nó từng là nơi trú ẩn cho Roya khỏi cái lạnh và đóng vai trò như một tiền đồn thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -34467,7 +34435,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Trước đây được biết đến với tên gọi Spacetrek Collective: Polar Nghiên cứu Outpost Frostlands, cơ sở này là dự án hợp tác giữa Spacetrek Collective và người Roya. Được xây dựng quanh thanh đại kiếm của Exostrider cắm sâu trong băng, nó đóng vai trò như một trung tâm hậu cần quan trọng.
+          <t>Trước đây được biết đến với tên gọi Tập Đoàn Spacetrek: Trạm Nghiên Cứu Vùng Cực Frostlands, cơ sở này là dự án hợp tác giữa Tập Đoàn Spacetrek và người Roya. Được xây dựng quanh thanh đại kiếm của Exostrider cắm sâu trong băng, nó đóng vai trò như một trung tâm hậu cần quan trọng.
 Tại đây, các nhà nghiên cứu nỗ lực khôi phục dữ liệu từ các vệ tinh và trạm vũ trụ đã rơi trước Thảm Họa, chạy chẩn đoán không xâm lấn trên Exostrider để theo dõi quá trình phục hồi, và khảo sát hệ sinh thái nhằm hồi sinh hệ thực vật và động vật cổ đại đã bị đóng băng từ lâu.</t>
         </is>
       </c>
@@ -34665,7 +34633,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Giảng đường công cộng của Startorch Academy là địa điểm chính cho các sự kiện trong nhà quy mô lớn. Nơi đây mở cửa cho các hoạt động của sinh viên. Để tổ chức sự kiện tại đây, các hội nhóm hoặc câu lạc bộ sinh viên phải nộp đề xuất và đơn đăng ký lên Hội đồng Sinh viên trước ít nhất ba ngày làm việc. Sau khi được phê duyệt, sự kiện sẽ được chính thức đăng ký và thông báo.</t>
+          <t>Giảng đường công cộng của Học viện Startorch là địa điểm chính cho các sự kiện trong nhà quy mô lớn. Nơi đây mở cửa cho các hoạt động của sinh viên. Để tổ chức sự kiện tại đây, các hội nhóm hoặc câu lạc bộ sinh viên phải nộp đề xuất và đơn đăng ký lên Hội đồng Sinh viên trước ít nhất ba ngày làm việc. Sau khi được phê duyệt, sự kiện sẽ được chính thức đăng ký và thông báo.</t>
         </is>
       </c>
     </row>
@@ -34731,7 +34699,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Được đặt theo tên của Scott Rabelle, người sáng lập Thuyết Đường Cong Resonance và là người phát minh ra Rabelle's Curve, học viện này—còn được gọi là Khoa Đồng Bộ—xác định và đào tạo các Đồng Bộ viên thông qua những phương pháp khắt khe, dựa trên dữ liệu.
+          <t>Được đặt theo tên của Scott Rabelle, người sáng lập Thuyết Đường Cong Cộng Hưởng và là người phát minh ra Đường Cong Rabelle, học viện này—còn được gọi là Khoa Đồng Bộ—xác định và đào tạo các Đồng Bộ viên thông qua những phương pháp khắt khe, dựa trên dữ liệu.
 Việc tiếp cận Học viện Rabelle đòi hỏi sự cho phép đặc biệt và thường không mở cửa cho sinh viên các khoa khác.</t>
         </is>
       </c>
@@ -34799,7 +34767,7 @@
       <c r="M494" t="inlineStr">
         <is>
           <t>Một Sonoro tập thể xuất hiện tự nhiên tại Lahai-Roi. Nguyên nhân hình thành vẫn chưa được xác nhận.
-Dưới ảnh hưởng của tiềm thức và tần số còn sót lại của Resonators tại Startorch Academy, nó dần tiến hóa thành một hình chiếu phản chiếu của Học viện, trở thành một hiện tượng độc nhất tồn tại trong khuôn viên.</t>
+Dưới ảnh hưởng của tiềm thức và tần số còn sót lại của các Resonator tại Học viện Startorch, nó dần tiến hóa thành một hình chiếu phản chiếu của Học viện, trở thành một hiện tượng độc nhất tồn tại trong khuôn viên.</t>
         </is>
       </c>
     </row>
@@ -34932,7 +34900,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Viện Nghiên Cứu đã phong ấn Mặt Tối trong những câu đố, vô hiệu hóa mối nguy hiểm và biến nó thành trò chơi thường niên mà học sinh háo hức chờ đợi.
+          <t>Viện Nghiên cứu đã phong ấn Mặt Tối trong những câu đố, vô hiệu hóa mối nguy hiểm và biến nó thành trò chơi thường niên mà học sinh háo hức chờ đợi.
 Bằng cách giải những câu đố này, học sinh đối mặt trực tiếp với nghi ngờ của bản thân, giải phóng và xua tan năng lượng tiêu cực tích tụ trong Mặt Tối.</t>
         </is>
       </c>
@@ -35066,7 +35034,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Con thỏ dẫn dắt những ai dám bước vào Mặt Tối của Học Viện, đối diện với nỗi sợ và sự thật mà họ thường Dodge.
+          <t>Con thỏ dẫn dắt những ai dám bước vào Mặt Tối của Học Viện, đối diện với nỗi sợ và sự thật mà họ thường né tránh.
 Ngay cả sau sự cố của Sigrika, vẫn có học sinh và giáo sư tiếp tục đối mặt với những vấn đề riêng trong Mặt Tối.</t>
         </is>
       </c>
@@ -35133,7 +35101,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sự kỳ vọng của mọi người giống như vàng, vừa là phước lành, vừa là gánh nặng. Ngay cả giữa tiếng cười của New Solar Celebration, sự nghi ngờ và trống rỗng vẫn có thể len lỏi.
+          <t>Sự kỳ vọng của mọi người giống như vàng, vừa là phước lành, vừa là gánh nặng. Ngay cả giữa tiếng cười của Lễ Hội Mặt Trời Mới, sự nghi ngờ và trống rỗng vẫn có thể len lỏi.
 Khi sự thật đứng trên cán cân, những bóng tối rình rập sẽ đặt ra câu hỏi sắc bén cuối cùng: Liệu hành trình khám phá có thực sự ý nghĩa?</t>
         </is>
       </c>
@@ -35266,7 +35234,7 @@
       <c r="M501" t="inlineStr">
         <is>
           <t>Mẫu Helios đầu tiên bị nuốt chửng bởi một cơn Bão Hư Không, rồi trôi dạt đến đây và thu hút sự chú ý của Soliskin.
-Hoàng hôn là khoảng thời gian sau khi mặt trời lặn. Ở Dimmr Plains, đây là nơi Soliskin tụ họp lần cuối trước khi trở về Solistrees.</t>
+Hoàng hôn là khoảng thời gian sau khi mặt trời lặn. Ở Đồng Bằng Dimmr, đây là nơi Soliskin tụ họp lần cuối trước khi trở về Solistrees.</t>
         </is>
       </c>
     </row>
